--- a/03-Testing/EduCheck_UAT_Test_Cases.xlsx
+++ b/03-Testing/EduCheck_UAT_Test_Cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/998bf0dccc2814d1/Documents/GitHub/Capstone-Project_EduCheck/03-Testing/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_AB55A9DFDD99E534B5835654768CFB5B1E04E72F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{87334B94-42BA-417B-8A90-5EB35A372524}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_AA551D3F95301D246B83569C660AF5AB7743D79A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11328" yWindow="0" windowWidth="11712" windowHeight="12240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,7 @@
     <sheet name="Defect Log" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Cases'!$A$1:$Q$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Cases'!$A$1:$Q$68</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Test Cases'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="925" uniqueCount="560">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="956" uniqueCount="576">
   <si>
     <t>EduCheck - User Acceptance Test Cases</t>
   </si>
@@ -437,6 +437,44 @@
     <t>TC-009</t>
   </si>
   <si>
+    <t>Functional suitability</t>
+  </si>
+  <si>
+    <t>Settings shows own profile and assignments</t>
+  </si>
+  <si>
+    <t>Teacher profile and assignments exist.</t>
+  </si>
+  <si>
+    <t>1. Open Settings.
+2. Check Account Information and My Assignments.
+3. Open the Dashboard.</t>
+  </si>
+  <si>
+    <t>Full name, employee no. and contact number are shown read-only, with a note to ask the Administrator for changes. My Assignments lists only this teacher's sections and subjects with the school year. The Dashboard header shows the full name.</t>
+  </si>
+  <si>
+    <t>TC-010</t>
+  </si>
+  <si>
+    <t>L-05</t>
+  </si>
+  <si>
+    <t>Account without a teacher profile</t>
+  </si>
+  <si>
+    <t>Logged in as Principal or Admin.</t>
+  </si>
+  <si>
+    <t>1. Open Settings.</t>
+  </si>
+  <si>
+    <t>Username, email, role and status are shown. No name rows and no My Assignments card appear. Nothing is broken or blank.</t>
+  </si>
+  <si>
+    <t>TC-011</t>
+  </si>
+  <si>
     <t>Weak new password is rejected</t>
   </si>
   <si>
@@ -450,13 +488,10 @@
     <t>The change is refused with a message explaining the password rule.</t>
   </si>
   <si>
-    <t>TC-010</t>
+    <t>TC-012</t>
   </si>
   <si>
     <t>User Management</t>
-  </si>
-  <si>
-    <t>Functional suitability</t>
   </si>
   <si>
     <t>Create a user account</t>
@@ -476,7 +511,7 @@
     <t>The user appears in the list with the chosen role and Active status, and can log in.</t>
   </si>
   <si>
-    <t>TC-011</t>
+    <t>TC-013</t>
   </si>
   <si>
     <t>Edit a user and deactivate it</t>
@@ -495,7 +530,7 @@
     <t>Changes are saved and shown in the list. The inactive user can no longer log in (see TC for inactive login).</t>
   </si>
   <si>
-    <t>TC-012</t>
+    <t>TC-014</t>
   </si>
   <si>
     <t>L-02</t>
@@ -511,7 +546,7 @@
     <t>The user can log in with the new password (this is the password-recovery path, see Known Limitations L-02).</t>
   </si>
   <si>
-    <t>TC-013</t>
+    <t>TC-015</t>
   </si>
   <si>
     <t>Search users</t>
@@ -529,7 +564,7 @@
     <t>Only matching users are listed.</t>
   </si>
   <si>
-    <t>TC-014</t>
+    <t>TC-016</t>
   </si>
   <si>
     <t>Teacher Management</t>
@@ -549,7 +584,7 @@
     <t>The teacher is saved and the changes appear in the list.</t>
   </si>
   <si>
-    <t>TC-015</t>
+    <t>TC-017</t>
   </si>
   <si>
     <t>Section &amp; Assignments</t>
@@ -574,7 +609,7 @@
     <t>The assignment is saved. The teacher now sees that subject and section on the upload page.</t>
   </si>
   <si>
-    <t>TC-016</t>
+    <t>TC-018</t>
   </si>
   <si>
     <t>Grade-level mismatch is rejected</t>
@@ -589,7 +624,23 @@
     <t>The assignment is refused with a message that the grade levels do not match.</t>
   </si>
   <si>
-    <t>TC-017</t>
+    <t>TC-019</t>
+  </si>
+  <si>
+    <t>Subject Teacher account cannot be Class Adviser</t>
+  </si>
+  <si>
+    <t>A section without a Class Adviser.</t>
+  </si>
+  <si>
+    <t>1. Choose a teacher with a Subject Teacher account.
+2. Leave Subject blank (Class Adviser) and save.</t>
+  </si>
+  <si>
+    <t>The assignment is refused with a message that only an Adviser account can be Class Adviser. The section's Adviser slot stays free.</t>
+  </si>
+  <si>
+    <t>TC-020</t>
   </si>
   <si>
     <t>Set section staffing mode</t>
@@ -607,7 +658,7 @@
     <t>Self-Contained: the Adviser sees the upload page. Departmentalized: the Adviser's upload menu is hidden.</t>
   </si>
   <si>
-    <t>TC-018</t>
+    <t>TC-021</t>
   </si>
   <si>
     <t>Audit Log</t>
@@ -629,7 +680,7 @@
     <t>Each action shows who did it, what was done and when.</t>
   </si>
   <si>
-    <t>TC-019</t>
+    <t>TC-022</t>
   </si>
   <si>
     <t>Upload</t>
@@ -655,7 +706,7 @@
     <t>Upload succeeds. The record shows as Validated with 0 errors and appears in the teacher's upload list.</t>
   </si>
   <si>
-    <t>TC-020</t>
+    <t>TC-023</t>
   </si>
   <si>
     <t>Only assigned subjects and sections are offered</t>
@@ -670,7 +721,7 @@
     <t>Only the teacher's own assigned subject/section pairs are listed.</t>
   </si>
   <si>
-    <t>TC-021</t>
+    <t>TC-024</t>
   </si>
   <si>
     <t>EPIC-02</t>
@@ -688,7 +739,7 @@
     <t>The upload is refused with a message that only Excel files are accepted.</t>
   </si>
   <si>
-    <t>TC-022</t>
+    <t>TC-025</t>
   </si>
   <si>
     <t>D-06</t>
@@ -706,7 +757,7 @@
     <t>The upload is refused with "The file is larger than 10 MB..."</t>
   </si>
   <si>
-    <t>TC-023</t>
+    <t>TC-026</t>
   </si>
   <si>
     <t>EPIC-02/03</t>
@@ -727,7 +778,7 @@
     <t>The upload is refused with a message that the learners do not match the section's roster.</t>
   </si>
   <si>
-    <t>TC-024</t>
+    <t>TC-027</t>
   </si>
   <si>
     <t>Validation</t>
@@ -752,7 +803,7 @@
     <t>Status is Needs Attention. Each issue lists the learner, term, rule and a readable message, with errors and warnings told apart.</t>
   </si>
   <si>
-    <t>TC-025</t>
+    <t>TC-028</t>
   </si>
   <si>
     <t>EPIC-04, D-02</t>
@@ -774,7 +825,7 @@
     <t>The new upload is Validated and replaces the earlier grades for that subject.</t>
   </si>
   <si>
-    <t>TC-026</t>
+    <t>TC-029</t>
   </si>
   <si>
     <t>D-01</t>
@@ -789,7 +840,7 @@
     <t>The DepEd rules are listed for reference. There is no way to edit or switch them off.</t>
   </si>
   <si>
-    <t>TC-027</t>
+    <t>TC-030</t>
   </si>
   <si>
     <t>US-011</t>
@@ -811,7 +862,7 @@
     <t>Upload succeeds as for a Subject Teacher.</t>
   </si>
   <si>
-    <t>TC-028</t>
+    <t>TC-031</t>
   </si>
   <si>
     <t>Consolidation</t>
@@ -832,7 +883,7 @@
     <t>Only learners of the Adviser's own section are listed, each with a subject count such as 8/8.</t>
   </si>
   <si>
-    <t>TC-029</t>
+    <t>TC-032</t>
   </si>
   <si>
     <t>§6.2, US-008</t>
@@ -850,7 +901,7 @@
     <t>No learners or grades from other sections are shown anywhere.</t>
   </si>
   <si>
-    <t>TC-030</t>
+    <t>TC-033</t>
   </si>
   <si>
     <t>EPIC-06, US-006</t>
@@ -872,7 +923,7 @@
     <t>Subject status becomes Needs Revision. The Subject Teacher gets a notification with the reason.</t>
   </si>
   <si>
-    <t>TC-031</t>
+    <t>TC-034</t>
   </si>
   <si>
     <t>EPIC-06</t>
@@ -893,7 +944,7 @@
     <t>The return is refused and the user is asked for a reason.</t>
   </si>
   <si>
-    <t>TC-032</t>
+    <t>TC-035</t>
   </si>
   <si>
     <t>Submission</t>
@@ -915,7 +966,7 @@
     <t>Status becomes Pending Approval. The Admin is notified.</t>
   </si>
   <si>
-    <t>TC-033</t>
+    <t>TC-036</t>
   </si>
   <si>
     <t>Incomplete record cannot be submitted</t>
@@ -933,7 +984,7 @@
     <t>Submission is refused: every expected subject must have a recorded grade first.</t>
   </si>
   <si>
-    <t>TC-034</t>
+    <t>TC-037</t>
   </si>
   <si>
     <t>Submit all eligible records at once</t>
@@ -948,7 +999,7 @@
     <t>Only the complete learners move to Pending Approval. Incomplete learners are skipped and counted.</t>
   </si>
   <si>
-    <t>TC-035</t>
+    <t>TC-038</t>
   </si>
   <si>
     <t>Section Progress</t>
@@ -969,7 +1020,7 @@
     <t>Each subject shows its upload/validation status and how complete the section is.</t>
   </si>
   <si>
-    <t>TC-036</t>
+    <t>TC-039</t>
   </si>
   <si>
     <t>Submission Review</t>
@@ -994,7 +1045,7 @@
     <t>Status becomes Approved. The Adviser and subject teachers are notified. The record now appears in the repository.</t>
   </si>
   <si>
-    <t>TC-037</t>
+    <t>TC-040</t>
   </si>
   <si>
     <t>Reject a submitted record with a reason</t>
@@ -1007,7 +1058,7 @@
     <t>Status becomes Rejected. The Adviser and subject teachers are notified with the reason.</t>
   </si>
   <si>
-    <t>TC-038</t>
+    <t>TC-041</t>
   </si>
   <si>
     <t>D-04</t>
@@ -1028,7 +1079,7 @@
     <t>The upload is refused because the record is approved.</t>
   </si>
   <si>
-    <t>TC-039</t>
+    <t>TC-042</t>
   </si>
   <si>
     <t>D-04, EPIC-06</t>
@@ -1044,7 +1095,7 @@
     <t>Status becomes Amendment Requested and the re-upload is then accepted.</t>
   </si>
   <si>
-    <t>TC-040</t>
+    <t>TC-043</t>
   </si>
   <si>
     <t>Principal can view school-wide data</t>
@@ -1059,7 +1110,7 @@
     <t>All sections are visible on every page.</t>
   </si>
   <si>
-    <t>TC-041</t>
+    <t>TC-044</t>
   </si>
   <si>
     <t>D-03</t>
@@ -1074,7 +1125,7 @@
     <t>No action buttons are shown. Everything is read-only.</t>
   </si>
   <si>
-    <t>TC-042</t>
+    <t>TC-045</t>
   </si>
   <si>
     <t>Repository</t>
@@ -1099,7 +1150,7 @@
     <t>Matching learners are listed for every type of search. An empty search asks for a search term.</t>
   </si>
   <si>
-    <t>TC-043</t>
+    <t>TC-046</t>
   </si>
   <si>
     <t>SF10</t>
@@ -1122,7 +1173,7 @@
     <t>Readiness is PARTIAL. The file opens in Excel with Grade 4 on the Front and Grade 5 on the Back, and prints on the official form layout.</t>
   </si>
   <si>
-    <t>TC-044</t>
+    <t>TC-047</t>
   </si>
   <si>
     <t>D-05</t>
@@ -1143,7 +1194,7 @@
     <t>Download is refused with a message that there is nothing to put on the SF10 yet, and the readiness report explains why.</t>
   </si>
   <si>
-    <t>TC-045</t>
+    <t>TC-048</t>
   </si>
   <si>
     <t>US-014</t>
@@ -1165,7 +1216,7 @@
     <t>The year is saved and appears in the readiness report and in the downloaded SF10. The action is in the audit log.</t>
   </si>
   <si>
-    <t>TC-046</t>
+    <t>TC-049</t>
   </si>
   <si>
     <t>Invalid historical grades are refused</t>
@@ -1183,7 +1234,7 @@
     <t>Saving is refused with a message naming the problem.</t>
   </si>
   <si>
-    <t>TC-047</t>
+    <t>TC-050</t>
   </si>
   <si>
     <t>Analytics</t>
@@ -1204,7 +1255,7 @@
     <t>Charts show grade distribution and subject performance, and they update when the school year changes.</t>
   </si>
   <si>
-    <t>TC-048</t>
+    <t>TC-051</t>
   </si>
   <si>
     <t>Notifications</t>
@@ -1223,7 +1274,7 @@
     <t>New notifications are shown and the unread count drops to 0.</t>
   </si>
   <si>
-    <t>TC-049</t>
+    <t>TC-052</t>
   </si>
   <si>
     <t>Mobile</t>
@@ -1249,7 +1300,7 @@
     <t>The app connects and shows the role's home screen.</t>
   </si>
   <si>
-    <t>TC-050</t>
+    <t>TC-053</t>
   </si>
   <si>
     <t>View my uploads and validation results</t>
@@ -1265,7 +1316,7 @@
     <t>Uploads match the web list. Validation issues are shown for the selected upload.</t>
   </si>
   <si>
-    <t>TC-051</t>
+    <t>TC-054</t>
   </si>
   <si>
     <t>Submit a record for approval on mobile</t>
@@ -1281,7 +1332,7 @@
     <t>Status becomes Pending Approval and matches the web app.</t>
   </si>
   <si>
-    <t>TC-052</t>
+    <t>TC-055</t>
   </si>
   <si>
     <t>Return a subject to its teacher on mobile</t>
@@ -1293,7 +1344,7 @@
     <t>Subject becomes Needs Revision and the teacher is notified.</t>
   </si>
   <si>
-    <t>TC-053</t>
+    <t>TC-056</t>
   </si>
   <si>
     <t>Approve and return records on mobile</t>
@@ -1310,7 +1361,7 @@
     <t>Statuses change to Approved and Rejected, and the web app shows the same.</t>
   </si>
   <si>
-    <t>TC-054</t>
+    <t>TC-057</t>
   </si>
   <si>
     <t>Principal is read-only on mobile</t>
@@ -1322,7 +1373,7 @@
     <t>No Approve, Return or Submit buttons are shown.</t>
   </si>
   <si>
-    <t>TC-055</t>
+    <t>TC-058</t>
   </si>
   <si>
     <t>Reliability</t>
@@ -1341,7 +1392,7 @@
     <t>Cached data is shown with an offline banner and the time it was saved. The app does not crash.</t>
   </si>
   <si>
-    <t>TC-056</t>
+    <t>TC-059</t>
   </si>
   <si>
     <t>L-01</t>
@@ -1360,7 +1411,7 @@
     <t>A notification appears in the app within about 30 seconds.</t>
   </si>
   <si>
-    <t>TC-057</t>
+    <t>TC-060</t>
   </si>
   <si>
     <t>Log out clears the session</t>
@@ -1376,7 +1427,7 @@
     <t>The second user sees only their own data. Nothing cached from the first user is shown.</t>
   </si>
   <si>
-    <t>TC-058</t>
+    <t>TC-061</t>
   </si>
   <si>
     <t>Performance</t>
@@ -1401,7 +1452,7 @@
     <t>Upload completes without a timeout. Record the seconds taken in Actual Result.</t>
   </si>
   <si>
-    <t>TC-059</t>
+    <t>TC-062</t>
   </si>
   <si>
     <t>Page load time</t>
@@ -1414,7 +1465,7 @@
     <t>Each page shows its data without timeouts. Record the seconds for each page.</t>
   </si>
   <si>
-    <t>TC-060</t>
+    <t>TC-063</t>
   </si>
   <si>
     <t>Works on Chrome, Edge and Firefox</t>
@@ -1429,7 +1480,7 @@
     <t>Same behaviour and layout in every browser. Note browser versions in Remarks.</t>
   </si>
   <si>
-    <t>TC-061</t>
+    <t>TC-064</t>
   </si>
   <si>
     <t>Layout at laptop and tablet widths</t>
@@ -1444,7 +1495,7 @@
     <t>Content stays readable, nothing overlaps, and all buttons can be reached.</t>
   </si>
   <si>
-    <t>TC-062</t>
+    <t>TC-065</t>
   </si>
   <si>
     <t>First-time task completion</t>
@@ -1459,7 +1510,7 @@
     <t>The tester completes the task without help. Note where they hesitated in Remarks.</t>
   </si>
   <si>
-    <t>TC-063</t>
+    <t>TC-066</t>
   </si>
   <si>
     <t>Light and dark theme are readable</t>
@@ -1475,7 +1526,7 @@
     <t>Text, status badges and charts are readable in both themes.</t>
   </si>
   <si>
-    <t>TC-064</t>
+    <t>TC-067</t>
   </si>
   <si>
     <t>Session expires</t>
@@ -1976,10 +2027,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2610,7 +2657,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q65"/>
+  <dimension ref="A1:Q68"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -2720,9 +2767,7 @@
         <v>84</v>
       </c>
       <c r="L2" s="16"/>
-      <c r="M2" s="17" t="s">
-        <v>30</v>
-      </c>
+      <c r="M2" s="17"/>
       <c r="N2" s="16"/>
       <c r="O2" s="18"/>
       <c r="P2" s="17"/>
@@ -2763,9 +2808,7 @@
         <v>88</v>
       </c>
       <c r="L3" s="16"/>
-      <c r="M3" s="17" t="s">
-        <v>470</v>
-      </c>
+      <c r="M3" s="17"/>
       <c r="N3" s="16"/>
       <c r="O3" s="18"/>
       <c r="P3" s="17"/>
@@ -3017,7 +3060,7 @@
       <c r="P9" s="17"/>
       <c r="Q9" s="16"/>
     </row>
-    <row r="10" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" ht="87" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="14" t="s">
         <v>127</v>
       </c>
@@ -3025,31 +3068,31 @@
         <v>122</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="D10" s="15" t="s">
         <v>77</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>78</v>
+        <v>128</v>
       </c>
       <c r="F10" s="13" t="s">
         <v>91</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>111</v>
+        <v>130</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>130</v>
+        <v>50</v>
       </c>
       <c r="K10" s="13" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L10" s="16"/>
       <c r="M10" s="17"/>
@@ -3060,22 +3103,22 @@
     </row>
     <row r="11" spans="1:17" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="14" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="D11" s="15" t="s">
         <v>77</v>
       </c>
       <c r="E11" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="F11" s="13" t="s">
         <v>134</v>
-      </c>
-      <c r="F11" s="13" t="s">
-        <v>109</v>
       </c>
       <c r="G11" s="13" t="s">
         <v>135</v>
@@ -3087,10 +3130,10 @@
         <v>137</v>
       </c>
       <c r="J11" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="K11" s="13" t="s">
         <v>138</v>
-      </c>
-      <c r="K11" s="13" t="s">
-        <v>139</v>
       </c>
       <c r="L11" s="16"/>
       <c r="M11" s="17"/>
@@ -3099,39 +3142,39 @@
       <c r="P11" s="17"/>
       <c r="Q11" s="16"/>
     </row>
-    <row r="12" spans="1:17" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="14" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="D12" s="15" t="s">
         <v>77</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="G12" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="H12" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="I12" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="H12" s="13" t="s">
+      <c r="J12" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="I12" s="13" t="s">
+      <c r="K12" s="13" t="s">
         <v>143</v>
-      </c>
-      <c r="J12" s="13" t="s">
-        <v>144</v>
-      </c>
-      <c r="K12" s="13" t="s">
-        <v>145</v>
       </c>
       <c r="L12" s="16"/>
       <c r="M12" s="17"/>
@@ -3142,10 +3185,10 @@
     </row>
     <row r="13" spans="1:17" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="14" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="C13" s="15" t="s">
         <v>45</v>
@@ -3154,22 +3197,22 @@
         <v>77</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="F13" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="G13" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="H13" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="G13" s="13" t="s">
+      <c r="I13" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="H13" s="13" t="s">
-        <v>142</v>
-      </c>
-      <c r="I13" s="13" t="s">
+      <c r="J13" s="13" t="s">
         <v>149</v>
-      </c>
-      <c r="J13" s="13" t="s">
-        <v>144</v>
       </c>
       <c r="K13" s="13" t="s">
         <v>150</v>
@@ -3181,12 +3224,12 @@
       <c r="P13" s="17"/>
       <c r="Q13" s="16"/>
     </row>
-    <row r="14" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="14" t="s">
         <v>151</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="C14" s="15" t="s">
         <v>45</v>
@@ -3195,7 +3238,7 @@
         <v>77</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>90</v>
+        <v>128</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>109</v>
@@ -3227,7 +3270,7 @@
         <v>157</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="C15" s="15" t="s">
         <v>45</v>
@@ -3236,25 +3279,25 @@
         <v>77</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>109</v>
+        <v>158</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>159</v>
       </c>
       <c r="H15" s="13" t="s">
-        <v>136</v>
+        <v>153</v>
       </c>
       <c r="I15" s="13" t="s">
         <v>160</v>
       </c>
       <c r="J15" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="K15" s="13" t="s">
         <v>161</v>
-      </c>
-      <c r="K15" s="13" t="s">
-        <v>162</v>
       </c>
       <c r="L15" s="16"/>
       <c r="M15" s="17"/>
@@ -3263,12 +3306,12 @@
       <c r="P15" s="17"/>
       <c r="Q15" s="16"/>
     </row>
-    <row r="16" spans="1:17" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="14" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>164</v>
+        <v>145</v>
       </c>
       <c r="C16" s="15" t="s">
         <v>45</v>
@@ -3277,25 +3320,25 @@
         <v>77</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>134</v>
+        <v>90</v>
       </c>
       <c r="F16" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="G16" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="H16" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="I16" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="G16" s="13" t="s">
+      <c r="J16" s="13" t="s">
         <v>166</v>
       </c>
-      <c r="H16" s="13" t="s">
+      <c r="K16" s="13" t="s">
         <v>167</v>
-      </c>
-      <c r="I16" s="13" t="s">
-        <v>168</v>
-      </c>
-      <c r="J16" s="13" t="s">
-        <v>169</v>
-      </c>
-      <c r="K16" s="13" t="s">
-        <v>170</v>
       </c>
       <c r="L16" s="16"/>
       <c r="M16" s="17"/>
@@ -3304,12 +3347,12 @@
       <c r="P16" s="17"/>
       <c r="Q16" s="16"/>
     </row>
-    <row r="17" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="14" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="C17" s="15" t="s">
         <v>45</v>
@@ -3318,25 +3361,25 @@
         <v>77</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>165</v>
+        <v>109</v>
       </c>
       <c r="G17" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="H17" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="I17" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="J17" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="H17" s="13" t="s">
-        <v>136</v>
-      </c>
-      <c r="I17" s="13" t="s">
+      <c r="K17" s="13" t="s">
         <v>173</v>
-      </c>
-      <c r="J17" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="K17" s="13" t="s">
-        <v>175</v>
       </c>
       <c r="L17" s="16"/>
       <c r="M17" s="17"/>
@@ -3347,10 +3390,10 @@
     </row>
     <row r="18" spans="1:17" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="14" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="C18" s="15" t="s">
         <v>45</v>
@@ -3359,10 +3402,10 @@
         <v>77</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="F18" s="13" t="s">
-        <v>109</v>
+        <v>176</v>
       </c>
       <c r="G18" s="13" t="s">
         <v>177</v>
@@ -3386,12 +3429,12 @@
       <c r="P18" s="17"/>
       <c r="Q18" s="16"/>
     </row>
-    <row r="19" spans="1:17" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="14" t="s">
         <v>182</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="C19" s="15" t="s">
         <v>45</v>
@@ -3400,25 +3443,25 @@
         <v>77</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="F19" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="G19" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="H19" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="I19" s="13" t="s">
         <v>184</v>
       </c>
-      <c r="G19" s="13" t="s">
+      <c r="J19" s="13" t="s">
         <v>185</v>
       </c>
-      <c r="H19" s="13" t="s">
+      <c r="K19" s="13" t="s">
         <v>186</v>
-      </c>
-      <c r="I19" s="13" t="s">
-        <v>187</v>
-      </c>
-      <c r="J19" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="K19" s="13" t="s">
-        <v>188</v>
       </c>
       <c r="L19" s="16"/>
       <c r="M19" s="17"/>
@@ -3427,39 +3470,39 @@
       <c r="P19" s="17"/>
       <c r="Q19" s="16"/>
     </row>
-    <row r="20" spans="1:17" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:17" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="14" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D20" s="15" t="s">
         <v>77</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="F20" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="G20" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="H20" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="I20" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="J20" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="K20" s="13" t="s">
         <v>191</v>
-      </c>
-      <c r="G20" s="13" t="s">
-        <v>192</v>
-      </c>
-      <c r="H20" s="13" t="s">
-        <v>193</v>
-      </c>
-      <c r="I20" s="13" t="s">
-        <v>194</v>
-      </c>
-      <c r="J20" s="13" t="s">
-        <v>195</v>
-      </c>
-      <c r="K20" s="13" t="s">
-        <v>196</v>
       </c>
       <c r="L20" s="16"/>
       <c r="M20" s="17"/>
@@ -3468,39 +3511,39 @@
       <c r="P20" s="17"/>
       <c r="Q20" s="16"/>
     </row>
-    <row r="21" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:17" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="14" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D21" s="15" t="s">
         <v>77</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>191</v>
+        <v>109</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="H21" s="13" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="I21" s="13" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="J21" s="13" t="s">
-        <v>113</v>
+        <v>196</v>
       </c>
       <c r="K21" s="13" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="L21" s="16"/>
       <c r="M21" s="17"/>
@@ -3509,39 +3552,39 @@
       <c r="P21" s="17"/>
       <c r="Q21" s="16"/>
     </row>
-    <row r="22" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:17" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="14" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D22" s="15" t="s">
         <v>77</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>78</v>
+        <v>128</v>
       </c>
       <c r="F22" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="G22" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="I22" s="13" t="s">
         <v>203</v>
       </c>
-      <c r="G22" s="13" t="s">
+      <c r="J22" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="K22" s="13" t="s">
         <v>204</v>
-      </c>
-      <c r="H22" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="I22" s="13" t="s">
-        <v>205</v>
-      </c>
-      <c r="J22" s="13" t="s">
-        <v>206</v>
-      </c>
-      <c r="K22" s="13" t="s">
-        <v>207</v>
       </c>
       <c r="L22" s="16"/>
       <c r="M22" s="17"/>
@@ -3550,12 +3593,12 @@
       <c r="P22" s="17"/>
       <c r="Q22" s="16"/>
     </row>
-    <row r="23" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:17" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="14" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>190</v>
+        <v>206</v>
       </c>
       <c r="C23" s="15" t="s">
         <v>51</v>
@@ -3564,25 +3607,25 @@
         <v>77</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>78</v>
+        <v>128</v>
       </c>
       <c r="F23" s="13" t="s">
+        <v>207</v>
+      </c>
+      <c r="G23" s="13" t="s">
+        <v>208</v>
+      </c>
+      <c r="H23" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="G23" s="13" t="s">
+      <c r="I23" s="13" t="s">
         <v>210</v>
       </c>
-      <c r="H23" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="I23" s="13" t="s">
+      <c r="J23" s="13" t="s">
         <v>211</v>
       </c>
-      <c r="J23" s="13" t="s">
+      <c r="K23" s="13" t="s">
         <v>212</v>
-      </c>
-      <c r="K23" s="13" t="s">
-        <v>213</v>
       </c>
       <c r="L23" s="16"/>
       <c r="M23" s="17"/>
@@ -3591,12 +3634,12 @@
       <c r="P23" s="17"/>
       <c r="Q23" s="16"/>
     </row>
-    <row r="24" spans="1:17" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="14" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>190</v>
+        <v>206</v>
       </c>
       <c r="C24" s="15" t="s">
         <v>51</v>
@@ -3605,25 +3648,25 @@
         <v>77</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="F24" s="13" t="s">
+        <v>207</v>
+      </c>
+      <c r="G24" s="13" t="s">
+        <v>214</v>
+      </c>
+      <c r="H24" s="13" t="s">
         <v>215</v>
       </c>
-      <c r="G24" s="13" t="s">
+      <c r="I24" s="13" t="s">
         <v>216</v>
       </c>
-      <c r="H24" s="13" t="s">
+      <c r="J24" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="K24" s="13" t="s">
         <v>217</v>
-      </c>
-      <c r="I24" s="13" t="s">
-        <v>218</v>
-      </c>
-      <c r="J24" s="13" t="s">
-        <v>219</v>
-      </c>
-      <c r="K24" s="13" t="s">
-        <v>220</v>
       </c>
       <c r="L24" s="16"/>
       <c r="M24" s="17"/>
@@ -3632,12 +3675,12 @@
       <c r="P24" s="17"/>
       <c r="Q24" s="16"/>
     </row>
-    <row r="25" spans="1:17" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="14" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="C25" s="15" t="s">
         <v>51</v>
@@ -3646,25 +3689,25 @@
         <v>77</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="F25" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="G25" s="13" t="s">
+        <v>220</v>
+      </c>
+      <c r="H25" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="I25" s="13" t="s">
+        <v>221</v>
+      </c>
+      <c r="J25" s="13" t="s">
+        <v>222</v>
+      </c>
+      <c r="K25" s="13" t="s">
         <v>223</v>
-      </c>
-      <c r="G25" s="13" t="s">
-        <v>224</v>
-      </c>
-      <c r="H25" s="13" t="s">
-        <v>225</v>
-      </c>
-      <c r="I25" s="13" t="s">
-        <v>226</v>
-      </c>
-      <c r="J25" s="13" t="s">
-        <v>227</v>
-      </c>
-      <c r="K25" s="13" t="s">
-        <v>228</v>
       </c>
       <c r="L25" s="16"/>
       <c r="M25" s="17"/>
@@ -3675,10 +3718,10 @@
     </row>
     <row r="26" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="14" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="C26" s="15" t="s">
         <v>51</v>
@@ -3687,25 +3730,25 @@
         <v>77</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="F26" s="13" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="G26" s="13" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="H26" s="13" t="s">
-        <v>232</v>
+        <v>118</v>
       </c>
       <c r="I26" s="13" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="J26" s="13" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="K26" s="13" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="L26" s="16"/>
       <c r="M26" s="17"/>
@@ -3716,37 +3759,37 @@
     </row>
     <row r="27" spans="1:17" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="14" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="D27" s="15" t="s">
         <v>77</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="F27" s="13" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="G27" s="13" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="H27" s="13" t="s">
-        <v>136</v>
+        <v>233</v>
       </c>
       <c r="I27" s="13" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="J27" s="13" t="s">
-        <v>113</v>
+        <v>235</v>
       </c>
       <c r="K27" s="13" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="L27" s="16"/>
       <c r="M27" s="17"/>
@@ -3755,39 +3798,39 @@
       <c r="P27" s="17"/>
       <c r="Q27" s="16"/>
     </row>
-    <row r="28" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:17" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="14" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>190</v>
+        <v>238</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D28" s="15" t="s">
         <v>77</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="F28" s="13" t="s">
+        <v>239</v>
+      </c>
+      <c r="G28" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="H28" s="13" t="s">
+        <v>241</v>
+      </c>
+      <c r="I28" s="13" t="s">
         <v>242</v>
       </c>
-      <c r="G28" s="13" t="s">
+      <c r="J28" s="13" t="s">
         <v>243</v>
       </c>
-      <c r="H28" s="13" t="s">
+      <c r="K28" s="13" t="s">
         <v>244</v>
-      </c>
-      <c r="I28" s="13" t="s">
-        <v>245</v>
-      </c>
-      <c r="J28" s="13" t="s">
-        <v>246</v>
-      </c>
-      <c r="K28" s="13" t="s">
-        <v>247</v>
       </c>
       <c r="L28" s="16"/>
       <c r="M28" s="17"/>
@@ -3796,39 +3839,39 @@
       <c r="P28" s="17"/>
       <c r="Q28" s="16"/>
     </row>
-    <row r="29" spans="1:17" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="14" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D29" s="15" t="s">
         <v>77</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="F29" s="13" t="s">
+        <v>246</v>
+      </c>
+      <c r="G29" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>248</v>
+      </c>
+      <c r="I29" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="J29" s="13" t="s">
         <v>250</v>
       </c>
-      <c r="G29" s="13" t="s">
+      <c r="K29" s="13" t="s">
         <v>251</v>
-      </c>
-      <c r="H29" s="13" t="s">
-        <v>252</v>
-      </c>
-      <c r="I29" s="13" t="s">
-        <v>253</v>
-      </c>
-      <c r="J29" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="K29" s="13" t="s">
-        <v>254</v>
       </c>
       <c r="L29" s="16"/>
       <c r="M29" s="17"/>
@@ -3837,39 +3880,39 @@
       <c r="P29" s="17"/>
       <c r="Q29" s="16"/>
     </row>
-    <row r="30" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:17" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="14" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D30" s="15" t="s">
         <v>77</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>78</v>
+        <v>128</v>
       </c>
       <c r="F30" s="13" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="G30" s="13" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="H30" s="13" t="s">
-        <v>258</v>
+        <v>147</v>
       </c>
       <c r="I30" s="13" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="J30" s="13" t="s">
         <v>113</v>
       </c>
       <c r="K30" s="13" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="L30" s="16"/>
       <c r="M30" s="17"/>
@@ -3878,12 +3921,12 @@
       <c r="P30" s="17"/>
       <c r="Q30" s="16"/>
     </row>
-    <row r="31" spans="1:17" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="14" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>249</v>
+        <v>206</v>
       </c>
       <c r="C31" s="15" t="s">
         <v>48</v>
@@ -3892,25 +3935,25 @@
         <v>77</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="F31" s="13" t="s">
+        <v>258</v>
+      </c>
+      <c r="G31" s="13" t="s">
+        <v>259</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>260</v>
+      </c>
+      <c r="I31" s="13" t="s">
+        <v>261</v>
+      </c>
+      <c r="J31" s="13" t="s">
         <v>262</v>
       </c>
-      <c r="G31" s="13" t="s">
+      <c r="K31" s="13" t="s">
         <v>263</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>264</v>
-      </c>
-      <c r="I31" s="13" t="s">
-        <v>265</v>
-      </c>
-      <c r="J31" s="13" t="s">
-        <v>266</v>
-      </c>
-      <c r="K31" s="13" t="s">
-        <v>267</v>
       </c>
       <c r="L31" s="16"/>
       <c r="M31" s="17"/>
@@ -3919,12 +3962,12 @@
       <c r="P31" s="17"/>
       <c r="Q31" s="16"/>
     </row>
-    <row r="32" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:17" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="14" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>249</v>
+        <v>265</v>
       </c>
       <c r="C32" s="15" t="s">
         <v>48</v>
@@ -3933,25 +3976,25 @@
         <v>77</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="F32" s="13" t="s">
+        <v>266</v>
+      </c>
+      <c r="G32" s="13" t="s">
+        <v>267</v>
+      </c>
+      <c r="H32" s="13" t="s">
+        <v>268</v>
+      </c>
+      <c r="I32" s="13" t="s">
         <v>269</v>
       </c>
-      <c r="G32" s="13" t="s">
+      <c r="J32" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="K32" s="13" t="s">
         <v>270</v>
-      </c>
-      <c r="H32" s="13" t="s">
-        <v>271</v>
-      </c>
-      <c r="I32" s="13" t="s">
-        <v>272</v>
-      </c>
-      <c r="J32" s="13" t="s">
-        <v>273</v>
-      </c>
-      <c r="K32" s="13" t="s">
-        <v>274</v>
       </c>
       <c r="L32" s="16"/>
       <c r="M32" s="17"/>
@@ -3960,12 +4003,12 @@
       <c r="P32" s="17"/>
       <c r="Q32" s="16"/>
     </row>
-    <row r="33" spans="1:17" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="14" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="C33" s="15" t="s">
         <v>48</v>
@@ -3974,25 +4017,25 @@
         <v>77</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="F33" s="13" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="G33" s="13" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="I33" s="13" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="J33" s="13" t="s">
-        <v>280</v>
+        <v>113</v>
       </c>
       <c r="K33" s="13" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="L33" s="16"/>
       <c r="M33" s="17"/>
@@ -4001,12 +4044,12 @@
       <c r="P33" s="17"/>
       <c r="Q33" s="16"/>
     </row>
-    <row r="34" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:17" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="14" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="C34" s="15" t="s">
         <v>48</v>
@@ -4015,25 +4058,25 @@
         <v>77</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="F34" s="13" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="G34" s="13" t="s">
+        <v>279</v>
+      </c>
+      <c r="H34" s="13" t="s">
+        <v>280</v>
+      </c>
+      <c r="I34" s="13" t="s">
+        <v>281</v>
+      </c>
+      <c r="J34" s="13" t="s">
+        <v>282</v>
+      </c>
+      <c r="K34" s="13" t="s">
         <v>283</v>
-      </c>
-      <c r="H34" s="13" t="s">
-        <v>284</v>
-      </c>
-      <c r="I34" s="13" t="s">
-        <v>285</v>
-      </c>
-      <c r="J34" s="13" t="s">
-        <v>286</v>
-      </c>
-      <c r="K34" s="13" t="s">
-        <v>287</v>
       </c>
       <c r="L34" s="16"/>
       <c r="M34" s="17"/>
@@ -4042,12 +4085,12 @@
       <c r="P34" s="17"/>
       <c r="Q34" s="16"/>
     </row>
-    <row r="35" spans="1:17" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="14" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="C35" s="15" t="s">
         <v>48</v>
@@ -4056,25 +4099,25 @@
         <v>77</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="F35" s="13" t="s">
-        <v>269</v>
+        <v>285</v>
       </c>
       <c r="G35" s="13" t="s">
+        <v>286</v>
+      </c>
+      <c r="H35" s="13" t="s">
+        <v>287</v>
+      </c>
+      <c r="I35" s="13" t="s">
+        <v>288</v>
+      </c>
+      <c r="J35" s="13" t="s">
         <v>289</v>
       </c>
-      <c r="H35" s="13" t="s">
+      <c r="K35" s="13" t="s">
         <v>290</v>
-      </c>
-      <c r="I35" s="13" t="s">
-        <v>291</v>
-      </c>
-      <c r="J35" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="K35" s="13" t="s">
-        <v>292</v>
       </c>
       <c r="L35" s="16"/>
       <c r="M35" s="17"/>
@@ -4083,12 +4126,12 @@
       <c r="P35" s="17"/>
       <c r="Q35" s="16"/>
     </row>
-    <row r="36" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:17" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="14" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C36" s="15" t="s">
         <v>48</v>
@@ -4097,25 +4140,25 @@
         <v>77</v>
       </c>
       <c r="E36" s="13" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="F36" s="13" t="s">
+        <v>278</v>
+      </c>
+      <c r="G36" s="13" t="s">
+        <v>293</v>
+      </c>
+      <c r="H36" s="13" t="s">
+        <v>294</v>
+      </c>
+      <c r="I36" s="13" t="s">
         <v>295</v>
       </c>
-      <c r="G36" s="13" t="s">
+      <c r="J36" s="13" t="s">
         <v>296</v>
       </c>
-      <c r="H36" s="13" t="s">
+      <c r="K36" s="13" t="s">
         <v>297</v>
-      </c>
-      <c r="I36" s="13" t="s">
-        <v>298</v>
-      </c>
-      <c r="J36" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="K36" s="13" t="s">
-        <v>299</v>
       </c>
       <c r="L36" s="16"/>
       <c r="M36" s="17"/>
@@ -4124,39 +4167,39 @@
       <c r="P36" s="17"/>
       <c r="Q36" s="16"/>
     </row>
-    <row r="37" spans="1:17" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="14" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D37" s="15" t="s">
         <v>77</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="F37" s="13" t="s">
+        <v>285</v>
+      </c>
+      <c r="G37" s="13" t="s">
+        <v>299</v>
+      </c>
+      <c r="H37" s="13" t="s">
+        <v>300</v>
+      </c>
+      <c r="I37" s="13" t="s">
+        <v>301</v>
+      </c>
+      <c r="J37" s="13" t="s">
         <v>302</v>
       </c>
-      <c r="G37" s="13" t="s">
+      <c r="K37" s="13" t="s">
         <v>303</v>
-      </c>
-      <c r="H37" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="I37" s="13" t="s">
-        <v>305</v>
-      </c>
-      <c r="J37" s="13" t="s">
-        <v>306</v>
-      </c>
-      <c r="K37" s="13" t="s">
-        <v>307</v>
       </c>
       <c r="L37" s="16"/>
       <c r="M37" s="17"/>
@@ -4167,37 +4210,37 @@
     </row>
     <row r="38" spans="1:17" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="14" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="C38" s="15" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D38" s="15" t="s">
         <v>77</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="F38" s="13" t="s">
-        <v>302</v>
+        <v>285</v>
       </c>
       <c r="G38" s="13" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="H38" s="13" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="I38" s="13" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="J38" s="13" t="s">
-        <v>266</v>
+        <v>113</v>
       </c>
       <c r="K38" s="13" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="L38" s="16"/>
       <c r="M38" s="17"/>
@@ -4208,10 +4251,10 @@
     </row>
     <row r="39" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="14" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="C39" s="15" t="s">
         <v>48</v>
@@ -4220,25 +4263,25 @@
         <v>77</v>
       </c>
       <c r="E39" s="13" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="F39" s="13" t="s">
+        <v>311</v>
+      </c>
+      <c r="G39" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="H39" s="13" t="s">
         <v>313</v>
       </c>
-      <c r="G39" s="13" t="s">
+      <c r="I39" s="13" t="s">
         <v>314</v>
       </c>
-      <c r="H39" s="13" t="s">
+      <c r="J39" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="K39" s="13" t="s">
         <v>315</v>
-      </c>
-      <c r="I39" s="13" t="s">
-        <v>316</v>
-      </c>
-      <c r="J39" s="13" t="s">
-        <v>317</v>
-      </c>
-      <c r="K39" s="13" t="s">
-        <v>318</v>
       </c>
       <c r="L39" s="16"/>
       <c r="M39" s="17"/>
@@ -4247,36 +4290,36 @@
       <c r="P39" s="17"/>
       <c r="Q39" s="16"/>
     </row>
-    <row r="40" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:17" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="14" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>301</v>
+        <v>317</v>
       </c>
       <c r="C40" s="15" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D40" s="15" t="s">
         <v>77</v>
       </c>
       <c r="E40" s="13" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="F40" s="13" t="s">
+        <v>318</v>
+      </c>
+      <c r="G40" s="13" t="s">
+        <v>319</v>
+      </c>
+      <c r="H40" s="13" t="s">
         <v>320</v>
       </c>
-      <c r="G40" s="13" t="s">
+      <c r="I40" s="13" t="s">
         <v>321</v>
       </c>
-      <c r="H40" s="13" t="s">
-        <v>315</v>
-      </c>
-      <c r="I40" s="13" t="s">
+      <c r="J40" s="13" t="s">
         <v>322</v>
-      </c>
-      <c r="J40" s="13" t="s">
-        <v>266</v>
       </c>
       <c r="K40" s="13" t="s">
         <v>323</v>
@@ -4288,39 +4331,39 @@
       <c r="P40" s="17"/>
       <c r="Q40" s="16"/>
     </row>
-    <row r="41" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:17" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="14" t="s">
         <v>324</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>54</v>
+        <v>317</v>
       </c>
       <c r="C41" s="15" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="D41" s="15" t="s">
         <v>77</v>
       </c>
       <c r="E41" s="13" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="F41" s="13" t="s">
-        <v>109</v>
+        <v>318</v>
       </c>
       <c r="G41" s="13" t="s">
         <v>325</v>
       </c>
       <c r="H41" s="13" t="s">
+        <v>320</v>
+      </c>
+      <c r="I41" s="13" t="s">
         <v>326</v>
       </c>
-      <c r="I41" s="13" t="s">
+      <c r="J41" s="13" t="s">
+        <v>282</v>
+      </c>
+      <c r="K41" s="13" t="s">
         <v>327</v>
-      </c>
-      <c r="J41" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="K41" s="13" t="s">
-        <v>328</v>
       </c>
       <c r="L41" s="16"/>
       <c r="M41" s="17"/>
@@ -4331,37 +4374,37 @@
     </row>
     <row r="42" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="14" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>54</v>
+        <v>317</v>
       </c>
       <c r="C42" s="15" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D42" s="15" t="s">
         <v>77</v>
       </c>
       <c r="E42" s="13" t="s">
-        <v>78</v>
+        <v>128</v>
       </c>
       <c r="F42" s="13" t="s">
+        <v>329</v>
+      </c>
+      <c r="G42" s="13" t="s">
         <v>330</v>
       </c>
-      <c r="G42" s="13" t="s">
+      <c r="H42" s="13" t="s">
         <v>331</v>
-      </c>
-      <c r="H42" s="13" t="s">
-        <v>326</v>
       </c>
       <c r="I42" s="13" t="s">
         <v>332</v>
       </c>
       <c r="J42" s="13" t="s">
-        <v>53</v>
+        <v>333</v>
       </c>
       <c r="K42" s="13" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L42" s="16"/>
       <c r="M42" s="17"/>
@@ -4370,21 +4413,21 @@
       <c r="P42" s="17"/>
       <c r="Q42" s="16"/>
     </row>
-    <row r="43" spans="1:17" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="14" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>335</v>
+        <v>317</v>
       </c>
       <c r="C43" s="15" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D43" s="15" t="s">
         <v>77</v>
       </c>
       <c r="E43" s="13" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="F43" s="13" t="s">
         <v>336</v>
@@ -4393,16 +4436,16 @@
         <v>337</v>
       </c>
       <c r="H43" s="13" t="s">
+        <v>331</v>
+      </c>
+      <c r="I43" s="13" t="s">
         <v>338</v>
       </c>
-      <c r="I43" s="13" t="s">
+      <c r="J43" s="13" t="s">
+        <v>282</v>
+      </c>
+      <c r="K43" s="13" t="s">
         <v>339</v>
-      </c>
-      <c r="J43" s="13" t="s">
-        <v>340</v>
-      </c>
-      <c r="K43" s="13" t="s">
-        <v>341</v>
       </c>
       <c r="L43" s="16"/>
       <c r="M43" s="17"/>
@@ -4411,39 +4454,39 @@
       <c r="P43" s="17"/>
       <c r="Q43" s="16"/>
     </row>
-    <row r="44" spans="1:17" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="14" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>343</v>
+        <v>54</v>
       </c>
       <c r="C44" s="15" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="D44" s="15" t="s">
         <v>77</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="F44" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="G44" s="13" t="s">
+        <v>341</v>
+      </c>
+      <c r="H44" s="13" t="s">
+        <v>342</v>
+      </c>
+      <c r="I44" s="13" t="s">
+        <v>343</v>
+      </c>
+      <c r="J44" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="K44" s="13" t="s">
         <v>344</v>
-      </c>
-      <c r="G44" s="13" t="s">
-        <v>345</v>
-      </c>
-      <c r="H44" s="13" t="s">
-        <v>346</v>
-      </c>
-      <c r="I44" s="13" t="s">
-        <v>347</v>
-      </c>
-      <c r="J44" s="13" t="s">
-        <v>340</v>
-      </c>
-      <c r="K44" s="13" t="s">
-        <v>348</v>
       </c>
       <c r="L44" s="16"/>
       <c r="M44" s="17"/>
@@ -4452,39 +4495,39 @@
       <c r="P44" s="17"/>
       <c r="Q44" s="16"/>
     </row>
-    <row r="45" spans="1:17" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="14" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="B45" s="13" t="s">
-        <v>343</v>
+        <v>54</v>
       </c>
       <c r="C45" s="15" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="D45" s="15" t="s">
         <v>77</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="F45" s="13" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="G45" s="13" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="H45" s="13" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="I45" s="13" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="J45" s="13" t="s">
-        <v>354</v>
+        <v>53</v>
       </c>
       <c r="K45" s="13" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="L45" s="16"/>
       <c r="M45" s="17"/>
@@ -4495,37 +4538,37 @@
     </row>
     <row r="46" spans="1:17" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="14" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="B46" s="13" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="C46" s="15" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D46" s="15" t="s">
         <v>77</v>
       </c>
       <c r="E46" s="13" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="F46" s="13" t="s">
+        <v>352</v>
+      </c>
+      <c r="G46" s="13" t="s">
+        <v>353</v>
+      </c>
+      <c r="H46" s="13" t="s">
+        <v>354</v>
+      </c>
+      <c r="I46" s="13" t="s">
+        <v>355</v>
+      </c>
+      <c r="J46" s="13" t="s">
+        <v>356</v>
+      </c>
+      <c r="K46" s="13" t="s">
         <v>357</v>
-      </c>
-      <c r="G46" s="13" t="s">
-        <v>358</v>
-      </c>
-      <c r="H46" s="13" t="s">
-        <v>359</v>
-      </c>
-      <c r="I46" s="13" t="s">
-        <v>360</v>
-      </c>
-      <c r="J46" s="13" t="s">
-        <v>361</v>
-      </c>
-      <c r="K46" s="13" t="s">
-        <v>362</v>
       </c>
       <c r="L46" s="16"/>
       <c r="M46" s="17"/>
@@ -4534,39 +4577,39 @@
       <c r="P46" s="17"/>
       <c r="Q46" s="16"/>
     </row>
-    <row r="47" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:17" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="14" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="B47" s="13" t="s">
-        <v>343</v>
+        <v>359</v>
       </c>
       <c r="C47" s="15" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D47" s="15" t="s">
         <v>77</v>
       </c>
       <c r="E47" s="13" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="F47" s="13" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="G47" s="13" t="s">
+        <v>361</v>
+      </c>
+      <c r="H47" s="13" t="s">
+        <v>362</v>
+      </c>
+      <c r="I47" s="13" t="s">
+        <v>363</v>
+      </c>
+      <c r="J47" s="13" t="s">
+        <v>356</v>
+      </c>
+      <c r="K47" s="13" t="s">
         <v>364</v>
-      </c>
-      <c r="H47" s="13" t="s">
-        <v>365</v>
-      </c>
-      <c r="I47" s="13" t="s">
-        <v>366</v>
-      </c>
-      <c r="J47" s="13" t="s">
-        <v>367</v>
-      </c>
-      <c r="K47" s="13" t="s">
-        <v>368</v>
       </c>
       <c r="L47" s="16"/>
       <c r="M47" s="17"/>
@@ -4577,10 +4620,10 @@
     </row>
     <row r="48" spans="1:17" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="14" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="B48" s="13" t="s">
-        <v>370</v>
+        <v>359</v>
       </c>
       <c r="C48" s="15" t="s">
         <v>45</v>
@@ -4589,25 +4632,25 @@
         <v>77</v>
       </c>
       <c r="E48" s="13" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="F48" s="13" t="s">
+        <v>366</v>
+      </c>
+      <c r="G48" s="13" t="s">
+        <v>367</v>
+      </c>
+      <c r="H48" s="13" t="s">
+        <v>368</v>
+      </c>
+      <c r="I48" s="13" t="s">
+        <v>369</v>
+      </c>
+      <c r="J48" s="13" t="s">
+        <v>370</v>
+      </c>
+      <c r="K48" s="13" t="s">
         <v>371</v>
-      </c>
-      <c r="G48" s="13" t="s">
-        <v>372</v>
-      </c>
-      <c r="H48" s="13" t="s">
-        <v>373</v>
-      </c>
-      <c r="I48" s="13" t="s">
-        <v>374</v>
-      </c>
-      <c r="J48" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="K48" s="13" t="s">
-        <v>375</v>
       </c>
       <c r="L48" s="16"/>
       <c r="M48" s="17"/>
@@ -4618,37 +4661,37 @@
     </row>
     <row r="49" spans="1:17" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="14" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="B49" s="13" t="s">
-        <v>377</v>
+        <v>359</v>
       </c>
       <c r="C49" s="15" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D49" s="15" t="s">
         <v>77</v>
       </c>
       <c r="E49" s="13" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="F49" s="13" t="s">
-        <v>269</v>
+        <v>373</v>
       </c>
       <c r="G49" s="13" t="s">
+        <v>374</v>
+      </c>
+      <c r="H49" s="13" t="s">
+        <v>375</v>
+      </c>
+      <c r="I49" s="13" t="s">
+        <v>376</v>
+      </c>
+      <c r="J49" s="13" t="s">
+        <v>377</v>
+      </c>
+      <c r="K49" s="13" t="s">
         <v>378</v>
-      </c>
-      <c r="H49" s="13" t="s">
-        <v>379</v>
-      </c>
-      <c r="I49" s="13" t="s">
-        <v>380</v>
-      </c>
-      <c r="J49" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="K49" s="13" t="s">
-        <v>381</v>
       </c>
       <c r="L49" s="16"/>
       <c r="M49" s="17"/>
@@ -4657,39 +4700,39 @@
       <c r="P49" s="17"/>
       <c r="Q49" s="16"/>
     </row>
-    <row r="50" spans="1:17" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="14" t="s">
+        <v>379</v>
+      </c>
+      <c r="B50" s="13" t="s">
+        <v>359</v>
+      </c>
+      <c r="C50" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="D50" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E50" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="F50" s="13" t="s">
+        <v>373</v>
+      </c>
+      <c r="G50" s="13" t="s">
+        <v>380</v>
+      </c>
+      <c r="H50" s="13" t="s">
+        <v>381</v>
+      </c>
+      <c r="I50" s="13" t="s">
         <v>382</v>
       </c>
-      <c r="B50" s="13" t="s">
+      <c r="J50" s="13" t="s">
         <v>383</v>
       </c>
-      <c r="C50" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="D50" s="15" t="s">
-        <v>383</v>
-      </c>
-      <c r="E50" s="13" t="s">
+      <c r="K50" s="13" t="s">
         <v>384</v>
-      </c>
-      <c r="F50" s="13" t="s">
-        <v>385</v>
-      </c>
-      <c r="G50" s="13" t="s">
-        <v>386</v>
-      </c>
-      <c r="H50" s="13" t="s">
-        <v>387</v>
-      </c>
-      <c r="I50" s="13" t="s">
-        <v>388</v>
-      </c>
-      <c r="J50" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="K50" s="13" t="s">
-        <v>389</v>
       </c>
       <c r="L50" s="16"/>
       <c r="M50" s="17"/>
@@ -4698,39 +4741,39 @@
       <c r="P50" s="17"/>
       <c r="Q50" s="16"/>
     </row>
-    <row r="51" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:17" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="14" t="s">
+        <v>385</v>
+      </c>
+      <c r="B51" s="13" t="s">
+        <v>386</v>
+      </c>
+      <c r="C51" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="D51" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E51" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="F51" s="13" t="s">
+        <v>387</v>
+      </c>
+      <c r="G51" s="13" t="s">
+        <v>388</v>
+      </c>
+      <c r="H51" s="13" t="s">
+        <v>389</v>
+      </c>
+      <c r="I51" s="13" t="s">
         <v>390</v>
       </c>
-      <c r="B51" s="13" t="s">
-        <v>383</v>
-      </c>
-      <c r="C51" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="D51" s="15" t="s">
-        <v>383</v>
-      </c>
-      <c r="E51" s="13" t="s">
-        <v>134</v>
-      </c>
-      <c r="F51" s="13" t="s">
-        <v>385</v>
-      </c>
-      <c r="G51" s="13" t="s">
+      <c r="J51" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="K51" s="13" t="s">
         <v>391</v>
-      </c>
-      <c r="H51" s="13" t="s">
-        <v>392</v>
-      </c>
-      <c r="I51" s="13" t="s">
-        <v>393</v>
-      </c>
-      <c r="J51" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="K51" s="13" t="s">
-        <v>394</v>
       </c>
       <c r="L51" s="16"/>
       <c r="M51" s="17"/>
@@ -4739,39 +4782,39 @@
       <c r="P51" s="17"/>
       <c r="Q51" s="16"/>
     </row>
-    <row r="52" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:17" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="14" t="s">
+        <v>392</v>
+      </c>
+      <c r="B52" s="13" t="s">
+        <v>393</v>
+      </c>
+      <c r="C52" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="D52" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E52" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="F52" s="13" t="s">
+        <v>285</v>
+      </c>
+      <c r="G52" s="13" t="s">
+        <v>394</v>
+      </c>
+      <c r="H52" s="13" t="s">
         <v>395</v>
       </c>
-      <c r="B52" s="13" t="s">
-        <v>383</v>
-      </c>
-      <c r="C52" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="D52" s="15" t="s">
-        <v>383</v>
-      </c>
-      <c r="E52" s="13" t="s">
-        <v>134</v>
-      </c>
-      <c r="F52" s="13" t="s">
-        <v>385</v>
-      </c>
-      <c r="G52" s="13" t="s">
+      <c r="I52" s="13" t="s">
         <v>396</v>
       </c>
-      <c r="H52" s="13" t="s">
+      <c r="J52" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="K52" s="13" t="s">
         <v>397</v>
-      </c>
-      <c r="I52" s="13" t="s">
-        <v>398</v>
-      </c>
-      <c r="J52" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="K52" s="13" t="s">
-        <v>399</v>
       </c>
       <c r="L52" s="16"/>
       <c r="M52" s="17"/>
@@ -4780,39 +4823,39 @@
       <c r="P52" s="17"/>
       <c r="Q52" s="16"/>
     </row>
-    <row r="53" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:17" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="14" t="s">
+        <v>398</v>
+      </c>
+      <c r="B53" s="13" t="s">
+        <v>399</v>
+      </c>
+      <c r="C53" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="D53" s="15" t="s">
+        <v>399</v>
+      </c>
+      <c r="E53" s="13" t="s">
         <v>400</v>
       </c>
-      <c r="B53" s="13" t="s">
-        <v>383</v>
-      </c>
-      <c r="C53" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="D53" s="15" t="s">
-        <v>383</v>
-      </c>
-      <c r="E53" s="13" t="s">
-        <v>134</v>
-      </c>
       <c r="F53" s="13" t="s">
-        <v>385</v>
+        <v>401</v>
       </c>
       <c r="G53" s="13" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H53" s="13" t="s">
-        <v>271</v>
+        <v>403</v>
       </c>
       <c r="I53" s="13" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="J53" s="13" t="s">
-        <v>266</v>
+        <v>83</v>
       </c>
       <c r="K53" s="13" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="L53" s="16"/>
       <c r="M53" s="17"/>
@@ -4821,39 +4864,39 @@
       <c r="P53" s="17"/>
       <c r="Q53" s="16"/>
     </row>
-    <row r="54" spans="1:17" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="14" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B54" s="13" t="s">
-        <v>383</v>
+        <v>399</v>
       </c>
       <c r="C54" s="15" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="D54" s="15" t="s">
-        <v>383</v>
+        <v>399</v>
       </c>
       <c r="E54" s="13" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="F54" s="13" t="s">
-        <v>385</v>
+        <v>401</v>
       </c>
       <c r="G54" s="13" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="H54" s="13" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="I54" s="13" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="J54" s="13" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="K54" s="13" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="L54" s="16"/>
       <c r="M54" s="17"/>
@@ -4864,37 +4907,37 @@
     </row>
     <row r="55" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="14" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B55" s="13" t="s">
-        <v>383</v>
+        <v>399</v>
       </c>
       <c r="C55" s="15" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D55" s="15" t="s">
-        <v>383</v>
+        <v>399</v>
       </c>
       <c r="E55" s="13" t="s">
-        <v>78</v>
+        <v>128</v>
       </c>
       <c r="F55" s="13" t="s">
-        <v>330</v>
+        <v>401</v>
       </c>
       <c r="G55" s="13" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="H55" s="13" t="s">
-        <v>326</v>
+        <v>413</v>
       </c>
       <c r="I55" s="13" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="J55" s="13" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="K55" s="13" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="L55" s="16"/>
       <c r="M55" s="17"/>
@@ -4903,39 +4946,39 @@
       <c r="P55" s="17"/>
       <c r="Q55" s="16"/>
     </row>
-    <row r="56" spans="1:17" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="14" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B56" s="13" t="s">
-        <v>383</v>
+        <v>399</v>
       </c>
       <c r="C56" s="15" t="s">
-        <v>76</v>
+        <v>48</v>
       </c>
       <c r="D56" s="15" t="s">
-        <v>383</v>
+        <v>399</v>
       </c>
       <c r="E56" s="13" t="s">
-        <v>414</v>
+        <v>128</v>
       </c>
       <c r="F56" s="13" t="s">
-        <v>385</v>
+        <v>401</v>
       </c>
       <c r="G56" s="13" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="H56" s="13" t="s">
-        <v>416</v>
+        <v>287</v>
       </c>
       <c r="I56" s="13" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="J56" s="13" t="s">
-        <v>113</v>
+        <v>282</v>
       </c>
       <c r="K56" s="13" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L56" s="16"/>
       <c r="M56" s="17"/>
@@ -4944,24 +4987,24 @@
       <c r="P56" s="17"/>
       <c r="Q56" s="16"/>
     </row>
-    <row r="57" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:17" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="14" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B57" s="13" t="s">
-        <v>383</v>
+        <v>399</v>
       </c>
       <c r="C57" s="15" t="s">
-        <v>76</v>
+        <v>45</v>
       </c>
       <c r="D57" s="15" t="s">
-        <v>383</v>
+        <v>399</v>
       </c>
       <c r="E57" s="13" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="F57" s="13" t="s">
-        <v>420</v>
+        <v>401</v>
       </c>
       <c r="G57" s="13" t="s">
         <v>421</v>
@@ -4973,7 +5016,7 @@
         <v>423</v>
       </c>
       <c r="J57" s="13" t="s">
-        <v>113</v>
+        <v>44</v>
       </c>
       <c r="K57" s="13" t="s">
         <v>424</v>
@@ -4985,39 +5028,39 @@
       <c r="P57" s="17"/>
       <c r="Q57" s="16"/>
     </row>
-    <row r="58" spans="1:17" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="14" t="s">
         <v>425</v>
       </c>
       <c r="B58" s="13" t="s">
-        <v>383</v>
+        <v>399</v>
       </c>
       <c r="C58" s="15" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="D58" s="15" t="s">
-        <v>383</v>
+        <v>399</v>
       </c>
       <c r="E58" s="13" t="s">
         <v>78</v>
       </c>
       <c r="F58" s="13" t="s">
-        <v>385</v>
+        <v>346</v>
       </c>
       <c r="G58" s="13" t="s">
         <v>426</v>
       </c>
       <c r="H58" s="13" t="s">
-        <v>111</v>
+        <v>342</v>
       </c>
       <c r="I58" s="13" t="s">
         <v>427</v>
       </c>
       <c r="J58" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="K58" s="13" t="s">
         <v>428</v>
-      </c>
-      <c r="K58" s="13" t="s">
-        <v>429</v>
       </c>
       <c r="L58" s="16"/>
       <c r="M58" s="17"/>
@@ -5026,39 +5069,39 @@
       <c r="P58" s="17"/>
       <c r="Q58" s="16"/>
     </row>
-    <row r="59" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:17" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="14" t="s">
+        <v>429</v>
+      </c>
+      <c r="B59" s="13" t="s">
+        <v>399</v>
+      </c>
+      <c r="C59" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="D59" s="15" t="s">
+        <v>399</v>
+      </c>
+      <c r="E59" s="13" t="s">
         <v>430</v>
       </c>
-      <c r="B59" s="13" t="s">
+      <c r="F59" s="13" t="s">
+        <v>401</v>
+      </c>
+      <c r="G59" s="13" t="s">
         <v>431</v>
       </c>
-      <c r="C59" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="D59" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="E59" s="13" t="s">
+      <c r="H59" s="13" t="s">
         <v>432</v>
       </c>
-      <c r="F59" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="G59" s="13" t="s">
+      <c r="I59" s="13" t="s">
         <v>433</v>
       </c>
-      <c r="H59" s="13" t="s">
+      <c r="J59" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="K59" s="13" t="s">
         <v>434</v>
-      </c>
-      <c r="I59" s="13" t="s">
-        <v>435</v>
-      </c>
-      <c r="J59" s="13" t="s">
-        <v>436</v>
-      </c>
-      <c r="K59" s="13" t="s">
-        <v>437</v>
       </c>
       <c r="L59" s="16"/>
       <c r="M59" s="17"/>
@@ -5069,37 +5112,37 @@
     </row>
     <row r="60" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="14" t="s">
+        <v>435</v>
+      </c>
+      <c r="B60" s="13" t="s">
+        <v>399</v>
+      </c>
+      <c r="C60" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="D60" s="15" t="s">
+        <v>399</v>
+      </c>
+      <c r="E60" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="F60" s="13" t="s">
+        <v>436</v>
+      </c>
+      <c r="G60" s="13" t="s">
+        <v>437</v>
+      </c>
+      <c r="H60" s="13" t="s">
         <v>438</v>
       </c>
-      <c r="B60" s="13" t="s">
-        <v>431</v>
-      </c>
-      <c r="C60" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="D60" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="E60" s="13" t="s">
-        <v>432</v>
-      </c>
-      <c r="F60" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="G60" s="13" t="s">
+      <c r="I60" s="13" t="s">
         <v>439</v>
-      </c>
-      <c r="H60" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="I60" s="13" t="s">
-        <v>440</v>
       </c>
       <c r="J60" s="13" t="s">
         <v>113</v>
       </c>
       <c r="K60" s="13" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="L60" s="16"/>
       <c r="M60" s="17"/>
@@ -5108,39 +5151,39 @@
       <c r="P60" s="17"/>
       <c r="Q60" s="16"/>
     </row>
-    <row r="61" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:17" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="14" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B61" s="13" t="s">
-        <v>384</v>
+        <v>399</v>
       </c>
       <c r="C61" s="15" t="s">
         <v>76</v>
       </c>
       <c r="D61" s="15" t="s">
-        <v>77</v>
+        <v>399</v>
       </c>
       <c r="E61" s="13" t="s">
-        <v>384</v>
+        <v>78</v>
       </c>
       <c r="F61" s="13" t="s">
-        <v>67</v>
+        <v>401</v>
       </c>
       <c r="G61" s="13" t="s">
+        <v>442</v>
+      </c>
+      <c r="H61" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="I61" s="13" t="s">
         <v>443</v>
       </c>
-      <c r="H61" s="13" t="s">
+      <c r="J61" s="13" t="s">
         <v>444</v>
       </c>
-      <c r="I61" s="13" t="s">
+      <c r="K61" s="13" t="s">
         <v>445</v>
-      </c>
-      <c r="J61" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="K61" s="13" t="s">
-        <v>446</v>
       </c>
       <c r="L61" s="16"/>
       <c r="M61" s="17"/>
@@ -5151,37 +5194,37 @@
     </row>
     <row r="62" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="14" t="s">
+        <v>446</v>
+      </c>
+      <c r="B62" s="13" t="s">
         <v>447</v>
       </c>
-      <c r="B62" s="13" t="s">
-        <v>384</v>
-      </c>
       <c r="C62" s="15" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="D62" s="15" t="s">
         <v>77</v>
       </c>
       <c r="E62" s="13" t="s">
-        <v>384</v>
+        <v>448</v>
       </c>
       <c r="F62" s="13" t="s">
         <v>67</v>
       </c>
       <c r="G62" s="13" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H62" s="13" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="I62" s="13" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="J62" s="13" t="s">
-        <v>113</v>
+        <v>452</v>
       </c>
       <c r="K62" s="13" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="L62" s="16"/>
       <c r="M62" s="17"/>
@@ -5192,37 +5235,37 @@
     </row>
     <row r="63" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="14" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B63" s="13" t="s">
-        <v>90</v>
+        <v>447</v>
       </c>
       <c r="C63" s="15" t="s">
-        <v>76</v>
+        <v>45</v>
       </c>
       <c r="D63" s="15" t="s">
         <v>77</v>
       </c>
       <c r="E63" s="13" t="s">
-        <v>90</v>
+        <v>448</v>
       </c>
       <c r="F63" s="13" t="s">
         <v>67</v>
       </c>
       <c r="G63" s="13" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="H63" s="13" t="s">
-        <v>454</v>
+        <v>111</v>
       </c>
       <c r="I63" s="13" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="J63" s="13" t="s">
         <v>113</v>
       </c>
       <c r="K63" s="13" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="L63" s="16"/>
       <c r="M63" s="17"/>
@@ -5233,10 +5276,10 @@
     </row>
     <row r="64" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="14" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B64" s="13" t="s">
-        <v>90</v>
+        <v>400</v>
       </c>
       <c r="C64" s="15" t="s">
         <v>76</v>
@@ -5245,25 +5288,25 @@
         <v>77</v>
       </c>
       <c r="E64" s="13" t="s">
-        <v>90</v>
+        <v>400</v>
       </c>
       <c r="F64" s="13" t="s">
         <v>67</v>
       </c>
       <c r="G64" s="13" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H64" s="13" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="I64" s="13" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="J64" s="13" t="s">
         <v>113</v>
       </c>
       <c r="K64" s="13" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="L64" s="16"/>
       <c r="M64" s="17"/>
@@ -5272,12 +5315,12 @@
       <c r="P64" s="17"/>
       <c r="Q64" s="16"/>
     </row>
-    <row r="65" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="14" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B65" s="13" t="s">
-        <v>78</v>
+        <v>400</v>
       </c>
       <c r="C65" s="15" t="s">
         <v>76</v>
@@ -5286,25 +5329,25 @@
         <v>77</v>
       </c>
       <c r="E65" s="13" t="s">
-        <v>78</v>
+        <v>400</v>
       </c>
       <c r="F65" s="13" t="s">
         <v>67</v>
       </c>
       <c r="G65" s="13" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H65" s="13" t="s">
-        <v>111</v>
+        <v>465</v>
       </c>
       <c r="I65" s="13" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="J65" s="13" t="s">
         <v>113</v>
       </c>
       <c r="K65" s="13" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="L65" s="16"/>
       <c r="M65" s="17"/>
@@ -5313,9 +5356,132 @@
       <c r="P65" s="17"/>
       <c r="Q65" s="16"/>
     </row>
+    <row r="66" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="14" t="s">
+        <v>468</v>
+      </c>
+      <c r="B66" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="C66" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="D66" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E66" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="F66" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="G66" s="13" t="s">
+        <v>469</v>
+      </c>
+      <c r="H66" s="13" t="s">
+        <v>470</v>
+      </c>
+      <c r="I66" s="13" t="s">
+        <v>471</v>
+      </c>
+      <c r="J66" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="K66" s="13" t="s">
+        <v>472</v>
+      </c>
+      <c r="L66" s="16"/>
+      <c r="M66" s="17"/>
+      <c r="N66" s="16"/>
+      <c r="O66" s="18"/>
+      <c r="P66" s="17"/>
+      <c r="Q66" s="16"/>
+    </row>
+    <row r="67" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="14" t="s">
+        <v>473</v>
+      </c>
+      <c r="B67" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="C67" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="D67" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E67" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="F67" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="G67" s="13" t="s">
+        <v>474</v>
+      </c>
+      <c r="H67" s="13" t="s">
+        <v>475</v>
+      </c>
+      <c r="I67" s="13" t="s">
+        <v>476</v>
+      </c>
+      <c r="J67" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="K67" s="13" t="s">
+        <v>477</v>
+      </c>
+      <c r="L67" s="16"/>
+      <c r="M67" s="17"/>
+      <c r="N67" s="16"/>
+      <c r="O67" s="18"/>
+      <c r="P67" s="17"/>
+      <c r="Q67" s="16"/>
+    </row>
+    <row r="68" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="14" t="s">
+        <v>478</v>
+      </c>
+      <c r="B68" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="C68" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="D68" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E68" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="F68" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="G68" s="13" t="s">
+        <v>479</v>
+      </c>
+      <c r="H68" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="I68" s="13" t="s">
+        <v>480</v>
+      </c>
+      <c r="J68" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="K68" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="L68" s="16"/>
+      <c r="M68" s="17"/>
+      <c r="N68" s="16"/>
+      <c r="O68" s="18"/>
+      <c r="P68" s="17"/>
+      <c r="Q68" s="16"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Q65" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
-  <conditionalFormatting sqref="M2:M65">
+  <autoFilter ref="A1:Q68" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <conditionalFormatting sqref="M2:M68">
     <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>"Pass"</formula>
     </cfRule>
@@ -5330,10 +5496,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" errorTitle="Status" error="Choose Pass, Fail, Blocked or Not Run." sqref="M2:M65" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" errorTitle="Status" error="Choose Pass, Fail, Blocked or Not Run." sqref="M2:M68" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Pass,Fail,Blocked,Not Run"</formula1>
     </dataValidation>
-    <dataValidation type="date" operator="greaterThan" allowBlank="1" error="Enter a date (YYYY-MM-DD)." sqref="O2:O65" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="date" operator="greaterThan" allowBlank="1" error="Enter a date (YYYY-MM-DD)." sqref="O2:O68" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>DATE(2026,1,1)</formula1>
     </dataValidation>
   </dataValidations>
@@ -5353,26 +5519,26 @@
   <sheetData>
     <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>466</v>
+        <v>482</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>467</v>
+        <v>483</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="19" t="s">
-        <v>468</v>
+        <v>484</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
-        <v>469</v>
+        <v>485</v>
       </c>
       <c r="B5" s="20">
-        <f>COUNTA('Test Cases'!$A$2:$A$65)</f>
-        <v>64</v>
+        <f>COUNTA('Test Cases'!$A$2:$A$68)</f>
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -5380,67 +5546,67 @@
         <v>30</v>
       </c>
       <c r="B6" s="20">
-        <f>COUNTIF('Test Cases'!$M$2:$M$65,"Pass")</f>
-        <v>1</v>
+        <f>COUNTIF('Test Cases'!$M$2:$M$68,"Pass")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
-        <v>470</v>
+        <v>486</v>
       </c>
       <c r="B7" s="20">
-        <f>COUNTIF('Test Cases'!$M$2:$M$65,"Fail")</f>
-        <v>1</v>
+        <f>COUNTIF('Test Cases'!$M$2:$M$68,"Fail")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>471</v>
+        <v>487</v>
       </c>
       <c r="B8" s="20">
-        <f>COUNTIF('Test Cases'!$M$2:$M$65,"Blocked")</f>
+        <f>COUNTIF('Test Cases'!$M$2:$M$68,"Blocked")</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
-        <v>472</v>
+        <v>488</v>
       </c>
       <c r="B9" s="20">
         <f>B5-B6-B7-B8</f>
-        <v>62</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
-        <v>473</v>
+        <v>489</v>
       </c>
       <c r="B10" s="20">
         <f>B6+B7</f>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
-        <v>474</v>
-      </c>
-      <c r="B11" s="21">
+        <v>490</v>
+      </c>
+      <c r="B11" s="21" t="str">
         <f>IF(B10=0,"-",B6/B10)</f>
-        <v>0.5</v>
+        <v>-</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
-        <v>475</v>
+        <v>491</v>
       </c>
       <c r="B12" s="21">
         <f>IF(B5=0,"-",(B10+B8)/B5)</f>
-        <v>3.125E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="19" t="s">
-        <v>476</v>
+        <v>492</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
@@ -5448,22 +5614,22 @@
         <v>65</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>477</v>
+        <v>493</v>
       </c>
       <c r="C16" s="11" t="s">
         <v>30</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>470</v>
+        <v>486</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>471</v>
+        <v>487</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>478</v>
+        <v>494</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>479</v>
+        <v>495</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
@@ -5471,28 +5637,28 @@
         <v>75</v>
       </c>
       <c r="B17" s="20">
-        <f>COUNTIF('Test Cases'!$B$2:$B$65,A17)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$68,A17)</f>
         <v>7</v>
       </c>
       <c r="C17" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$65,A17,'Test Cases'!$M$2:$M$65,"Pass")</f>
-        <v>1</v>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A17,'Test Cases'!$M$2:$M$68,"Pass")</f>
+        <v>0</v>
       </c>
       <c r="D17" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$65,A17,'Test Cases'!$M$2:$M$65,"Fail")</f>
-        <v>1</v>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A17,'Test Cases'!$M$2:$M$68,"Fail")</f>
+        <v>0</v>
       </c>
       <c r="E17" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$65,A17,'Test Cases'!$M$2:$M$65,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A17,'Test Cases'!$M$2:$M$68,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F17" s="20">
         <f t="shared" ref="F17:F38" si="0">B17-C17-D17-E17</f>
-        <v>5</v>
-      </c>
-      <c r="G17" s="21">
+        <v>7</v>
+      </c>
+      <c r="G17" s="21" t="str">
         <f t="shared" ref="G17:G38" si="1">IF(C17+D17=0,"-",C17/(C17+D17))</f>
-        <v>0.5</v>
+        <v>-</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
@@ -5500,24 +5666,24 @@
         <v>122</v>
       </c>
       <c r="B18" s="20">
-        <f>COUNTIF('Test Cases'!$B$2:$B$65,A18)</f>
-        <v>2</v>
+        <f>COUNTIF('Test Cases'!$B$2:$B$68,A18)</f>
+        <v>4</v>
       </c>
       <c r="C18" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$65,A18,'Test Cases'!$M$2:$M$65,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A18,'Test Cases'!$M$2:$M$68,"Pass")</f>
         <v>0</v>
       </c>
       <c r="D18" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$65,A18,'Test Cases'!$M$2:$M$65,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A18,'Test Cases'!$M$2:$M$68,"Fail")</f>
         <v>0</v>
       </c>
       <c r="E18" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$65,A18,'Test Cases'!$M$2:$M$65,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A18,'Test Cases'!$M$2:$M$68,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F18" s="20">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G18" s="21" t="str">
         <f t="shared" si="1"/>
@@ -5526,22 +5692,22 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="12" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="B19" s="20">
-        <f>COUNTIF('Test Cases'!$B$2:$B$65,A19)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$68,A19)</f>
         <v>4</v>
       </c>
       <c r="C19" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$65,A19,'Test Cases'!$M$2:$M$65,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A19,'Test Cases'!$M$2:$M$68,"Pass")</f>
         <v>0</v>
       </c>
       <c r="D19" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$65,A19,'Test Cases'!$M$2:$M$65,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A19,'Test Cases'!$M$2:$M$68,"Fail")</f>
         <v>0</v>
       </c>
       <c r="E19" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$65,A19,'Test Cases'!$M$2:$M$65,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A19,'Test Cases'!$M$2:$M$68,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F19" s="20">
@@ -5555,22 +5721,22 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="12" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="B20" s="20">
-        <f>COUNTIF('Test Cases'!$B$2:$B$65,A20)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$68,A20)</f>
         <v>1</v>
       </c>
       <c r="C20" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$65,A20,'Test Cases'!$M$2:$M$65,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A20,'Test Cases'!$M$2:$M$68,"Pass")</f>
         <v>0</v>
       </c>
       <c r="D20" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$65,A20,'Test Cases'!$M$2:$M$65,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A20,'Test Cases'!$M$2:$M$68,"Fail")</f>
         <v>0</v>
       </c>
       <c r="E20" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$65,A20,'Test Cases'!$M$2:$M$65,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A20,'Test Cases'!$M$2:$M$68,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F20" s="20">
@@ -5584,27 +5750,27 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="12" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="B21" s="20">
-        <f>COUNTIF('Test Cases'!$B$2:$B$65,A21)</f>
-        <v>3</v>
+        <f>COUNTIF('Test Cases'!$B$2:$B$68,A21)</f>
+        <v>4</v>
       </c>
       <c r="C21" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$65,A21,'Test Cases'!$M$2:$M$65,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A21,'Test Cases'!$M$2:$M$68,"Pass")</f>
         <v>0</v>
       </c>
       <c r="D21" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$65,A21,'Test Cases'!$M$2:$M$65,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A21,'Test Cases'!$M$2:$M$68,"Fail")</f>
         <v>0</v>
       </c>
       <c r="E21" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$65,A21,'Test Cases'!$M$2:$M$65,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A21,'Test Cases'!$M$2:$M$68,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F21" s="20">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G21" s="21" t="str">
         <f t="shared" si="1"/>
@@ -5613,22 +5779,22 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="12" t="s">
-        <v>183</v>
+        <v>199</v>
       </c>
       <c r="B22" s="20">
-        <f>COUNTIF('Test Cases'!$B$2:$B$65,A22)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$68,A22)</f>
         <v>1</v>
       </c>
       <c r="C22" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$65,A22,'Test Cases'!$M$2:$M$65,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A22,'Test Cases'!$M$2:$M$68,"Pass")</f>
         <v>0</v>
       </c>
       <c r="D22" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$65,A22,'Test Cases'!$M$2:$M$65,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A22,'Test Cases'!$M$2:$M$68,"Fail")</f>
         <v>0</v>
       </c>
       <c r="E22" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$65,A22,'Test Cases'!$M$2:$M$65,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A22,'Test Cases'!$M$2:$M$68,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F22" s="20">
@@ -5642,22 +5808,22 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="12" t="s">
-        <v>190</v>
+        <v>206</v>
       </c>
       <c r="B23" s="20">
-        <f>COUNTIF('Test Cases'!$B$2:$B$65,A23)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$68,A23)</f>
         <v>6</v>
       </c>
       <c r="C23" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$65,A23,'Test Cases'!$M$2:$M$65,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A23,'Test Cases'!$M$2:$M$68,"Pass")</f>
         <v>0</v>
       </c>
       <c r="D23" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$65,A23,'Test Cases'!$M$2:$M$65,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A23,'Test Cases'!$M$2:$M$68,"Fail")</f>
         <v>0</v>
       </c>
       <c r="E23" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$65,A23,'Test Cases'!$M$2:$M$65,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A23,'Test Cases'!$M$2:$M$68,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F23" s="20">
@@ -5671,22 +5837,22 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="12" t="s">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="B24" s="20">
-        <f>COUNTIF('Test Cases'!$B$2:$B$65,A24)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$68,A24)</f>
         <v>3</v>
       </c>
       <c r="C24" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$65,A24,'Test Cases'!$M$2:$M$65,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A24,'Test Cases'!$M$2:$M$68,"Pass")</f>
         <v>0</v>
       </c>
       <c r="D24" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$65,A24,'Test Cases'!$M$2:$M$65,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A24,'Test Cases'!$M$2:$M$68,"Fail")</f>
         <v>0</v>
       </c>
       <c r="E24" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$65,A24,'Test Cases'!$M$2:$M$65,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A24,'Test Cases'!$M$2:$M$68,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F24" s="20">
@@ -5700,22 +5866,22 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="12" t="s">
-        <v>249</v>
+        <v>265</v>
       </c>
       <c r="B25" s="20">
-        <f>COUNTIF('Test Cases'!$B$2:$B$65,A25)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$68,A25)</f>
         <v>4</v>
       </c>
       <c r="C25" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$65,A25,'Test Cases'!$M$2:$M$65,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A25,'Test Cases'!$M$2:$M$68,"Pass")</f>
         <v>0</v>
       </c>
       <c r="D25" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$65,A25,'Test Cases'!$M$2:$M$65,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A25,'Test Cases'!$M$2:$M$68,"Fail")</f>
         <v>0</v>
       </c>
       <c r="E25" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$65,A25,'Test Cases'!$M$2:$M$65,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A25,'Test Cases'!$M$2:$M$68,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F25" s="20">
@@ -5729,22 +5895,22 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="12" t="s">
-        <v>276</v>
+        <v>292</v>
       </c>
       <c r="B26" s="20">
-        <f>COUNTIF('Test Cases'!$B$2:$B$65,A26)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$68,A26)</f>
         <v>3</v>
       </c>
       <c r="C26" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$65,A26,'Test Cases'!$M$2:$M$65,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A26,'Test Cases'!$M$2:$M$68,"Pass")</f>
         <v>0</v>
       </c>
       <c r="D26" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$65,A26,'Test Cases'!$M$2:$M$65,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A26,'Test Cases'!$M$2:$M$68,"Fail")</f>
         <v>0</v>
       </c>
       <c r="E26" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$65,A26,'Test Cases'!$M$2:$M$65,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A26,'Test Cases'!$M$2:$M$68,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F26" s="20">
@@ -5758,22 +5924,22 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="12" t="s">
-        <v>294</v>
+        <v>310</v>
       </c>
       <c r="B27" s="20">
-        <f>COUNTIF('Test Cases'!$B$2:$B$65,A27)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$68,A27)</f>
         <v>1</v>
       </c>
       <c r="C27" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$65,A27,'Test Cases'!$M$2:$M$65,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A27,'Test Cases'!$M$2:$M$68,"Pass")</f>
         <v>0</v>
       </c>
       <c r="D27" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$65,A27,'Test Cases'!$M$2:$M$65,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A27,'Test Cases'!$M$2:$M$68,"Fail")</f>
         <v>0</v>
       </c>
       <c r="E27" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$65,A27,'Test Cases'!$M$2:$M$65,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A27,'Test Cases'!$M$2:$M$68,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F27" s="20">
@@ -5787,22 +5953,22 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="12" t="s">
-        <v>301</v>
+        <v>317</v>
       </c>
       <c r="B28" s="20">
-        <f>COUNTIF('Test Cases'!$B$2:$B$65,A28)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$68,A28)</f>
         <v>4</v>
       </c>
       <c r="C28" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$65,A28,'Test Cases'!$M$2:$M$65,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A28,'Test Cases'!$M$2:$M$68,"Pass")</f>
         <v>0</v>
       </c>
       <c r="D28" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$65,A28,'Test Cases'!$M$2:$M$65,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A28,'Test Cases'!$M$2:$M$68,"Fail")</f>
         <v>0</v>
       </c>
       <c r="E28" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$65,A28,'Test Cases'!$M$2:$M$65,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A28,'Test Cases'!$M$2:$M$68,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F28" s="20">
@@ -5819,19 +5985,19 @@
         <v>54</v>
       </c>
       <c r="B29" s="20">
-        <f>COUNTIF('Test Cases'!$B$2:$B$65,A29)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$68,A29)</f>
         <v>2</v>
       </c>
       <c r="C29" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$65,A29,'Test Cases'!$M$2:$M$65,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A29,'Test Cases'!$M$2:$M$68,"Pass")</f>
         <v>0</v>
       </c>
       <c r="D29" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$65,A29,'Test Cases'!$M$2:$M$65,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A29,'Test Cases'!$M$2:$M$68,"Fail")</f>
         <v>0</v>
       </c>
       <c r="E29" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$65,A29,'Test Cases'!$M$2:$M$65,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A29,'Test Cases'!$M$2:$M$68,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F29" s="20">
@@ -5845,22 +6011,22 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="12" t="s">
-        <v>335</v>
+        <v>351</v>
       </c>
       <c r="B30" s="20">
-        <f>COUNTIF('Test Cases'!$B$2:$B$65,A30)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$68,A30)</f>
         <v>1</v>
       </c>
       <c r="C30" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$65,A30,'Test Cases'!$M$2:$M$65,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A30,'Test Cases'!$M$2:$M$68,"Pass")</f>
         <v>0</v>
       </c>
       <c r="D30" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$65,A30,'Test Cases'!$M$2:$M$65,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A30,'Test Cases'!$M$2:$M$68,"Fail")</f>
         <v>0</v>
       </c>
       <c r="E30" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$65,A30,'Test Cases'!$M$2:$M$65,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A30,'Test Cases'!$M$2:$M$68,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F30" s="20">
@@ -5874,22 +6040,22 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="12" t="s">
-        <v>343</v>
+        <v>359</v>
       </c>
       <c r="B31" s="20">
-        <f>COUNTIF('Test Cases'!$B$2:$B$65,A31)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$68,A31)</f>
         <v>4</v>
       </c>
       <c r="C31" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$65,A31,'Test Cases'!$M$2:$M$65,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A31,'Test Cases'!$M$2:$M$68,"Pass")</f>
         <v>0</v>
       </c>
       <c r="D31" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$65,A31,'Test Cases'!$M$2:$M$65,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A31,'Test Cases'!$M$2:$M$68,"Fail")</f>
         <v>0</v>
       </c>
       <c r="E31" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$65,A31,'Test Cases'!$M$2:$M$65,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A31,'Test Cases'!$M$2:$M$68,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F31" s="20">
@@ -5903,22 +6069,22 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="12" t="s">
-        <v>370</v>
+        <v>386</v>
       </c>
       <c r="B32" s="20">
-        <f>COUNTIF('Test Cases'!$B$2:$B$65,A32)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$68,A32)</f>
         <v>1</v>
       </c>
       <c r="C32" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$65,A32,'Test Cases'!$M$2:$M$65,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A32,'Test Cases'!$M$2:$M$68,"Pass")</f>
         <v>0</v>
       </c>
       <c r="D32" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$65,A32,'Test Cases'!$M$2:$M$65,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A32,'Test Cases'!$M$2:$M$68,"Fail")</f>
         <v>0</v>
       </c>
       <c r="E32" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$65,A32,'Test Cases'!$M$2:$M$65,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A32,'Test Cases'!$M$2:$M$68,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F32" s="20">
@@ -5932,22 +6098,22 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="12" t="s">
-        <v>377</v>
+        <v>393</v>
       </c>
       <c r="B33" s="20">
-        <f>COUNTIF('Test Cases'!$B$2:$B$65,A33)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$68,A33)</f>
         <v>1</v>
       </c>
       <c r="C33" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$65,A33,'Test Cases'!$M$2:$M$65,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A33,'Test Cases'!$M$2:$M$68,"Pass")</f>
         <v>0</v>
       </c>
       <c r="D33" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$65,A33,'Test Cases'!$M$2:$M$65,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A33,'Test Cases'!$M$2:$M$68,"Fail")</f>
         <v>0</v>
       </c>
       <c r="E33" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$65,A33,'Test Cases'!$M$2:$M$65,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A33,'Test Cases'!$M$2:$M$68,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F33" s="20">
@@ -5961,22 +6127,22 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="12" t="s">
-        <v>383</v>
+        <v>399</v>
       </c>
       <c r="B34" s="20">
-        <f>COUNTIF('Test Cases'!$B$2:$B$65,A34)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$68,A34)</f>
         <v>9</v>
       </c>
       <c r="C34" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$65,A34,'Test Cases'!$M$2:$M$65,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A34,'Test Cases'!$M$2:$M$68,"Pass")</f>
         <v>0</v>
       </c>
       <c r="D34" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$65,A34,'Test Cases'!$M$2:$M$65,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A34,'Test Cases'!$M$2:$M$68,"Fail")</f>
         <v>0</v>
       </c>
       <c r="E34" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$65,A34,'Test Cases'!$M$2:$M$65,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A34,'Test Cases'!$M$2:$M$68,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F34" s="20">
@@ -5990,22 +6156,22 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="12" t="s">
-        <v>431</v>
+        <v>447</v>
       </c>
       <c r="B35" s="20">
-        <f>COUNTIF('Test Cases'!$B$2:$B$65,A35)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$68,A35)</f>
         <v>2</v>
       </c>
       <c r="C35" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$65,A35,'Test Cases'!$M$2:$M$65,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A35,'Test Cases'!$M$2:$M$68,"Pass")</f>
         <v>0</v>
       </c>
       <c r="D35" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$65,A35,'Test Cases'!$M$2:$M$65,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A35,'Test Cases'!$M$2:$M$68,"Fail")</f>
         <v>0</v>
       </c>
       <c r="E35" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$65,A35,'Test Cases'!$M$2:$M$65,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A35,'Test Cases'!$M$2:$M$68,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F35" s="20">
@@ -6019,22 +6185,22 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="12" t="s">
-        <v>384</v>
+        <v>400</v>
       </c>
       <c r="B36" s="20">
-        <f>COUNTIF('Test Cases'!$B$2:$B$65,A36)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$68,A36)</f>
         <v>2</v>
       </c>
       <c r="C36" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$65,A36,'Test Cases'!$M$2:$M$65,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A36,'Test Cases'!$M$2:$M$68,"Pass")</f>
         <v>0</v>
       </c>
       <c r="D36" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$65,A36,'Test Cases'!$M$2:$M$65,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A36,'Test Cases'!$M$2:$M$68,"Fail")</f>
         <v>0</v>
       </c>
       <c r="E36" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$65,A36,'Test Cases'!$M$2:$M$65,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A36,'Test Cases'!$M$2:$M$68,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F36" s="20">
@@ -6051,19 +6217,19 @@
         <v>90</v>
       </c>
       <c r="B37" s="20">
-        <f>COUNTIF('Test Cases'!$B$2:$B$65,A37)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$68,A37)</f>
         <v>2</v>
       </c>
       <c r="C37" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$65,A37,'Test Cases'!$M$2:$M$65,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A37,'Test Cases'!$M$2:$M$68,"Pass")</f>
         <v>0</v>
       </c>
       <c r="D37" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$65,A37,'Test Cases'!$M$2:$M$65,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A37,'Test Cases'!$M$2:$M$68,"Fail")</f>
         <v>0</v>
       </c>
       <c r="E37" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$65,A37,'Test Cases'!$M$2:$M$65,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A37,'Test Cases'!$M$2:$M$68,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F37" s="20">
@@ -6080,19 +6246,19 @@
         <v>78</v>
       </c>
       <c r="B38" s="20">
-        <f>COUNTIF('Test Cases'!$B$2:$B$65,A38)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$68,A38)</f>
         <v>1</v>
       </c>
       <c r="C38" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$65,A38,'Test Cases'!$M$2:$M$65,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A38,'Test Cases'!$M$2:$M$68,"Pass")</f>
         <v>0</v>
       </c>
       <c r="D38" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$65,A38,'Test Cases'!$M$2:$M$65,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A38,'Test Cases'!$M$2:$M$68,"Fail")</f>
         <v>0</v>
       </c>
       <c r="E38" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$65,A38,'Test Cases'!$M$2:$M$65,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A38,'Test Cases'!$M$2:$M$68,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F38" s="20">
@@ -6106,30 +6272,30 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="19" t="s">
-        <v>480</v>
+        <v>496</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="11" t="s">
-        <v>481</v>
+        <v>497</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>477</v>
+        <v>493</v>
       </c>
       <c r="C42" s="11" t="s">
         <v>30</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>470</v>
+        <v>486</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>471</v>
+        <v>487</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>478</v>
+        <v>494</v>
       </c>
       <c r="G42" s="11" t="s">
-        <v>479</v>
+        <v>495</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
@@ -6137,28 +6303,28 @@
         <v>78</v>
       </c>
       <c r="B43" s="20">
-        <f>COUNTIF('Test Cases'!$E$2:$E$65,A43)</f>
-        <v>15</v>
+        <f>COUNTIF('Test Cases'!$E$2:$E$68,A43)</f>
+        <v>16</v>
       </c>
       <c r="C43" s="20">
-        <f>COUNTIFS('Test Cases'!$E$2:$E$65,A43,'Test Cases'!$M$2:$M$65,"Pass")</f>
-        <v>1</v>
+        <f>COUNTIFS('Test Cases'!$E$2:$E$68,A43,'Test Cases'!$M$2:$M$68,"Pass")</f>
+        <v>0</v>
       </c>
       <c r="D43" s="20">
-        <f>COUNTIFS('Test Cases'!$E$2:$E$65,A43,'Test Cases'!$M$2:$M$65,"Fail")</f>
-        <v>1</v>
+        <f>COUNTIFS('Test Cases'!$E$2:$E$68,A43,'Test Cases'!$M$2:$M$68,"Fail")</f>
+        <v>0</v>
       </c>
       <c r="E43" s="20">
-        <f>COUNTIFS('Test Cases'!$E$2:$E$65,A43,'Test Cases'!$M$2:$M$65,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$E$2:$E$68,A43,'Test Cases'!$M$2:$M$68,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F43" s="20">
         <f t="shared" ref="F43:F48" si="2">B43-C43-D43-E43</f>
-        <v>13</v>
-      </c>
-      <c r="G43" s="21">
+        <v>16</v>
+      </c>
+      <c r="G43" s="21" t="str">
         <f t="shared" ref="G43:G48" si="3">IF(C43+D43=0,"-",C43/(C43+D43))</f>
-        <v>0.5</v>
+        <v>-</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
@@ -6166,19 +6332,19 @@
         <v>90</v>
       </c>
       <c r="B44" s="20">
-        <f>COUNTIF('Test Cases'!$E$2:$E$65,A44)</f>
+        <f>COUNTIF('Test Cases'!$E$2:$E$68,A44)</f>
         <v>4</v>
       </c>
       <c r="C44" s="20">
-        <f>COUNTIFS('Test Cases'!$E$2:$E$65,A44,'Test Cases'!$M$2:$M$65,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$E$2:$E$68,A44,'Test Cases'!$M$2:$M$68,"Pass")</f>
         <v>0</v>
       </c>
       <c r="D44" s="20">
-        <f>COUNTIFS('Test Cases'!$E$2:$E$65,A44,'Test Cases'!$M$2:$M$65,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$E$2:$E$68,A44,'Test Cases'!$M$2:$M$68,"Fail")</f>
         <v>0</v>
       </c>
       <c r="E44" s="20">
-        <f>COUNTIFS('Test Cases'!$E$2:$E$65,A44,'Test Cases'!$M$2:$M$65,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$E$2:$E$68,A44,'Test Cases'!$M$2:$M$68,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F44" s="20">
@@ -6192,27 +6358,27 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="12" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="B45" s="20">
-        <f>COUNTIF('Test Cases'!$E$2:$E$65,A45)</f>
-        <v>39</v>
+        <f>COUNTIF('Test Cases'!$E$2:$E$68,A45)</f>
+        <v>41</v>
       </c>
       <c r="C45" s="20">
-        <f>COUNTIFS('Test Cases'!$E$2:$E$65,A45,'Test Cases'!$M$2:$M$65,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$E$2:$E$68,A45,'Test Cases'!$M$2:$M$68,"Pass")</f>
         <v>0</v>
       </c>
       <c r="D45" s="20">
-        <f>COUNTIFS('Test Cases'!$E$2:$E$65,A45,'Test Cases'!$M$2:$M$65,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$E$2:$E$68,A45,'Test Cases'!$M$2:$M$68,"Fail")</f>
         <v>0</v>
       </c>
       <c r="E45" s="20">
-        <f>COUNTIFS('Test Cases'!$E$2:$E$65,A45,'Test Cases'!$M$2:$M$65,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$E$2:$E$68,A45,'Test Cases'!$M$2:$M$68,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F45" s="20">
         <f t="shared" si="2"/>
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G45" s="21" t="str">
         <f t="shared" si="3"/>
@@ -6221,22 +6387,22 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="12" t="s">
-        <v>384</v>
+        <v>400</v>
       </c>
       <c r="B46" s="20">
-        <f>COUNTIF('Test Cases'!$E$2:$E$65,A46)</f>
+        <f>COUNTIF('Test Cases'!$E$2:$E$68,A46)</f>
         <v>3</v>
       </c>
       <c r="C46" s="20">
-        <f>COUNTIFS('Test Cases'!$E$2:$E$65,A46,'Test Cases'!$M$2:$M$65,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$E$2:$E$68,A46,'Test Cases'!$M$2:$M$68,"Pass")</f>
         <v>0</v>
       </c>
       <c r="D46" s="20">
-        <f>COUNTIFS('Test Cases'!$E$2:$E$65,A46,'Test Cases'!$M$2:$M$65,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$E$2:$E$68,A46,'Test Cases'!$M$2:$M$68,"Fail")</f>
         <v>0</v>
       </c>
       <c r="E46" s="20">
-        <f>COUNTIFS('Test Cases'!$E$2:$E$65,A46,'Test Cases'!$M$2:$M$65,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$E$2:$E$68,A46,'Test Cases'!$M$2:$M$68,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F46" s="20">
@@ -6250,22 +6416,22 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="12" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
       <c r="B47" s="20">
-        <f>COUNTIF('Test Cases'!$E$2:$E$65,A47)</f>
+        <f>COUNTIF('Test Cases'!$E$2:$E$68,A47)</f>
         <v>1</v>
       </c>
       <c r="C47" s="20">
-        <f>COUNTIFS('Test Cases'!$E$2:$E$65,A47,'Test Cases'!$M$2:$M$65,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$E$2:$E$68,A47,'Test Cases'!$M$2:$M$68,"Pass")</f>
         <v>0</v>
       </c>
       <c r="D47" s="20">
-        <f>COUNTIFS('Test Cases'!$E$2:$E$65,A47,'Test Cases'!$M$2:$M$65,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$E$2:$E$68,A47,'Test Cases'!$M$2:$M$68,"Fail")</f>
         <v>0</v>
       </c>
       <c r="E47" s="20">
-        <f>COUNTIFS('Test Cases'!$E$2:$E$65,A47,'Test Cases'!$M$2:$M$65,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$E$2:$E$68,A47,'Test Cases'!$M$2:$M$68,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F47" s="20">
@@ -6279,22 +6445,22 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="12" t="s">
-        <v>432</v>
+        <v>448</v>
       </c>
       <c r="B48" s="20">
-        <f>COUNTIF('Test Cases'!$E$2:$E$65,A48)</f>
+        <f>COUNTIF('Test Cases'!$E$2:$E$68,A48)</f>
         <v>2</v>
       </c>
       <c r="C48" s="20">
-        <f>COUNTIFS('Test Cases'!$E$2:$E$65,A48,'Test Cases'!$M$2:$M$65,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$E$2:$E$68,A48,'Test Cases'!$M$2:$M$68,"Pass")</f>
         <v>0</v>
       </c>
       <c r="D48" s="20">
-        <f>COUNTIFS('Test Cases'!$E$2:$E$65,A48,'Test Cases'!$M$2:$M$65,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$E$2:$E$68,A48,'Test Cases'!$M$2:$M$68,"Fail")</f>
         <v>0</v>
       </c>
       <c r="E48" s="20">
-        <f>COUNTIFS('Test Cases'!$E$2:$E$65,A48,'Test Cases'!$M$2:$M$65,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$E$2:$E$68,A48,'Test Cases'!$M$2:$M$68,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F48" s="20">
@@ -6337,34 +6503,34 @@
         <v>25</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>482</v>
+        <v>498</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>483</v>
+        <v>499</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>484</v>
+        <v>500</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>485</v>
+        <v>501</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>486</v>
+        <v>502</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>487</v>
+        <v>503</v>
       </c>
       <c r="I1" s="11" t="s">
-        <v>488</v>
+        <v>504</v>
       </c>
       <c r="J1" s="11" t="s">
         <v>29</v>
       </c>
       <c r="K1" s="11" t="s">
-        <v>489</v>
+        <v>505</v>
       </c>
       <c r="L1" s="11" t="s">
-        <v>490</v>
+        <v>506</v>
       </c>
       <c r="M1" s="11" t="s">
         <v>37</v>
@@ -6372,7 +6538,7 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="14" t="s">
-        <v>491</v>
+        <v>507</v>
       </c>
       <c r="B2" s="16"/>
       <c r="C2" s="16"/>
@@ -6389,7 +6555,7 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
-        <v>492</v>
+        <v>508</v>
       </c>
       <c r="B3" s="16"/>
       <c r="C3" s="16"/>
@@ -6406,7 +6572,7 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="14" t="s">
-        <v>493</v>
+        <v>509</v>
       </c>
       <c r="B4" s="16"/>
       <c r="C4" s="16"/>
@@ -6423,7 +6589,7 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="14" t="s">
-        <v>494</v>
+        <v>510</v>
       </c>
       <c r="B5" s="16"/>
       <c r="C5" s="16"/>
@@ -6440,7 +6606,7 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="14" t="s">
-        <v>495</v>
+        <v>511</v>
       </c>
       <c r="B6" s="16"/>
       <c r="C6" s="16"/>
@@ -6457,7 +6623,7 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="14" t="s">
-        <v>496</v>
+        <v>512</v>
       </c>
       <c r="B7" s="16"/>
       <c r="C7" s="16"/>
@@ -6474,7 +6640,7 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="14" t="s">
-        <v>497</v>
+        <v>513</v>
       </c>
       <c r="B8" s="16"/>
       <c r="C8" s="16"/>
@@ -6491,7 +6657,7 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="14" t="s">
-        <v>498</v>
+        <v>514</v>
       </c>
       <c r="B9" s="16"/>
       <c r="C9" s="16"/>
@@ -6508,7 +6674,7 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="14" t="s">
-        <v>499</v>
+        <v>515</v>
       </c>
       <c r="B10" s="16"/>
       <c r="C10" s="16"/>
@@ -6525,7 +6691,7 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="14" t="s">
-        <v>500</v>
+        <v>516</v>
       </c>
       <c r="B11" s="16"/>
       <c r="C11" s="16"/>
@@ -6542,7 +6708,7 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="14" t="s">
-        <v>501</v>
+        <v>517</v>
       </c>
       <c r="B12" s="16"/>
       <c r="C12" s="16"/>
@@ -6559,7 +6725,7 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="14" t="s">
-        <v>502</v>
+        <v>518</v>
       </c>
       <c r="B13" s="16"/>
       <c r="C13" s="16"/>
@@ -6576,7 +6742,7 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="14" t="s">
-        <v>503</v>
+        <v>519</v>
       </c>
       <c r="B14" s="16"/>
       <c r="C14" s="16"/>
@@ -6593,7 +6759,7 @@
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="14" t="s">
-        <v>504</v>
+        <v>520</v>
       </c>
       <c r="B15" s="16"/>
       <c r="C15" s="16"/>
@@ -6610,7 +6776,7 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="14" t="s">
-        <v>505</v>
+        <v>521</v>
       </c>
       <c r="B16" s="16"/>
       <c r="C16" s="16"/>
@@ -6627,7 +6793,7 @@
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" s="14" t="s">
-        <v>506</v>
+        <v>522</v>
       </c>
       <c r="B17" s="16"/>
       <c r="C17" s="16"/>
@@ -6644,7 +6810,7 @@
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" s="14" t="s">
-        <v>507</v>
+        <v>523</v>
       </c>
       <c r="B18" s="16"/>
       <c r="C18" s="16"/>
@@ -6661,7 +6827,7 @@
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" s="14" t="s">
-        <v>508</v>
+        <v>524</v>
       </c>
       <c r="B19" s="16"/>
       <c r="C19" s="16"/>
@@ -6678,7 +6844,7 @@
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" s="14" t="s">
-        <v>509</v>
+        <v>525</v>
       </c>
       <c r="B20" s="16"/>
       <c r="C20" s="16"/>
@@ -6695,7 +6861,7 @@
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" s="14" t="s">
-        <v>510</v>
+        <v>526</v>
       </c>
       <c r="B21" s="16"/>
       <c r="C21" s="16"/>
@@ -6712,7 +6878,7 @@
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" s="14" t="s">
-        <v>511</v>
+        <v>527</v>
       </c>
       <c r="B22" s="16"/>
       <c r="C22" s="16"/>
@@ -6729,7 +6895,7 @@
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" s="14" t="s">
-        <v>512</v>
+        <v>528</v>
       </c>
       <c r="B23" s="16"/>
       <c r="C23" s="16"/>
@@ -6746,7 +6912,7 @@
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" s="14" t="s">
-        <v>513</v>
+        <v>529</v>
       </c>
       <c r="B24" s="16"/>
       <c r="C24" s="16"/>
@@ -6763,7 +6929,7 @@
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" s="14" t="s">
-        <v>514</v>
+        <v>530</v>
       </c>
       <c r="B25" s="16"/>
       <c r="C25" s="16"/>
@@ -6780,7 +6946,7 @@
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" s="14" t="s">
-        <v>515</v>
+        <v>531</v>
       </c>
       <c r="B26" s="16"/>
       <c r="C26" s="16"/>
@@ -6797,7 +6963,7 @@
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" s="14" t="s">
-        <v>516</v>
+        <v>532</v>
       </c>
       <c r="B27" s="16"/>
       <c r="C27" s="16"/>
@@ -6814,7 +6980,7 @@
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" s="14" t="s">
-        <v>517</v>
+        <v>533</v>
       </c>
       <c r="B28" s="16"/>
       <c r="C28" s="16"/>
@@ -6831,7 +6997,7 @@
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" s="14" t="s">
-        <v>518</v>
+        <v>534</v>
       </c>
       <c r="B29" s="16"/>
       <c r="C29" s="16"/>
@@ -6848,7 +7014,7 @@
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" s="14" t="s">
-        <v>519</v>
+        <v>535</v>
       </c>
       <c r="B30" s="16"/>
       <c r="C30" s="16"/>
@@ -6865,7 +7031,7 @@
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" s="14" t="s">
-        <v>520</v>
+        <v>536</v>
       </c>
       <c r="B31" s="16"/>
       <c r="C31" s="16"/>
@@ -6882,7 +7048,7 @@
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" s="14" t="s">
-        <v>521</v>
+        <v>537</v>
       </c>
       <c r="B32" s="16"/>
       <c r="C32" s="16"/>
@@ -6899,7 +7065,7 @@
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" s="14" t="s">
-        <v>522</v>
+        <v>538</v>
       </c>
       <c r="B33" s="16"/>
       <c r="C33" s="16"/>
@@ -6916,7 +7082,7 @@
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" s="14" t="s">
-        <v>523</v>
+        <v>539</v>
       </c>
       <c r="B34" s="16"/>
       <c r="C34" s="16"/>
@@ -6933,7 +7099,7 @@
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" s="14" t="s">
-        <v>524</v>
+        <v>540</v>
       </c>
       <c r="B35" s="16"/>
       <c r="C35" s="16"/>
@@ -6950,7 +7116,7 @@
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36" s="14" t="s">
-        <v>525</v>
+        <v>541</v>
       </c>
       <c r="B36" s="16"/>
       <c r="C36" s="16"/>
@@ -6967,7 +7133,7 @@
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" s="14" t="s">
-        <v>526</v>
+        <v>542</v>
       </c>
       <c r="B37" s="16"/>
       <c r="C37" s="16"/>
@@ -6984,7 +7150,7 @@
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" s="14" t="s">
-        <v>527</v>
+        <v>543</v>
       </c>
       <c r="B38" s="16"/>
       <c r="C38" s="16"/>
@@ -7001,7 +7167,7 @@
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39" s="14" t="s">
-        <v>528</v>
+        <v>544</v>
       </c>
       <c r="B39" s="16"/>
       <c r="C39" s="16"/>
@@ -7018,7 +7184,7 @@
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A40" s="14" t="s">
-        <v>529</v>
+        <v>545</v>
       </c>
       <c r="B40" s="16"/>
       <c r="C40" s="16"/>
@@ -7035,7 +7201,7 @@
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41" s="14" t="s">
-        <v>530</v>
+        <v>546</v>
       </c>
       <c r="B41" s="16"/>
       <c r="C41" s="16"/>
@@ -7052,7 +7218,7 @@
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A42" s="14" t="s">
-        <v>531</v>
+        <v>547</v>
       </c>
       <c r="B42" s="16"/>
       <c r="C42" s="16"/>
@@ -7069,7 +7235,7 @@
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A43" s="14" t="s">
-        <v>532</v>
+        <v>548</v>
       </c>
       <c r="B43" s="16"/>
       <c r="C43" s="16"/>
@@ -7086,7 +7252,7 @@
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A44" s="14" t="s">
-        <v>533</v>
+        <v>549</v>
       </c>
       <c r="B44" s="16"/>
       <c r="C44" s="16"/>
@@ -7103,7 +7269,7 @@
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A45" s="14" t="s">
-        <v>534</v>
+        <v>550</v>
       </c>
       <c r="B45" s="16"/>
       <c r="C45" s="16"/>
@@ -7120,7 +7286,7 @@
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A46" s="14" t="s">
-        <v>535</v>
+        <v>551</v>
       </c>
       <c r="B46" s="16"/>
       <c r="C46" s="16"/>
@@ -7137,7 +7303,7 @@
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A47" s="14" t="s">
-        <v>536</v>
+        <v>552</v>
       </c>
       <c r="B47" s="16"/>
       <c r="C47" s="16"/>
@@ -7154,7 +7320,7 @@
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A48" s="14" t="s">
-        <v>537</v>
+        <v>553</v>
       </c>
       <c r="B48" s="16"/>
       <c r="C48" s="16"/>
@@ -7171,7 +7337,7 @@
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A49" s="14" t="s">
-        <v>538</v>
+        <v>554</v>
       </c>
       <c r="B49" s="16"/>
       <c r="C49" s="16"/>
@@ -7188,7 +7354,7 @@
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A50" s="14" t="s">
-        <v>539</v>
+        <v>555</v>
       </c>
       <c r="B50" s="16"/>
       <c r="C50" s="16"/>
@@ -7205,7 +7371,7 @@
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A51" s="14" t="s">
-        <v>540</v>
+        <v>556</v>
       </c>
       <c r="B51" s="16"/>
       <c r="C51" s="16"/>
@@ -7222,7 +7388,7 @@
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A52" s="14" t="s">
-        <v>541</v>
+        <v>557</v>
       </c>
       <c r="B52" s="16"/>
       <c r="C52" s="16"/>
@@ -7239,7 +7405,7 @@
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A53" s="14" t="s">
-        <v>542</v>
+        <v>558</v>
       </c>
       <c r="B53" s="16"/>
       <c r="C53" s="16"/>
@@ -7256,7 +7422,7 @@
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A54" s="14" t="s">
-        <v>543</v>
+        <v>559</v>
       </c>
       <c r="B54" s="16"/>
       <c r="C54" s="16"/>
@@ -7273,7 +7439,7 @@
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A55" s="14" t="s">
-        <v>544</v>
+        <v>560</v>
       </c>
       <c r="B55" s="16"/>
       <c r="C55" s="16"/>
@@ -7290,7 +7456,7 @@
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A56" s="14" t="s">
-        <v>545</v>
+        <v>561</v>
       </c>
       <c r="B56" s="16"/>
       <c r="C56" s="16"/>
@@ -7307,7 +7473,7 @@
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A57" s="14" t="s">
-        <v>546</v>
+        <v>562</v>
       </c>
       <c r="B57" s="16"/>
       <c r="C57" s="16"/>
@@ -7324,7 +7490,7 @@
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A58" s="14" t="s">
-        <v>547</v>
+        <v>563</v>
       </c>
       <c r="B58" s="16"/>
       <c r="C58" s="16"/>
@@ -7341,7 +7507,7 @@
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A59" s="14" t="s">
-        <v>548</v>
+        <v>564</v>
       </c>
       <c r="B59" s="16"/>
       <c r="C59" s="16"/>
@@ -7358,7 +7524,7 @@
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A60" s="14" t="s">
-        <v>549</v>
+        <v>565</v>
       </c>
       <c r="B60" s="16"/>
       <c r="C60" s="16"/>
@@ -7375,7 +7541,7 @@
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A61" s="14" t="s">
-        <v>550</v>
+        <v>566</v>
       </c>
       <c r="B61" s="16"/>
       <c r="C61" s="16"/>
@@ -7392,15 +7558,15 @@
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A63" s="23" t="s">
-        <v>551</v>
+        <v>567</v>
       </c>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A64" s="5" t="s">
-        <v>552</v>
+        <v>568</v>
       </c>
       <c r="B64" s="26" t="s">
-        <v>553</v>
+        <v>569</v>
       </c>
       <c r="C64" s="25"/>
       <c r="D64" s="25"/>
@@ -7409,10 +7575,10 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" s="5" t="s">
-        <v>554</v>
+        <v>570</v>
       </c>
       <c r="B65" s="26" t="s">
-        <v>555</v>
+        <v>571</v>
       </c>
       <c r="C65" s="25"/>
       <c r="D65" s="25"/>
@@ -7421,10 +7587,10 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" s="5" t="s">
-        <v>556</v>
+        <v>572</v>
       </c>
       <c r="B66" s="26" t="s">
-        <v>557</v>
+        <v>573</v>
       </c>
       <c r="C66" s="25"/>
       <c r="D66" s="25"/>
@@ -7433,10 +7599,10 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" s="5" t="s">
-        <v>558</v>
+        <v>574</v>
       </c>
       <c r="B67" s="26" t="s">
-        <v>559</v>
+        <v>575</v>
       </c>
       <c r="C67" s="25"/>
       <c r="D67" s="25"/>

--- a/03-Testing/EduCheck_UAT_Test_Cases.xlsx
+++ b/03-Testing/EduCheck_UAT_Test_Cases.xlsx
@@ -3860,7 +3860,8 @@
       </c>
       <c r="I44" s="13" t="inlineStr">
         <is>
-          <t>1. Open Dashboard, Submission Review, Section Progress, Analytics, Digital Repository and SF10.</t>
+          <t>1. Open Dashboard, Submission Review, Section Progress, Analytics and Records &amp; SF10.
+2. In Records &amp; SF10, open a learner's Permanent Record (SF10).</t>
         </is>
       </c>
       <c r="J44" s="13" t="inlineStr">
@@ -3986,7 +3987,7 @@
       </c>
       <c r="I46" s="13" t="inlineStr">
         <is>
-          <t>1. Open Digital Repository.
+          <t>1. Open Records &amp; SF10.
 2. Search by LRN, then by name, then by grade level and school year.</t>
         </is>
       </c>
@@ -4050,7 +4051,7 @@
       </c>
       <c r="I47" s="13" t="inlineStr">
         <is>
-          <t>1. Open SF10 Permanent Records for the learner.
+          <t>1. Open Records &amp; SF10, search for the learner and click Permanent Record (SF10).
 2. Check the readiness report.
 3. Click Download and open the file in Excel.</t>
         </is>
@@ -4178,7 +4179,7 @@
       </c>
       <c r="I49" s="13" t="inlineStr">
         <is>
-          <t>1. Open the learner's SF10 page.
+          <t>1. Open Records &amp; SF10, search for the learner and click Permanent Record (SF10).
 2. Add a past school year with 4 quarter grades per subject and save.</t>
         </is>
       </c>
@@ -5072,7 +5073,7 @@
       </c>
       <c r="I63" s="13" t="inlineStr">
         <is>
-          <t>1. Open Dashboard, Consolidated Records, Analytics and Repository.
+          <t>1. Open Dashboard, Consolidated Records, Analytics and Records &amp; SF10.
 2. Time each page until its data appears.</t>
         </is>
       </c>

--- a/03-Testing/EduCheck_UAT_Test_Cases.xlsx
+++ b/03-Testing/EduCheck_UAT_Test_Cases.xlsx
@@ -1029,7 +1029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q68"/>
+  <dimension ref="A1:Q69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="9" customWidth="1" style="25" min="1" max="1"/>
@@ -2395,7 +2395,7 @@
       </c>
       <c r="H21" s="13" t="inlineStr">
         <is>
-          <t>A section exists.</t>
+          <t>A section whose Adviser has no subject assignment.</t>
         </is>
       </c>
       <c r="I21" s="13" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>Self-Contained: the Adviser sees the upload page. Departmentalized: the Adviser's upload menu is hidden.</t>
+          <t>Self-Contained: the Adviser can upload every subject of the section. Departmentalized: the Adviser can upload only subjects assigned to them; with none, the upload menu is hidden. Switch the section back afterwards.</t>
         </is>
       </c>
       <c r="L21" s="16" t="n"/>
@@ -3025,28 +3025,29 @@
       </c>
       <c r="G31" s="13" t="inlineStr">
         <is>
-          <t>Self-Contained Adviser can upload</t>
+          <t>Adviser uploads their own assigned subject</t>
         </is>
       </c>
       <c r="H31" s="13" t="inlineStr">
         <is>
-          <t>Adviser of a Self-Contained section.</t>
+          <t>Rizal is Departmentalized and the Adviser is assigned at least one of its subjects.</t>
         </is>
       </c>
       <c r="I31" s="13" t="inlineStr">
         <is>
           <t>1. Open Upload Files.
-2. Upload a record for a subject in the advisory section.</t>
+2. Check which subjects are offered for Rizal.
+3. Upload the file for one of the Adviser's own subjects.</t>
         </is>
       </c>
       <c r="J31" s="13" t="inlineStr">
         <is>
-          <t>adviser.grade6a, Rizal, UAT-files/TC-022_valid-ecr-rizal.xlsx</t>
+          <t>adviser.grade6a, Rizal, the matching file from UAT-files/per-subject/</t>
         </is>
       </c>
       <c r="K31" s="13" t="inlineStr">
         <is>
-          <t>Upload succeeds as for a Subject Teacher.</t>
+          <t>Only the Adviser's own subjects are offered. The upload succeeds as for a Subject Teacher.</t>
         </is>
       </c>
       <c r="L31" s="16" t="n"/>
@@ -5409,6 +5410,71 @@
       <c r="O68" s="18" t="n"/>
       <c r="P68" s="17" t="n"/>
       <c r="Q68" s="16" t="n"/>
+    </row>
+    <row r="69" ht="30" customHeight="1" s="25">
+      <c r="A69" s="14" t="inlineStr">
+        <is>
+          <t>TC-068</t>
+        </is>
+      </c>
+      <c r="B69" s="13" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
+      <c r="C69" s="15" t="inlineStr">
+        <is>
+          <t>Subject Teacher</t>
+        </is>
+      </c>
+      <c r="D69" s="15" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="E69" s="13" t="inlineStr">
+        <is>
+          <t>Functional suitability</t>
+        </is>
+      </c>
+      <c r="F69" s="13" t="inlineStr">
+        <is>
+          <t>EPIC-02, D-08</t>
+        </is>
+      </c>
+      <c r="G69" s="13" t="inlineStr">
+        <is>
+          <t>A file for another subject is refused</t>
+        </is>
+      </c>
+      <c r="H69" s="13" t="inlineStr">
+        <is>
+          <t>Teacher is assigned to Mathematics for Rizal. No Rizal learner is Approved.</t>
+        </is>
+      </c>
+      <c r="I69" s="13" t="inlineStr">
+        <is>
+          <t>1. Open Upload e-Class Record.
+2. Select Mathematics and Rizal.
+3. Upload the English file.</t>
+        </is>
+      </c>
+      <c r="J69" s="13" t="inlineStr">
+        <is>
+          <t>UAT-files/per-subject/ecr-rizal-English.xlsx</t>
+        </is>
+      </c>
+      <c r="K69" s="13" t="inlineStr">
+        <is>
+          <t>The upload is refused: the file is the e-Class Record for English but Mathematics was selected. Nothing is saved.</t>
+        </is>
+      </c>
+      <c r="L69" s="16" t="n"/>
+      <c r="M69" s="17" t="n"/>
+      <c r="N69" s="16" t="n"/>
+      <c r="O69" s="18" t="n"/>
+      <c r="P69" s="17" t="n"/>
+      <c r="Q69" s="16" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:Q68"/>
@@ -5427,10 +5493,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="M2:M68" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Status" error="Choose Pass, Fail, Blocked or Not Run." type="list">
+    <dataValidation sqref="M2:M69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Status" error="Choose Pass, Fail, Blocked or Not Run." type="list">
       <formula1>"Pass,Fail,Blocked,Not Run"</formula1>
     </dataValidation>
-    <dataValidation sqref="O2:O68" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Enter a date (YYYY-MM-DD)." type="date" operator="greaterThan">
+    <dataValidation sqref="O2:O69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Enter a date (YYYY-MM-DD)." type="date" operator="greaterThan">
       <formula1>DATE(2026,1,1)</formula1>
     </dataValidation>
   </dataValidations>
@@ -5466,6 +5532,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="19" t="inlineStr">
         <is>
@@ -5480,7 +5547,7 @@
         </is>
       </c>
       <c r="B5" s="20">
-        <f>COUNTA('Test Cases'!$A$2:$A$68)</f>
+        <f>COUNTA('Test Cases'!$A$2:$A$69)</f>
         <v/>
       </c>
     </row>
@@ -5491,7 +5558,7 @@
         </is>
       </c>
       <c r="B6" s="20">
-        <f>COUNTIF('Test Cases'!$M$2:$M$68,"Pass")</f>
+        <f>COUNTIF('Test Cases'!$M$2:$M$69,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -5502,7 +5569,7 @@
         </is>
       </c>
       <c r="B7" s="20">
-        <f>COUNTIF('Test Cases'!$M$2:$M$68,"Fail")</f>
+        <f>COUNTIF('Test Cases'!$M$2:$M$69,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -5513,7 +5580,7 @@
         </is>
       </c>
       <c r="B8" s="20">
-        <f>COUNTIF('Test Cases'!$M$2:$M$68,"Blocked")</f>
+        <f>COUNTIF('Test Cases'!$M$2:$M$69,"Blocked")</f>
         <v/>
       </c>
     </row>
@@ -5561,6 +5628,8 @@
         <v/>
       </c>
     </row>
+    <row r="13"/>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="19" t="inlineStr">
         <is>
@@ -5612,19 +5681,19 @@
         </is>
       </c>
       <c r="B17" s="20">
-        <f>COUNTIF('Test Cases'!$B$2:$B$68,A17)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$69,A17)</f>
         <v/>
       </c>
       <c r="C17" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A17,'Test Cases'!$M$2:$M$68,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A17,'Test Cases'!$M$2:$M$69,"Pass")</f>
         <v/>
       </c>
       <c r="D17" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A17,'Test Cases'!$M$2:$M$68,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A17,'Test Cases'!$M$2:$M$69,"Fail")</f>
         <v/>
       </c>
       <c r="E17" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A17,'Test Cases'!$M$2:$M$68,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A17,'Test Cases'!$M$2:$M$69,"Blocked")</f>
         <v/>
       </c>
       <c r="F17" s="20">
@@ -5643,19 +5712,19 @@
         </is>
       </c>
       <c r="B18" s="20">
-        <f>COUNTIF('Test Cases'!$B$2:$B$68,A18)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$69,A18)</f>
         <v/>
       </c>
       <c r="C18" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A18,'Test Cases'!$M$2:$M$68,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A18,'Test Cases'!$M$2:$M$69,"Pass")</f>
         <v/>
       </c>
       <c r="D18" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A18,'Test Cases'!$M$2:$M$68,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A18,'Test Cases'!$M$2:$M$69,"Fail")</f>
         <v/>
       </c>
       <c r="E18" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A18,'Test Cases'!$M$2:$M$68,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A18,'Test Cases'!$M$2:$M$69,"Blocked")</f>
         <v/>
       </c>
       <c r="F18" s="20">
@@ -5674,19 +5743,19 @@
         </is>
       </c>
       <c r="B19" s="20">
-        <f>COUNTIF('Test Cases'!$B$2:$B$68,A19)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$69,A19)</f>
         <v/>
       </c>
       <c r="C19" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A19,'Test Cases'!$M$2:$M$68,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A19,'Test Cases'!$M$2:$M$69,"Pass")</f>
         <v/>
       </c>
       <c r="D19" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A19,'Test Cases'!$M$2:$M$68,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A19,'Test Cases'!$M$2:$M$69,"Fail")</f>
         <v/>
       </c>
       <c r="E19" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A19,'Test Cases'!$M$2:$M$68,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A19,'Test Cases'!$M$2:$M$69,"Blocked")</f>
         <v/>
       </c>
       <c r="F19" s="20">
@@ -5705,19 +5774,19 @@
         </is>
       </c>
       <c r="B20" s="20">
-        <f>COUNTIF('Test Cases'!$B$2:$B$68,A20)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$69,A20)</f>
         <v/>
       </c>
       <c r="C20" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A20,'Test Cases'!$M$2:$M$68,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A20,'Test Cases'!$M$2:$M$69,"Pass")</f>
         <v/>
       </c>
       <c r="D20" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A20,'Test Cases'!$M$2:$M$68,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A20,'Test Cases'!$M$2:$M$69,"Fail")</f>
         <v/>
       </c>
       <c r="E20" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A20,'Test Cases'!$M$2:$M$68,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A20,'Test Cases'!$M$2:$M$69,"Blocked")</f>
         <v/>
       </c>
       <c r="F20" s="20">
@@ -5736,19 +5805,19 @@
         </is>
       </c>
       <c r="B21" s="20">
-        <f>COUNTIF('Test Cases'!$B$2:$B$68,A21)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$69,A21)</f>
         <v/>
       </c>
       <c r="C21" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A21,'Test Cases'!$M$2:$M$68,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A21,'Test Cases'!$M$2:$M$69,"Pass")</f>
         <v/>
       </c>
       <c r="D21" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A21,'Test Cases'!$M$2:$M$68,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A21,'Test Cases'!$M$2:$M$69,"Fail")</f>
         <v/>
       </c>
       <c r="E21" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A21,'Test Cases'!$M$2:$M$68,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A21,'Test Cases'!$M$2:$M$69,"Blocked")</f>
         <v/>
       </c>
       <c r="F21" s="20">
@@ -5767,19 +5836,19 @@
         </is>
       </c>
       <c r="B22" s="20">
-        <f>COUNTIF('Test Cases'!$B$2:$B$68,A22)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$69,A22)</f>
         <v/>
       </c>
       <c r="C22" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A22,'Test Cases'!$M$2:$M$68,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A22,'Test Cases'!$M$2:$M$69,"Pass")</f>
         <v/>
       </c>
       <c r="D22" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A22,'Test Cases'!$M$2:$M$68,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A22,'Test Cases'!$M$2:$M$69,"Fail")</f>
         <v/>
       </c>
       <c r="E22" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A22,'Test Cases'!$M$2:$M$68,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A22,'Test Cases'!$M$2:$M$69,"Blocked")</f>
         <v/>
       </c>
       <c r="F22" s="20">
@@ -5798,19 +5867,19 @@
         </is>
       </c>
       <c r="B23" s="20">
-        <f>COUNTIF('Test Cases'!$B$2:$B$68,A23)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$69,A23)</f>
         <v/>
       </c>
       <c r="C23" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A23,'Test Cases'!$M$2:$M$68,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A23,'Test Cases'!$M$2:$M$69,"Pass")</f>
         <v/>
       </c>
       <c r="D23" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A23,'Test Cases'!$M$2:$M$68,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A23,'Test Cases'!$M$2:$M$69,"Fail")</f>
         <v/>
       </c>
       <c r="E23" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A23,'Test Cases'!$M$2:$M$68,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A23,'Test Cases'!$M$2:$M$69,"Blocked")</f>
         <v/>
       </c>
       <c r="F23" s="20">
@@ -5829,19 +5898,19 @@
         </is>
       </c>
       <c r="B24" s="20">
-        <f>COUNTIF('Test Cases'!$B$2:$B$68,A24)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$69,A24)</f>
         <v/>
       </c>
       <c r="C24" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A24,'Test Cases'!$M$2:$M$68,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A24,'Test Cases'!$M$2:$M$69,"Pass")</f>
         <v/>
       </c>
       <c r="D24" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A24,'Test Cases'!$M$2:$M$68,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A24,'Test Cases'!$M$2:$M$69,"Fail")</f>
         <v/>
       </c>
       <c r="E24" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A24,'Test Cases'!$M$2:$M$68,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A24,'Test Cases'!$M$2:$M$69,"Blocked")</f>
         <v/>
       </c>
       <c r="F24" s="20">
@@ -5860,19 +5929,19 @@
         </is>
       </c>
       <c r="B25" s="20">
-        <f>COUNTIF('Test Cases'!$B$2:$B$68,A25)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$69,A25)</f>
         <v/>
       </c>
       <c r="C25" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A25,'Test Cases'!$M$2:$M$68,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A25,'Test Cases'!$M$2:$M$69,"Pass")</f>
         <v/>
       </c>
       <c r="D25" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A25,'Test Cases'!$M$2:$M$68,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A25,'Test Cases'!$M$2:$M$69,"Fail")</f>
         <v/>
       </c>
       <c r="E25" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A25,'Test Cases'!$M$2:$M$68,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A25,'Test Cases'!$M$2:$M$69,"Blocked")</f>
         <v/>
       </c>
       <c r="F25" s="20">
@@ -5891,19 +5960,19 @@
         </is>
       </c>
       <c r="B26" s="20">
-        <f>COUNTIF('Test Cases'!$B$2:$B$68,A26)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$69,A26)</f>
         <v/>
       </c>
       <c r="C26" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A26,'Test Cases'!$M$2:$M$68,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A26,'Test Cases'!$M$2:$M$69,"Pass")</f>
         <v/>
       </c>
       <c r="D26" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A26,'Test Cases'!$M$2:$M$68,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A26,'Test Cases'!$M$2:$M$69,"Fail")</f>
         <v/>
       </c>
       <c r="E26" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A26,'Test Cases'!$M$2:$M$68,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A26,'Test Cases'!$M$2:$M$69,"Blocked")</f>
         <v/>
       </c>
       <c r="F26" s="20">
@@ -5922,19 +5991,19 @@
         </is>
       </c>
       <c r="B27" s="20">
-        <f>COUNTIF('Test Cases'!$B$2:$B$68,A27)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$69,A27)</f>
         <v/>
       </c>
       <c r="C27" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A27,'Test Cases'!$M$2:$M$68,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A27,'Test Cases'!$M$2:$M$69,"Pass")</f>
         <v/>
       </c>
       <c r="D27" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A27,'Test Cases'!$M$2:$M$68,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A27,'Test Cases'!$M$2:$M$69,"Fail")</f>
         <v/>
       </c>
       <c r="E27" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A27,'Test Cases'!$M$2:$M$68,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A27,'Test Cases'!$M$2:$M$69,"Blocked")</f>
         <v/>
       </c>
       <c r="F27" s="20">
@@ -5953,19 +6022,19 @@
         </is>
       </c>
       <c r="B28" s="20">
-        <f>COUNTIF('Test Cases'!$B$2:$B$68,A28)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$69,A28)</f>
         <v/>
       </c>
       <c r="C28" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A28,'Test Cases'!$M$2:$M$68,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A28,'Test Cases'!$M$2:$M$69,"Pass")</f>
         <v/>
       </c>
       <c r="D28" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A28,'Test Cases'!$M$2:$M$68,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A28,'Test Cases'!$M$2:$M$69,"Fail")</f>
         <v/>
       </c>
       <c r="E28" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A28,'Test Cases'!$M$2:$M$68,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A28,'Test Cases'!$M$2:$M$69,"Blocked")</f>
         <v/>
       </c>
       <c r="F28" s="20">
@@ -5984,19 +6053,19 @@
         </is>
       </c>
       <c r="B29" s="20">
-        <f>COUNTIF('Test Cases'!$B$2:$B$68,A29)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$69,A29)</f>
         <v/>
       </c>
       <c r="C29" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A29,'Test Cases'!$M$2:$M$68,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A29,'Test Cases'!$M$2:$M$69,"Pass")</f>
         <v/>
       </c>
       <c r="D29" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A29,'Test Cases'!$M$2:$M$68,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A29,'Test Cases'!$M$2:$M$69,"Fail")</f>
         <v/>
       </c>
       <c r="E29" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A29,'Test Cases'!$M$2:$M$68,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A29,'Test Cases'!$M$2:$M$69,"Blocked")</f>
         <v/>
       </c>
       <c r="F29" s="20">
@@ -6015,19 +6084,19 @@
         </is>
       </c>
       <c r="B30" s="20">
-        <f>COUNTIF('Test Cases'!$B$2:$B$68,A30)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$69,A30)</f>
         <v/>
       </c>
       <c r="C30" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A30,'Test Cases'!$M$2:$M$68,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A30,'Test Cases'!$M$2:$M$69,"Pass")</f>
         <v/>
       </c>
       <c r="D30" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A30,'Test Cases'!$M$2:$M$68,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A30,'Test Cases'!$M$2:$M$69,"Fail")</f>
         <v/>
       </c>
       <c r="E30" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A30,'Test Cases'!$M$2:$M$68,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A30,'Test Cases'!$M$2:$M$69,"Blocked")</f>
         <v/>
       </c>
       <c r="F30" s="20">
@@ -6046,19 +6115,19 @@
         </is>
       </c>
       <c r="B31" s="20">
-        <f>COUNTIF('Test Cases'!$B$2:$B$68,A31)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$69,A31)</f>
         <v/>
       </c>
       <c r="C31" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A31,'Test Cases'!$M$2:$M$68,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A31,'Test Cases'!$M$2:$M$69,"Pass")</f>
         <v/>
       </c>
       <c r="D31" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A31,'Test Cases'!$M$2:$M$68,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A31,'Test Cases'!$M$2:$M$69,"Fail")</f>
         <v/>
       </c>
       <c r="E31" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A31,'Test Cases'!$M$2:$M$68,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A31,'Test Cases'!$M$2:$M$69,"Blocked")</f>
         <v/>
       </c>
       <c r="F31" s="20">
@@ -6077,19 +6146,19 @@
         </is>
       </c>
       <c r="B32" s="20">
-        <f>COUNTIF('Test Cases'!$B$2:$B$68,A32)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$69,A32)</f>
         <v/>
       </c>
       <c r="C32" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A32,'Test Cases'!$M$2:$M$68,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A32,'Test Cases'!$M$2:$M$69,"Pass")</f>
         <v/>
       </c>
       <c r="D32" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A32,'Test Cases'!$M$2:$M$68,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A32,'Test Cases'!$M$2:$M$69,"Fail")</f>
         <v/>
       </c>
       <c r="E32" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A32,'Test Cases'!$M$2:$M$68,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A32,'Test Cases'!$M$2:$M$69,"Blocked")</f>
         <v/>
       </c>
       <c r="F32" s="20">
@@ -6108,19 +6177,19 @@
         </is>
       </c>
       <c r="B33" s="20">
-        <f>COUNTIF('Test Cases'!$B$2:$B$68,A33)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$69,A33)</f>
         <v/>
       </c>
       <c r="C33" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A33,'Test Cases'!$M$2:$M$68,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A33,'Test Cases'!$M$2:$M$69,"Pass")</f>
         <v/>
       </c>
       <c r="D33" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A33,'Test Cases'!$M$2:$M$68,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A33,'Test Cases'!$M$2:$M$69,"Fail")</f>
         <v/>
       </c>
       <c r="E33" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A33,'Test Cases'!$M$2:$M$68,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A33,'Test Cases'!$M$2:$M$69,"Blocked")</f>
         <v/>
       </c>
       <c r="F33" s="20">
@@ -6139,19 +6208,19 @@
         </is>
       </c>
       <c r="B34" s="20">
-        <f>COUNTIF('Test Cases'!$B$2:$B$68,A34)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$69,A34)</f>
         <v/>
       </c>
       <c r="C34" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A34,'Test Cases'!$M$2:$M$68,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A34,'Test Cases'!$M$2:$M$69,"Pass")</f>
         <v/>
       </c>
       <c r="D34" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A34,'Test Cases'!$M$2:$M$68,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A34,'Test Cases'!$M$2:$M$69,"Fail")</f>
         <v/>
       </c>
       <c r="E34" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A34,'Test Cases'!$M$2:$M$68,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A34,'Test Cases'!$M$2:$M$69,"Blocked")</f>
         <v/>
       </c>
       <c r="F34" s="20">
@@ -6170,19 +6239,19 @@
         </is>
       </c>
       <c r="B35" s="20">
-        <f>COUNTIF('Test Cases'!$B$2:$B$68,A35)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$69,A35)</f>
         <v/>
       </c>
       <c r="C35" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A35,'Test Cases'!$M$2:$M$68,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A35,'Test Cases'!$M$2:$M$69,"Pass")</f>
         <v/>
       </c>
       <c r="D35" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A35,'Test Cases'!$M$2:$M$68,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A35,'Test Cases'!$M$2:$M$69,"Fail")</f>
         <v/>
       </c>
       <c r="E35" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A35,'Test Cases'!$M$2:$M$68,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A35,'Test Cases'!$M$2:$M$69,"Blocked")</f>
         <v/>
       </c>
       <c r="F35" s="20">
@@ -6201,19 +6270,19 @@
         </is>
       </c>
       <c r="B36" s="20">
-        <f>COUNTIF('Test Cases'!$B$2:$B$68,A36)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$69,A36)</f>
         <v/>
       </c>
       <c r="C36" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A36,'Test Cases'!$M$2:$M$68,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A36,'Test Cases'!$M$2:$M$69,"Pass")</f>
         <v/>
       </c>
       <c r="D36" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A36,'Test Cases'!$M$2:$M$68,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A36,'Test Cases'!$M$2:$M$69,"Fail")</f>
         <v/>
       </c>
       <c r="E36" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A36,'Test Cases'!$M$2:$M$68,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A36,'Test Cases'!$M$2:$M$69,"Blocked")</f>
         <v/>
       </c>
       <c r="F36" s="20">
@@ -6232,19 +6301,19 @@
         </is>
       </c>
       <c r="B37" s="20">
-        <f>COUNTIF('Test Cases'!$B$2:$B$68,A37)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$69,A37)</f>
         <v/>
       </c>
       <c r="C37" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A37,'Test Cases'!$M$2:$M$68,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A37,'Test Cases'!$M$2:$M$69,"Pass")</f>
         <v/>
       </c>
       <c r="D37" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A37,'Test Cases'!$M$2:$M$68,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A37,'Test Cases'!$M$2:$M$69,"Fail")</f>
         <v/>
       </c>
       <c r="E37" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A37,'Test Cases'!$M$2:$M$68,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A37,'Test Cases'!$M$2:$M$69,"Blocked")</f>
         <v/>
       </c>
       <c r="F37" s="20">
@@ -6263,19 +6332,19 @@
         </is>
       </c>
       <c r="B38" s="20">
-        <f>COUNTIF('Test Cases'!$B$2:$B$68,A38)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$69,A38)</f>
         <v/>
       </c>
       <c r="C38" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A38,'Test Cases'!$M$2:$M$68,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A38,'Test Cases'!$M$2:$M$69,"Pass")</f>
         <v/>
       </c>
       <c r="D38" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A38,'Test Cases'!$M$2:$M$68,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A38,'Test Cases'!$M$2:$M$69,"Fail")</f>
         <v/>
       </c>
       <c r="E38" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$68,A38,'Test Cases'!$M$2:$M$68,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A38,'Test Cases'!$M$2:$M$69,"Blocked")</f>
         <v/>
       </c>
       <c r="F38" s="20">
@@ -6287,6 +6356,8 @@
         <v/>
       </c>
     </row>
+    <row r="39"/>
+    <row r="40"/>
     <row r="41">
       <c r="A41" s="19" t="inlineStr">
         <is>
@@ -6338,19 +6409,19 @@
         </is>
       </c>
       <c r="B43" s="20">
-        <f>COUNTIF('Test Cases'!$E$2:$E$68,A43)</f>
+        <f>COUNTIF('Test Cases'!$E$2:$E$69,A43)</f>
         <v/>
       </c>
       <c r="C43" s="20">
-        <f>COUNTIFS('Test Cases'!$E$2:$E$68,A43,'Test Cases'!$M$2:$M$68,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$E$2:$E$69,A43,'Test Cases'!$M$2:$M$69,"Pass")</f>
         <v/>
       </c>
       <c r="D43" s="20">
-        <f>COUNTIFS('Test Cases'!$E$2:$E$68,A43,'Test Cases'!$M$2:$M$68,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$E$2:$E$69,A43,'Test Cases'!$M$2:$M$69,"Fail")</f>
         <v/>
       </c>
       <c r="E43" s="20">
-        <f>COUNTIFS('Test Cases'!$E$2:$E$68,A43,'Test Cases'!$M$2:$M$68,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$E$2:$E$69,A43,'Test Cases'!$M$2:$M$69,"Blocked")</f>
         <v/>
       </c>
       <c r="F43" s="20">
@@ -6369,19 +6440,19 @@
         </is>
       </c>
       <c r="B44" s="20">
-        <f>COUNTIF('Test Cases'!$E$2:$E$68,A44)</f>
+        <f>COUNTIF('Test Cases'!$E$2:$E$69,A44)</f>
         <v/>
       </c>
       <c r="C44" s="20">
-        <f>COUNTIFS('Test Cases'!$E$2:$E$68,A44,'Test Cases'!$M$2:$M$68,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$E$2:$E$69,A44,'Test Cases'!$M$2:$M$69,"Pass")</f>
         <v/>
       </c>
       <c r="D44" s="20">
-        <f>COUNTIFS('Test Cases'!$E$2:$E$68,A44,'Test Cases'!$M$2:$M$68,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$E$2:$E$69,A44,'Test Cases'!$M$2:$M$69,"Fail")</f>
         <v/>
       </c>
       <c r="E44" s="20">
-        <f>COUNTIFS('Test Cases'!$E$2:$E$68,A44,'Test Cases'!$M$2:$M$68,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$E$2:$E$69,A44,'Test Cases'!$M$2:$M$69,"Blocked")</f>
         <v/>
       </c>
       <c r="F44" s="20">
@@ -6400,19 +6471,19 @@
         </is>
       </c>
       <c r="B45" s="20">
-        <f>COUNTIF('Test Cases'!$E$2:$E$68,A45)</f>
+        <f>COUNTIF('Test Cases'!$E$2:$E$69,A45)</f>
         <v/>
       </c>
       <c r="C45" s="20">
-        <f>COUNTIFS('Test Cases'!$E$2:$E$68,A45,'Test Cases'!$M$2:$M$68,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$E$2:$E$69,A45,'Test Cases'!$M$2:$M$69,"Pass")</f>
         <v/>
       </c>
       <c r="D45" s="20">
-        <f>COUNTIFS('Test Cases'!$E$2:$E$68,A45,'Test Cases'!$M$2:$M$68,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$E$2:$E$69,A45,'Test Cases'!$M$2:$M$69,"Fail")</f>
         <v/>
       </c>
       <c r="E45" s="20">
-        <f>COUNTIFS('Test Cases'!$E$2:$E$68,A45,'Test Cases'!$M$2:$M$68,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$E$2:$E$69,A45,'Test Cases'!$M$2:$M$69,"Blocked")</f>
         <v/>
       </c>
       <c r="F45" s="20">
@@ -6431,19 +6502,19 @@
         </is>
       </c>
       <c r="B46" s="20">
-        <f>COUNTIF('Test Cases'!$E$2:$E$68,A46)</f>
+        <f>COUNTIF('Test Cases'!$E$2:$E$69,A46)</f>
         <v/>
       </c>
       <c r="C46" s="20">
-        <f>COUNTIFS('Test Cases'!$E$2:$E$68,A46,'Test Cases'!$M$2:$M$68,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$E$2:$E$69,A46,'Test Cases'!$M$2:$M$69,"Pass")</f>
         <v/>
       </c>
       <c r="D46" s="20">
-        <f>COUNTIFS('Test Cases'!$E$2:$E$68,A46,'Test Cases'!$M$2:$M$68,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$E$2:$E$69,A46,'Test Cases'!$M$2:$M$69,"Fail")</f>
         <v/>
       </c>
       <c r="E46" s="20">
-        <f>COUNTIFS('Test Cases'!$E$2:$E$68,A46,'Test Cases'!$M$2:$M$68,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$E$2:$E$69,A46,'Test Cases'!$M$2:$M$69,"Blocked")</f>
         <v/>
       </c>
       <c r="F46" s="20">
@@ -6462,19 +6533,19 @@
         </is>
       </c>
       <c r="B47" s="20">
-        <f>COUNTIF('Test Cases'!$E$2:$E$68,A47)</f>
+        <f>COUNTIF('Test Cases'!$E$2:$E$69,A47)</f>
         <v/>
       </c>
       <c r="C47" s="20">
-        <f>COUNTIFS('Test Cases'!$E$2:$E$68,A47,'Test Cases'!$M$2:$M$68,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$E$2:$E$69,A47,'Test Cases'!$M$2:$M$69,"Pass")</f>
         <v/>
       </c>
       <c r="D47" s="20">
-        <f>COUNTIFS('Test Cases'!$E$2:$E$68,A47,'Test Cases'!$M$2:$M$68,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$E$2:$E$69,A47,'Test Cases'!$M$2:$M$69,"Fail")</f>
         <v/>
       </c>
       <c r="E47" s="20">
-        <f>COUNTIFS('Test Cases'!$E$2:$E$68,A47,'Test Cases'!$M$2:$M$68,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$E$2:$E$69,A47,'Test Cases'!$M$2:$M$69,"Blocked")</f>
         <v/>
       </c>
       <c r="F47" s="20">
@@ -6493,19 +6564,19 @@
         </is>
       </c>
       <c r="B48" s="20">
-        <f>COUNTIF('Test Cases'!$E$2:$E$68,A48)</f>
+        <f>COUNTIF('Test Cases'!$E$2:$E$69,A48)</f>
         <v/>
       </c>
       <c r="C48" s="20">
-        <f>COUNTIFS('Test Cases'!$E$2:$E$68,A48,'Test Cases'!$M$2:$M$68,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$E$2:$E$69,A48,'Test Cases'!$M$2:$M$69,"Pass")</f>
         <v/>
       </c>
       <c r="D48" s="20">
-        <f>COUNTIFS('Test Cases'!$E$2:$E$68,A48,'Test Cases'!$M$2:$M$68,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$E$2:$E$69,A48,'Test Cases'!$M$2:$M$69,"Fail")</f>
         <v/>
       </c>
       <c r="E48" s="20">
-        <f>COUNTIFS('Test Cases'!$E$2:$E$68,A48,'Test Cases'!$M$2:$M$68,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$E$2:$E$69,A48,'Test Cases'!$M$2:$M$69,"Blocked")</f>
         <v/>
       </c>
       <c r="F48" s="20">

--- a/03-Testing/EduCheck_UAT_Test_Cases.xlsx
+++ b/03-Testing/EduCheck_UAT_Test_Cases.xlsx
@@ -2199,28 +2199,29 @@
       </c>
       <c r="G18" s="13" t="inlineStr">
         <is>
-          <t>Assign a Subject Teacher to a subject and section</t>
+          <t>Assign a teacher to several subjects of a section in one save</t>
         </is>
       </c>
       <c r="H18" s="13" t="inlineStr">
         <is>
-          <t>A section, a Subject Teacher and the subject exist.</t>
+          <t>A section, a teacher, and subjects of the section's grade level not yet assigned.</t>
         </is>
       </c>
       <c r="I18" s="13" t="inlineStr">
         <is>
-          <t>1. Open Section &amp; Teacher Assignments.
-2. Assign the teacher to a subject for a section of the same grade level.</t>
+          <t>1. Open Section &amp; Teacher Assignments and click Add Assignment.
+2. Choose the teacher, section and school year.
+3. Tick two or more subjects and save.</t>
         </is>
       </c>
       <c r="J18" s="13" t="inlineStr">
         <is>
-          <t>e.g. Grade 6 English to Rizal</t>
+          <t>e.g. Grade 6 English and Science to Rizal</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>The assignment is saved. The teacher now sees that subject and section on the upload page.</t>
+          <t>One save creates every ticked assignment, each listed separately. Subjects already held by another teacher show who holds them and cannot be ticked. The teacher now sees those subjects for that section on the upload page.</t>
         </is>
       </c>
       <c r="L18" s="16" t="n"/>
@@ -2263,7 +2264,7 @@
       </c>
       <c r="G19" s="13" t="inlineStr">
         <is>
-          <t>Grade-level mismatch is rejected</t>
+          <t>Only the section's own grade-level subjects are offered</t>
         </is>
       </c>
       <c r="H19" s="13" t="inlineStr">
@@ -2273,17 +2274,18 @@
       </c>
       <c r="I19" s="13" t="inlineStr">
         <is>
-          <t>1. Try to assign a Grade 3 subject to a Grade 6 section.</t>
+          <t>1. Open Add Assignment and choose a Grade 6 section.
+2. Look at the subject checklist.</t>
         </is>
       </c>
       <c r="J19" s="13" t="inlineStr">
         <is>
-          <t>Grade 3 subject, Rizal (Grade 6)</t>
+          <t>Rizal (Grade 6)</t>
         </is>
       </c>
       <c r="K19" s="13" t="inlineStr">
         <is>
-          <t>The assignment is refused with a message that the grade levels do not match.</t>
+          <t>Only Grade 6 subjects are listed, so a subject from another grade level cannot be chosen.</t>
         </is>
       </c>
       <c r="L19" s="16" t="n"/>
@@ -2336,8 +2338,9 @@
       </c>
       <c r="I20" s="13" t="inlineStr">
         <is>
-          <t>1. Choose a teacher with a Subject Teacher account.
-2. Leave Subject blank (Class Adviser) and save.</t>
+          <t>1. Open Add Assignment.
+2. Choose a teacher with a Subject Teacher account and a section without a Class Adviser.
+3. Look at the Class Adviser box.</t>
         </is>
       </c>
       <c r="J20" s="13" t="inlineStr">
@@ -2347,7 +2350,7 @@
       </c>
       <c r="K20" s="13" t="inlineStr">
         <is>
-          <t>The assignment is refused with a message that only an Adviser account can be Class Adviser. The section's Adviser slot stays free.</t>
+          <t>The Class Adviser box cannot be ticked and says it needs an Adviser account. The section's Adviser slot stays free.</t>
         </is>
       </c>
       <c r="L20" s="16" t="n"/>
@@ -5532,7 +5535,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="19" t="inlineStr">
         <is>
@@ -5628,8 +5630,6 @@
         <v/>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14"/>
     <row r="15">
       <c r="A15" s="19" t="inlineStr">
         <is>
@@ -6356,8 +6356,6 @@
         <v/>
       </c>
     </row>
-    <row r="39"/>
-    <row r="40"/>
     <row r="41">
       <c r="A41" s="19" t="inlineStr">
         <is>

--- a/03-Testing/EduCheck_UAT_Test_Cases.xlsx
+++ b/03-Testing/EduCheck_UAT_Test_Cases.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="11328" yWindow="0" windowWidth="11712" windowHeight="12240" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Test Cases" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Summary" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Defect Log" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Cases" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Defect Log" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Cases'!$A$1:$Q$68</definedName>
@@ -1029,7 +1029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q69"/>
+  <dimension ref="A1:Q72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="9" customWidth="1" style="25" min="1" max="1"/>
@@ -4105,7 +4105,7 @@
       </c>
       <c r="F48" s="13" t="inlineStr">
         <is>
-          <t>D-05</t>
+          <t>US-005</t>
         </is>
       </c>
       <c r="G48" s="13" t="inlineStr">
@@ -4115,7 +4115,7 @@
       </c>
       <c r="H48" s="13" t="inlineStr">
         <is>
-          <t>Learner has only a 3-term year.</t>
+          <t>Learner's only year is a 2025-2026 EduCheck record that is not yet approved.</t>
         </is>
       </c>
       <c r="I48" s="13" t="inlineStr">
@@ -5478,6 +5478,201 @@
       <c r="O69" s="18" t="n"/>
       <c r="P69" s="17" t="n"/>
       <c r="Q69" s="16" t="n"/>
+    </row>
+    <row r="70" ht="30" customHeight="1" s="25">
+      <c r="A70" s="14" t="inlineStr">
+        <is>
+          <t>TC-069</t>
+        </is>
+      </c>
+      <c r="B70" s="13" t="inlineStr">
+        <is>
+          <t>SF10</t>
+        </is>
+      </c>
+      <c r="C70" s="15" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D70" s="15" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="E70" s="13" t="inlineStr">
+        <is>
+          <t>Functional suitability</t>
+        </is>
+      </c>
+      <c r="F70" s="13" t="inlineStr">
+        <is>
+          <t>D-05, US-005</t>
+        </is>
+      </c>
+      <c r="G70" s="13" t="inlineStr">
+        <is>
+          <t>A 3-term year prints as Terms 1-3</t>
+        </is>
+      </c>
+      <c r="H70" s="13" t="inlineStr">
+        <is>
+          <t>A Rizal learner's 2025-2026 record has been approved (e.g. after TC-039).</t>
+        </is>
+      </c>
+      <c r="I70" s="13" t="inlineStr">
+        <is>
+          <t>1. Open Records &amp; SF10 and open that learner's Permanent Record (SF10).
+2. Check the Grade 6 card.
+3. Click Generate SF10 and open the file in Excel (Back sheet, Grade 6).</t>
+        </is>
+      </c>
+      <c r="J70" s="13" t="inlineStr">
+        <is>
+          <t>LRN of the approved learner</t>
+        </is>
+      </c>
+      <c r="K70" s="13" t="inlineStr">
+        <is>
+          <t>The Grade 6 card says it was graded in 3 terms. In the file, the Grade 6 block is headed "Term Rating" with columns T1, T2, T3 and –; each learning area shows its three term grades, final rating and remarks; the fourth column is empty; the school details are Atimonan Central School Annex.</t>
+        </is>
+      </c>
+      <c r="L70" s="16" t="n"/>
+      <c r="M70" s="17" t="n"/>
+      <c r="N70" s="16" t="n"/>
+      <c r="O70" s="18" t="n"/>
+      <c r="P70" s="17" t="n"/>
+      <c r="Q70" s="16" t="n"/>
+    </row>
+    <row r="71" ht="30" customHeight="1" s="25">
+      <c r="A71" s="14" t="inlineStr">
+        <is>
+          <t>TC-070</t>
+        </is>
+      </c>
+      <c r="B71" s="13" t="inlineStr">
+        <is>
+          <t>SF10</t>
+        </is>
+      </c>
+      <c r="C71" s="15" t="inlineStr">
+        <is>
+          <t>Adviser</t>
+        </is>
+      </c>
+      <c r="D71" s="15" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="E71" s="13" t="inlineStr">
+        <is>
+          <t>Functional suitability</t>
+        </is>
+      </c>
+      <c r="F71" s="13" t="inlineStr">
+        <is>
+          <t>US-014</t>
+        </is>
+      </c>
+      <c r="G71" s="13" t="inlineStr">
+        <is>
+          <t>Import earlier years from an existing SF10 file</t>
+        </is>
+      </c>
+      <c r="H71" s="13" t="inlineStr">
+        <is>
+          <t>Logged in as the Rizal Adviser. Learner 100000000001 has Grade 4 and Grade 5 records.</t>
+        </is>
+      </c>
+      <c r="I71" s="13" t="inlineStr">
+        <is>
+          <t>1. Open the Permanent Record of 100000000001 and click Generate SF10 to save a copy.
+2. Delete the Grade 5 year.
+3. Click Import from SF10 and choose the saved file.
+4. Check the preview, keep only Grade 5 ticked and click Import.</t>
+        </is>
+      </c>
+      <c r="J71" s="13" t="inlineStr">
+        <is>
+          <t>LRN 100000000001; the SF10 file from step 1</t>
+        </is>
+      </c>
+      <c r="K71" s="13" t="inlineStr">
+        <is>
+          <t>The preview lists Grade 4 and Grade 5 with school year, grading, number of learning areas and general average, and nothing is saved until Import is clicked. Grade 5 is restored with the same grades, appears in the readiness report and in a newly generated SF10, and the save is in the Audit Log.</t>
+        </is>
+      </c>
+      <c r="L71" s="16" t="n"/>
+      <c r="M71" s="17" t="n"/>
+      <c r="N71" s="16" t="n"/>
+      <c r="O71" s="18" t="n"/>
+      <c r="P71" s="17" t="n"/>
+      <c r="Q71" s="16" t="n"/>
+    </row>
+    <row r="72" ht="30" customHeight="1" s="25">
+      <c r="A72" s="14" t="inlineStr">
+        <is>
+          <t>TC-071</t>
+        </is>
+      </c>
+      <c r="B72" s="13" t="inlineStr">
+        <is>
+          <t>SF10</t>
+        </is>
+      </c>
+      <c r="C72" s="15" t="inlineStr">
+        <is>
+          <t>Adviser</t>
+        </is>
+      </c>
+      <c r="D72" s="15" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="E72" s="13" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="F72" s="13" t="inlineStr">
+        <is>
+          <t>US-014</t>
+        </is>
+      </c>
+      <c r="G72" s="13" t="inlineStr">
+        <is>
+          <t>Import refuses another learner's SF10</t>
+        </is>
+      </c>
+      <c r="H72" s="13" t="inlineStr">
+        <is>
+          <t>Logged in as the Rizal Adviser. The SF10 file of 100000000001 from TC-070.</t>
+        </is>
+      </c>
+      <c r="I72" s="13" t="inlineStr">
+        <is>
+          <t>1. Open the Permanent Record of another Rizal learner.
+2. Click Import from SF10 and choose 100000000001's file.</t>
+        </is>
+      </c>
+      <c r="J72" s="13" t="inlineStr">
+        <is>
+          <t>e.g. LRN 100000000004</t>
+        </is>
+      </c>
+      <c r="K72" s="13" t="inlineStr">
+        <is>
+          <t>The import is refused with a message that the SF10 belongs to LRN 100000000001. Nothing is saved.</t>
+        </is>
+      </c>
+      <c r="L72" s="16" t="n"/>
+      <c r="M72" s="17" t="n"/>
+      <c r="N72" s="16" t="n"/>
+      <c r="O72" s="18" t="n"/>
+      <c r="P72" s="17" t="n"/>
+      <c r="Q72" s="16" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:Q68"/>
@@ -5496,10 +5691,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="M2:M69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Status" error="Choose Pass, Fail, Blocked or Not Run." type="list">
+    <dataValidation sqref="M2:M72" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Status" error="Choose Pass, Fail, Blocked or Not Run." type="list">
       <formula1>"Pass,Fail,Blocked,Not Run"</formula1>
     </dataValidation>
-    <dataValidation sqref="O2:O69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Enter a date (YYYY-MM-DD)." type="date" operator="greaterThan">
+    <dataValidation sqref="O2:O72" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Enter a date (YYYY-MM-DD)." type="date" operator="greaterThan">
       <formula1>DATE(2026,1,1)</formula1>
     </dataValidation>
   </dataValidations>
@@ -5535,6 +5730,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="19" t="inlineStr">
         <is>
@@ -5549,7 +5745,7 @@
         </is>
       </c>
       <c r="B5" s="20">
-        <f>COUNTA('Test Cases'!$A$2:$A$69)</f>
+        <f>COUNTA('Test Cases'!$A$2:$A$72)</f>
         <v/>
       </c>
     </row>
@@ -5560,7 +5756,7 @@
         </is>
       </c>
       <c r="B6" s="20">
-        <f>COUNTIF('Test Cases'!$M$2:$M$69,"Pass")</f>
+        <f>COUNTIF('Test Cases'!$M$2:$M$72,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -5571,7 +5767,7 @@
         </is>
       </c>
       <c r="B7" s="20">
-        <f>COUNTIF('Test Cases'!$M$2:$M$69,"Fail")</f>
+        <f>COUNTIF('Test Cases'!$M$2:$M$72,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -5582,7 +5778,7 @@
         </is>
       </c>
       <c r="B8" s="20">
-        <f>COUNTIF('Test Cases'!$M$2:$M$69,"Blocked")</f>
+        <f>COUNTIF('Test Cases'!$M$2:$M$72,"Blocked")</f>
         <v/>
       </c>
     </row>
@@ -5630,6 +5826,8 @@
         <v/>
       </c>
     </row>
+    <row r="13"/>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="19" t="inlineStr">
         <is>
@@ -5681,19 +5879,19 @@
         </is>
       </c>
       <c r="B17" s="20">
-        <f>COUNTIF('Test Cases'!$B$2:$B$69,A17)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$72,A17)</f>
         <v/>
       </c>
       <c r="C17" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A17,'Test Cases'!$M$2:$M$69,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$72,A17,'Test Cases'!$M$2:$M$72,"Pass")</f>
         <v/>
       </c>
       <c r="D17" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A17,'Test Cases'!$M$2:$M$69,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$72,A17,'Test Cases'!$M$2:$M$72,"Fail")</f>
         <v/>
       </c>
       <c r="E17" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A17,'Test Cases'!$M$2:$M$69,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$72,A17,'Test Cases'!$M$2:$M$72,"Blocked")</f>
         <v/>
       </c>
       <c r="F17" s="20">
@@ -5712,19 +5910,19 @@
         </is>
       </c>
       <c r="B18" s="20">
-        <f>COUNTIF('Test Cases'!$B$2:$B$69,A18)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$72,A18)</f>
         <v/>
       </c>
       <c r="C18" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A18,'Test Cases'!$M$2:$M$69,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$72,A18,'Test Cases'!$M$2:$M$72,"Pass")</f>
         <v/>
       </c>
       <c r="D18" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A18,'Test Cases'!$M$2:$M$69,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$72,A18,'Test Cases'!$M$2:$M$72,"Fail")</f>
         <v/>
       </c>
       <c r="E18" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A18,'Test Cases'!$M$2:$M$69,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$72,A18,'Test Cases'!$M$2:$M$72,"Blocked")</f>
         <v/>
       </c>
       <c r="F18" s="20">
@@ -5743,19 +5941,19 @@
         </is>
       </c>
       <c r="B19" s="20">
-        <f>COUNTIF('Test Cases'!$B$2:$B$69,A19)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$72,A19)</f>
         <v/>
       </c>
       <c r="C19" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A19,'Test Cases'!$M$2:$M$69,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$72,A19,'Test Cases'!$M$2:$M$72,"Pass")</f>
         <v/>
       </c>
       <c r="D19" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A19,'Test Cases'!$M$2:$M$69,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$72,A19,'Test Cases'!$M$2:$M$72,"Fail")</f>
         <v/>
       </c>
       <c r="E19" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A19,'Test Cases'!$M$2:$M$69,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$72,A19,'Test Cases'!$M$2:$M$72,"Blocked")</f>
         <v/>
       </c>
       <c r="F19" s="20">
@@ -5774,19 +5972,19 @@
         </is>
       </c>
       <c r="B20" s="20">
-        <f>COUNTIF('Test Cases'!$B$2:$B$69,A20)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$72,A20)</f>
         <v/>
       </c>
       <c r="C20" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A20,'Test Cases'!$M$2:$M$69,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$72,A20,'Test Cases'!$M$2:$M$72,"Pass")</f>
         <v/>
       </c>
       <c r="D20" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A20,'Test Cases'!$M$2:$M$69,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$72,A20,'Test Cases'!$M$2:$M$72,"Fail")</f>
         <v/>
       </c>
       <c r="E20" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A20,'Test Cases'!$M$2:$M$69,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$72,A20,'Test Cases'!$M$2:$M$72,"Blocked")</f>
         <v/>
       </c>
       <c r="F20" s="20">
@@ -5805,19 +6003,19 @@
         </is>
       </c>
       <c r="B21" s="20">
-        <f>COUNTIF('Test Cases'!$B$2:$B$69,A21)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$72,A21)</f>
         <v/>
       </c>
       <c r="C21" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A21,'Test Cases'!$M$2:$M$69,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$72,A21,'Test Cases'!$M$2:$M$72,"Pass")</f>
         <v/>
       </c>
       <c r="D21" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A21,'Test Cases'!$M$2:$M$69,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$72,A21,'Test Cases'!$M$2:$M$72,"Fail")</f>
         <v/>
       </c>
       <c r="E21" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A21,'Test Cases'!$M$2:$M$69,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$72,A21,'Test Cases'!$M$2:$M$72,"Blocked")</f>
         <v/>
       </c>
       <c r="F21" s="20">
@@ -5836,19 +6034,19 @@
         </is>
       </c>
       <c r="B22" s="20">
-        <f>COUNTIF('Test Cases'!$B$2:$B$69,A22)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$72,A22)</f>
         <v/>
       </c>
       <c r="C22" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A22,'Test Cases'!$M$2:$M$69,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$72,A22,'Test Cases'!$M$2:$M$72,"Pass")</f>
         <v/>
       </c>
       <c r="D22" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A22,'Test Cases'!$M$2:$M$69,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$72,A22,'Test Cases'!$M$2:$M$72,"Fail")</f>
         <v/>
       </c>
       <c r="E22" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A22,'Test Cases'!$M$2:$M$69,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$72,A22,'Test Cases'!$M$2:$M$72,"Blocked")</f>
         <v/>
       </c>
       <c r="F22" s="20">
@@ -5867,19 +6065,19 @@
         </is>
       </c>
       <c r="B23" s="20">
-        <f>COUNTIF('Test Cases'!$B$2:$B$69,A23)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$72,A23)</f>
         <v/>
       </c>
       <c r="C23" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A23,'Test Cases'!$M$2:$M$69,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$72,A23,'Test Cases'!$M$2:$M$72,"Pass")</f>
         <v/>
       </c>
       <c r="D23" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A23,'Test Cases'!$M$2:$M$69,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$72,A23,'Test Cases'!$M$2:$M$72,"Fail")</f>
         <v/>
       </c>
       <c r="E23" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A23,'Test Cases'!$M$2:$M$69,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$72,A23,'Test Cases'!$M$2:$M$72,"Blocked")</f>
         <v/>
       </c>
       <c r="F23" s="20">
@@ -5898,19 +6096,19 @@
         </is>
       </c>
       <c r="B24" s="20">
-        <f>COUNTIF('Test Cases'!$B$2:$B$69,A24)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$72,A24)</f>
         <v/>
       </c>
       <c r="C24" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A24,'Test Cases'!$M$2:$M$69,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$72,A24,'Test Cases'!$M$2:$M$72,"Pass")</f>
         <v/>
       </c>
       <c r="D24" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A24,'Test Cases'!$M$2:$M$69,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$72,A24,'Test Cases'!$M$2:$M$72,"Fail")</f>
         <v/>
       </c>
       <c r="E24" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A24,'Test Cases'!$M$2:$M$69,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$72,A24,'Test Cases'!$M$2:$M$72,"Blocked")</f>
         <v/>
       </c>
       <c r="F24" s="20">
@@ -5929,19 +6127,19 @@
         </is>
       </c>
       <c r="B25" s="20">
-        <f>COUNTIF('Test Cases'!$B$2:$B$69,A25)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$72,A25)</f>
         <v/>
       </c>
       <c r="C25" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A25,'Test Cases'!$M$2:$M$69,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$72,A25,'Test Cases'!$M$2:$M$72,"Pass")</f>
         <v/>
       </c>
       <c r="D25" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A25,'Test Cases'!$M$2:$M$69,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$72,A25,'Test Cases'!$M$2:$M$72,"Fail")</f>
         <v/>
       </c>
       <c r="E25" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A25,'Test Cases'!$M$2:$M$69,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$72,A25,'Test Cases'!$M$2:$M$72,"Blocked")</f>
         <v/>
       </c>
       <c r="F25" s="20">
@@ -5960,19 +6158,19 @@
         </is>
       </c>
       <c r="B26" s="20">
-        <f>COUNTIF('Test Cases'!$B$2:$B$69,A26)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$72,A26)</f>
         <v/>
       </c>
       <c r="C26" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A26,'Test Cases'!$M$2:$M$69,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$72,A26,'Test Cases'!$M$2:$M$72,"Pass")</f>
         <v/>
       </c>
       <c r="D26" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A26,'Test Cases'!$M$2:$M$69,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$72,A26,'Test Cases'!$M$2:$M$72,"Fail")</f>
         <v/>
       </c>
       <c r="E26" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A26,'Test Cases'!$M$2:$M$69,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$72,A26,'Test Cases'!$M$2:$M$72,"Blocked")</f>
         <v/>
       </c>
       <c r="F26" s="20">
@@ -5991,19 +6189,19 @@
         </is>
       </c>
       <c r="B27" s="20">
-        <f>COUNTIF('Test Cases'!$B$2:$B$69,A27)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$72,A27)</f>
         <v/>
       </c>
       <c r="C27" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A27,'Test Cases'!$M$2:$M$69,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$72,A27,'Test Cases'!$M$2:$M$72,"Pass")</f>
         <v/>
       </c>
       <c r="D27" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A27,'Test Cases'!$M$2:$M$69,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$72,A27,'Test Cases'!$M$2:$M$72,"Fail")</f>
         <v/>
       </c>
       <c r="E27" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A27,'Test Cases'!$M$2:$M$69,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$72,A27,'Test Cases'!$M$2:$M$72,"Blocked")</f>
         <v/>
       </c>
       <c r="F27" s="20">
@@ -6022,19 +6220,19 @@
         </is>
       </c>
       <c r="B28" s="20">
-        <f>COUNTIF('Test Cases'!$B$2:$B$69,A28)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$72,A28)</f>
         <v/>
       </c>
       <c r="C28" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A28,'Test Cases'!$M$2:$M$69,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$72,A28,'Test Cases'!$M$2:$M$72,"Pass")</f>
         <v/>
       </c>
       <c r="D28" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A28,'Test Cases'!$M$2:$M$69,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$72,A28,'Test Cases'!$M$2:$M$72,"Fail")</f>
         <v/>
       </c>
       <c r="E28" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A28,'Test Cases'!$M$2:$M$69,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$72,A28,'Test Cases'!$M$2:$M$72,"Blocked")</f>
         <v/>
       </c>
       <c r="F28" s="20">
@@ -6053,19 +6251,19 @@
         </is>
       </c>
       <c r="B29" s="20">
-        <f>COUNTIF('Test Cases'!$B$2:$B$69,A29)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$72,A29)</f>
         <v/>
       </c>
       <c r="C29" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A29,'Test Cases'!$M$2:$M$69,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$72,A29,'Test Cases'!$M$2:$M$72,"Pass")</f>
         <v/>
       </c>
       <c r="D29" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A29,'Test Cases'!$M$2:$M$69,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$72,A29,'Test Cases'!$M$2:$M$72,"Fail")</f>
         <v/>
       </c>
       <c r="E29" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A29,'Test Cases'!$M$2:$M$69,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$72,A29,'Test Cases'!$M$2:$M$72,"Blocked")</f>
         <v/>
       </c>
       <c r="F29" s="20">
@@ -6084,19 +6282,19 @@
         </is>
       </c>
       <c r="B30" s="20">
-        <f>COUNTIF('Test Cases'!$B$2:$B$69,A30)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$72,A30)</f>
         <v/>
       </c>
       <c r="C30" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A30,'Test Cases'!$M$2:$M$69,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$72,A30,'Test Cases'!$M$2:$M$72,"Pass")</f>
         <v/>
       </c>
       <c r="D30" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A30,'Test Cases'!$M$2:$M$69,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$72,A30,'Test Cases'!$M$2:$M$72,"Fail")</f>
         <v/>
       </c>
       <c r="E30" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A30,'Test Cases'!$M$2:$M$69,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$72,A30,'Test Cases'!$M$2:$M$72,"Blocked")</f>
         <v/>
       </c>
       <c r="F30" s="20">
@@ -6115,19 +6313,19 @@
         </is>
       </c>
       <c r="B31" s="20">
-        <f>COUNTIF('Test Cases'!$B$2:$B$69,A31)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$72,A31)</f>
         <v/>
       </c>
       <c r="C31" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A31,'Test Cases'!$M$2:$M$69,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$72,A31,'Test Cases'!$M$2:$M$72,"Pass")</f>
         <v/>
       </c>
       <c r="D31" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A31,'Test Cases'!$M$2:$M$69,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$72,A31,'Test Cases'!$M$2:$M$72,"Fail")</f>
         <v/>
       </c>
       <c r="E31" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A31,'Test Cases'!$M$2:$M$69,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$72,A31,'Test Cases'!$M$2:$M$72,"Blocked")</f>
         <v/>
       </c>
       <c r="F31" s="20">
@@ -6146,19 +6344,19 @@
         </is>
       </c>
       <c r="B32" s="20">
-        <f>COUNTIF('Test Cases'!$B$2:$B$69,A32)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$72,A32)</f>
         <v/>
       </c>
       <c r="C32" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A32,'Test Cases'!$M$2:$M$69,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$72,A32,'Test Cases'!$M$2:$M$72,"Pass")</f>
         <v/>
       </c>
       <c r="D32" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A32,'Test Cases'!$M$2:$M$69,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$72,A32,'Test Cases'!$M$2:$M$72,"Fail")</f>
         <v/>
       </c>
       <c r="E32" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A32,'Test Cases'!$M$2:$M$69,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$72,A32,'Test Cases'!$M$2:$M$72,"Blocked")</f>
         <v/>
       </c>
       <c r="F32" s="20">
@@ -6177,19 +6375,19 @@
         </is>
       </c>
       <c r="B33" s="20">
-        <f>COUNTIF('Test Cases'!$B$2:$B$69,A33)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$72,A33)</f>
         <v/>
       </c>
       <c r="C33" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A33,'Test Cases'!$M$2:$M$69,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$72,A33,'Test Cases'!$M$2:$M$72,"Pass")</f>
         <v/>
       </c>
       <c r="D33" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A33,'Test Cases'!$M$2:$M$69,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$72,A33,'Test Cases'!$M$2:$M$72,"Fail")</f>
         <v/>
       </c>
       <c r="E33" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A33,'Test Cases'!$M$2:$M$69,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$72,A33,'Test Cases'!$M$2:$M$72,"Blocked")</f>
         <v/>
       </c>
       <c r="F33" s="20">
@@ -6208,19 +6406,19 @@
         </is>
       </c>
       <c r="B34" s="20">
-        <f>COUNTIF('Test Cases'!$B$2:$B$69,A34)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$72,A34)</f>
         <v/>
       </c>
       <c r="C34" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A34,'Test Cases'!$M$2:$M$69,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$72,A34,'Test Cases'!$M$2:$M$72,"Pass")</f>
         <v/>
       </c>
       <c r="D34" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A34,'Test Cases'!$M$2:$M$69,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$72,A34,'Test Cases'!$M$2:$M$72,"Fail")</f>
         <v/>
       </c>
       <c r="E34" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A34,'Test Cases'!$M$2:$M$69,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$72,A34,'Test Cases'!$M$2:$M$72,"Blocked")</f>
         <v/>
       </c>
       <c r="F34" s="20">
@@ -6239,19 +6437,19 @@
         </is>
       </c>
       <c r="B35" s="20">
-        <f>COUNTIF('Test Cases'!$B$2:$B$69,A35)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$72,A35)</f>
         <v/>
       </c>
       <c r="C35" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A35,'Test Cases'!$M$2:$M$69,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$72,A35,'Test Cases'!$M$2:$M$72,"Pass")</f>
         <v/>
       </c>
       <c r="D35" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A35,'Test Cases'!$M$2:$M$69,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$72,A35,'Test Cases'!$M$2:$M$72,"Fail")</f>
         <v/>
       </c>
       <c r="E35" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A35,'Test Cases'!$M$2:$M$69,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$72,A35,'Test Cases'!$M$2:$M$72,"Blocked")</f>
         <v/>
       </c>
       <c r="F35" s="20">
@@ -6270,19 +6468,19 @@
         </is>
       </c>
       <c r="B36" s="20">
-        <f>COUNTIF('Test Cases'!$B$2:$B$69,A36)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$72,A36)</f>
         <v/>
       </c>
       <c r="C36" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A36,'Test Cases'!$M$2:$M$69,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$72,A36,'Test Cases'!$M$2:$M$72,"Pass")</f>
         <v/>
       </c>
       <c r="D36" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A36,'Test Cases'!$M$2:$M$69,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$72,A36,'Test Cases'!$M$2:$M$72,"Fail")</f>
         <v/>
       </c>
       <c r="E36" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A36,'Test Cases'!$M$2:$M$69,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$72,A36,'Test Cases'!$M$2:$M$72,"Blocked")</f>
         <v/>
       </c>
       <c r="F36" s="20">
@@ -6301,19 +6499,19 @@
         </is>
       </c>
       <c r="B37" s="20">
-        <f>COUNTIF('Test Cases'!$B$2:$B$69,A37)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$72,A37)</f>
         <v/>
       </c>
       <c r="C37" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A37,'Test Cases'!$M$2:$M$69,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$72,A37,'Test Cases'!$M$2:$M$72,"Pass")</f>
         <v/>
       </c>
       <c r="D37" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A37,'Test Cases'!$M$2:$M$69,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$72,A37,'Test Cases'!$M$2:$M$72,"Fail")</f>
         <v/>
       </c>
       <c r="E37" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A37,'Test Cases'!$M$2:$M$69,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$72,A37,'Test Cases'!$M$2:$M$72,"Blocked")</f>
         <v/>
       </c>
       <c r="F37" s="20">
@@ -6332,19 +6530,19 @@
         </is>
       </c>
       <c r="B38" s="20">
-        <f>COUNTIF('Test Cases'!$B$2:$B$69,A38)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$72,A38)</f>
         <v/>
       </c>
       <c r="C38" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A38,'Test Cases'!$M$2:$M$69,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$72,A38,'Test Cases'!$M$2:$M$72,"Pass")</f>
         <v/>
       </c>
       <c r="D38" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A38,'Test Cases'!$M$2:$M$69,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$72,A38,'Test Cases'!$M$2:$M$72,"Fail")</f>
         <v/>
       </c>
       <c r="E38" s="20">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$69,A38,'Test Cases'!$M$2:$M$69,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$72,A38,'Test Cases'!$M$2:$M$72,"Blocked")</f>
         <v/>
       </c>
       <c r="F38" s="20">
@@ -6356,6 +6554,8 @@
         <v/>
       </c>
     </row>
+    <row r="39"/>
+    <row r="40"/>
     <row r="41">
       <c r="A41" s="19" t="inlineStr">
         <is>
@@ -6407,19 +6607,19 @@
         </is>
       </c>
       <c r="B43" s="20">
-        <f>COUNTIF('Test Cases'!$E$2:$E$69,A43)</f>
+        <f>COUNTIF('Test Cases'!$E$2:$E$72,A43)</f>
         <v/>
       </c>
       <c r="C43" s="20">
-        <f>COUNTIFS('Test Cases'!$E$2:$E$69,A43,'Test Cases'!$M$2:$M$69,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$E$2:$E$72,A43,'Test Cases'!$M$2:$M$72,"Pass")</f>
         <v/>
       </c>
       <c r="D43" s="20">
-        <f>COUNTIFS('Test Cases'!$E$2:$E$69,A43,'Test Cases'!$M$2:$M$69,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$E$2:$E$72,A43,'Test Cases'!$M$2:$M$72,"Fail")</f>
         <v/>
       </c>
       <c r="E43" s="20">
-        <f>COUNTIFS('Test Cases'!$E$2:$E$69,A43,'Test Cases'!$M$2:$M$69,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$E$2:$E$72,A43,'Test Cases'!$M$2:$M$72,"Blocked")</f>
         <v/>
       </c>
       <c r="F43" s="20">
@@ -6438,19 +6638,19 @@
         </is>
       </c>
       <c r="B44" s="20">
-        <f>COUNTIF('Test Cases'!$E$2:$E$69,A44)</f>
+        <f>COUNTIF('Test Cases'!$E$2:$E$72,A44)</f>
         <v/>
       </c>
       <c r="C44" s="20">
-        <f>COUNTIFS('Test Cases'!$E$2:$E$69,A44,'Test Cases'!$M$2:$M$69,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$E$2:$E$72,A44,'Test Cases'!$M$2:$M$72,"Pass")</f>
         <v/>
       </c>
       <c r="D44" s="20">
-        <f>COUNTIFS('Test Cases'!$E$2:$E$69,A44,'Test Cases'!$M$2:$M$69,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$E$2:$E$72,A44,'Test Cases'!$M$2:$M$72,"Fail")</f>
         <v/>
       </c>
       <c r="E44" s="20">
-        <f>COUNTIFS('Test Cases'!$E$2:$E$69,A44,'Test Cases'!$M$2:$M$69,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$E$2:$E$72,A44,'Test Cases'!$M$2:$M$72,"Blocked")</f>
         <v/>
       </c>
       <c r="F44" s="20">
@@ -6469,19 +6669,19 @@
         </is>
       </c>
       <c r="B45" s="20">
-        <f>COUNTIF('Test Cases'!$E$2:$E$69,A45)</f>
+        <f>COUNTIF('Test Cases'!$E$2:$E$72,A45)</f>
         <v/>
       </c>
       <c r="C45" s="20">
-        <f>COUNTIFS('Test Cases'!$E$2:$E$69,A45,'Test Cases'!$M$2:$M$69,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$E$2:$E$72,A45,'Test Cases'!$M$2:$M$72,"Pass")</f>
         <v/>
       </c>
       <c r="D45" s="20">
-        <f>COUNTIFS('Test Cases'!$E$2:$E$69,A45,'Test Cases'!$M$2:$M$69,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$E$2:$E$72,A45,'Test Cases'!$M$2:$M$72,"Fail")</f>
         <v/>
       </c>
       <c r="E45" s="20">
-        <f>COUNTIFS('Test Cases'!$E$2:$E$69,A45,'Test Cases'!$M$2:$M$69,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$E$2:$E$72,A45,'Test Cases'!$M$2:$M$72,"Blocked")</f>
         <v/>
       </c>
       <c r="F45" s="20">
@@ -6500,19 +6700,19 @@
         </is>
       </c>
       <c r="B46" s="20">
-        <f>COUNTIF('Test Cases'!$E$2:$E$69,A46)</f>
+        <f>COUNTIF('Test Cases'!$E$2:$E$72,A46)</f>
         <v/>
       </c>
       <c r="C46" s="20">
-        <f>COUNTIFS('Test Cases'!$E$2:$E$69,A46,'Test Cases'!$M$2:$M$69,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$E$2:$E$72,A46,'Test Cases'!$M$2:$M$72,"Pass")</f>
         <v/>
       </c>
       <c r="D46" s="20">
-        <f>COUNTIFS('Test Cases'!$E$2:$E$69,A46,'Test Cases'!$M$2:$M$69,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$E$2:$E$72,A46,'Test Cases'!$M$2:$M$72,"Fail")</f>
         <v/>
       </c>
       <c r="E46" s="20">
-        <f>COUNTIFS('Test Cases'!$E$2:$E$69,A46,'Test Cases'!$M$2:$M$69,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$E$2:$E$72,A46,'Test Cases'!$M$2:$M$72,"Blocked")</f>
         <v/>
       </c>
       <c r="F46" s="20">
@@ -6531,19 +6731,19 @@
         </is>
       </c>
       <c r="B47" s="20">
-        <f>COUNTIF('Test Cases'!$E$2:$E$69,A47)</f>
+        <f>COUNTIF('Test Cases'!$E$2:$E$72,A47)</f>
         <v/>
       </c>
       <c r="C47" s="20">
-        <f>COUNTIFS('Test Cases'!$E$2:$E$69,A47,'Test Cases'!$M$2:$M$69,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$E$2:$E$72,A47,'Test Cases'!$M$2:$M$72,"Pass")</f>
         <v/>
       </c>
       <c r="D47" s="20">
-        <f>COUNTIFS('Test Cases'!$E$2:$E$69,A47,'Test Cases'!$M$2:$M$69,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$E$2:$E$72,A47,'Test Cases'!$M$2:$M$72,"Fail")</f>
         <v/>
       </c>
       <c r="E47" s="20">
-        <f>COUNTIFS('Test Cases'!$E$2:$E$69,A47,'Test Cases'!$M$2:$M$69,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$E$2:$E$72,A47,'Test Cases'!$M$2:$M$72,"Blocked")</f>
         <v/>
       </c>
       <c r="F47" s="20">
@@ -6562,19 +6762,19 @@
         </is>
       </c>
       <c r="B48" s="20">
-        <f>COUNTIF('Test Cases'!$E$2:$E$69,A48)</f>
+        <f>COUNTIF('Test Cases'!$E$2:$E$72,A48)</f>
         <v/>
       </c>
       <c r="C48" s="20">
-        <f>COUNTIFS('Test Cases'!$E$2:$E$69,A48,'Test Cases'!$M$2:$M$69,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$E$2:$E$72,A48,'Test Cases'!$M$2:$M$72,"Pass")</f>
         <v/>
       </c>
       <c r="D48" s="20">
-        <f>COUNTIFS('Test Cases'!$E$2:$E$69,A48,'Test Cases'!$M$2:$M$69,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$E$2:$E$72,A48,'Test Cases'!$M$2:$M$72,"Fail")</f>
         <v/>
       </c>
       <c r="E48" s="20">
-        <f>COUNTIFS('Test Cases'!$E$2:$E$69,A48,'Test Cases'!$M$2:$M$69,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$E$2:$E$72,A48,'Test Cases'!$M$2:$M$72,"Blocked")</f>
         <v/>
       </c>
       <c r="F48" s="20">

--- a/03-Testing/EduCheck_UAT_Test_Cases.xlsx
+++ b/03-Testing/EduCheck_UAT_Test_Cases.xlsx
@@ -908,7 +908,7 @@
       <c r="C33" s="6" t="n"/>
       <c r="D33" s="13" t="inlineStr">
         <is>
-          <t>Adviser of Rizal (Grade 6, Self-Contained).</t>
+          <t>Maria Teresa Santos (fictitious name). Class Adviser of Rizal (Grade 6, Departmentalized); teaches English, ESP, Filipino and Science.</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       <c r="C34" s="6" t="n"/>
       <c r="D34" s="13" t="inlineStr">
         <is>
-          <t>Uploads e-class records.</t>
+          <t>Jose Miguel Reyes (fictitious name). Teaches Araling Panlipunan, MAPEH, Mathematics and TLE in Rizal.</t>
         </is>
       </c>
     </row>
@@ -966,7 +966,7 @@
       </c>
       <c r="B38" s="24" t="inlineStr">
         <is>
-          <t>Rizal (Grade 6, Self-Contained, 100 learners). Mabini (Grade 3, Departmentalized, 5 learners LRN 300000000001-005, no Class Adviser). School year 2025-2026. Pending Approval at start: LRN 100000000004-015. Incomplete (no TLE grade): LRN 100000000099 and 100000000100. No Approved records at start.</t>
+          <t>Rizal (Grade 6, Departmentalized, 100 learners). Mabini (Grade 3, Self-Contained, 5 learners LRN 300000000001-005, no Class Adviser). School year 2025-2026. Pending Approval at start: LRN 100000000004-015. Incomplete (no TLE grade): LRN 100000000099 and 100000000100. No Approved records at start.</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
       </c>
       <c r="B39" s="24" t="inlineStr">
         <is>
-          <t>LRN 100000000001 (Adrian Aguilar). Sample Grade 4 and 5 history; readiness PARTIAL.</t>
+          <t>LRN 100000000001 (Adrian Aguilar). Sample Grade 4 and 5 history; readiness PARTIAL. Grade 6 prints as Terms 1-3 only after approval (D-05).</t>
         </is>
       </c>
     </row>
@@ -4120,12 +4120,12 @@
       </c>
       <c r="I48" s="13" t="inlineStr">
         <is>
-          <t>1. Try to download the SF10 of any other Rizal learner.</t>
+          <t>1. Try to download the SF10 of a Rizal learner who is not approved.</t>
         </is>
       </c>
       <c r="J48" s="13" t="inlineStr">
         <is>
-          <t>e.g. LRN 100000000004</t>
+          <t>e.g. LRN 100000000020 (never submitted or approved in the session)</t>
         </is>
       </c>
       <c r="K48" s="13" t="inlineStr">
@@ -5730,7 +5730,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="19" t="inlineStr">
         <is>
@@ -5826,8 +5825,6 @@
         <v/>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14"/>
     <row r="15">
       <c r="A15" s="19" t="inlineStr">
         <is>
@@ -6554,8 +6551,6 @@
         <v/>
       </c>
     </row>
-    <row r="39"/>
-    <row r="40"/>
     <row r="41">
       <c r="A41" s="19" t="inlineStr">
         <is>

--- a/03-Testing/EduCheck_UAT_Test_Cases.xlsx
+++ b/03-Testing/EduCheck_UAT_Test_Cases.xlsx
@@ -3727,7 +3727,7 @@
       </c>
       <c r="G42" s="13" t="inlineStr">
         <is>
-          <t>Approved record is locked against re-upload</t>
+          <t>Approved learner is locked against re-upload</t>
         </is>
       </c>
       <c r="H42" s="13" t="inlineStr">
@@ -3747,7 +3747,7 @@
       </c>
       <c r="K42" s="13" t="inlineStr">
         <is>
-          <t>The upload is refused because the record is approved.</t>
+          <t>The upload is accepted for the rest of the class. The result page lists the approved learner as not updated, and that learner's grades and Approved status do not change.</t>
         </is>
       </c>
       <c r="L42" s="16" t="n"/>

--- a/03-Testing/EduCheck_UAT_Test_Cases.xlsx
+++ b/03-Testing/EduCheck_UAT_Test_Cases.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NITROV~1\AppData\Local\Temp\claude\c--Users-NITRO-V-OneDrive-Documents-GitHub-Capstone-Project-EduCheck\9bebcca7-c289-4db2-9cc5-12eb7c524200\scratchpad\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/998bf0dccc2814d1/Documents/GitHub/Capstone-Project_EduCheck/03-Testing/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52CD8B1F-557E-4A49-BA7B-443700968FCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_C1F5BA203F8BA9F4AE009BB4139EBEDC2939DAAE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="11712" windowHeight="12240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -40,11 +40,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1055" uniqueCount="636">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1105" uniqueCount="667">
   <si>
     <t>EduCheck - User Acceptance Test Cases</t>
   </si>
   <si>
+    <t>Formal testing and UAT, ISO/IEC 25010. Read 03-Testing/EduCheck_Known_Limitations.md first: items listed there are not defects. Revised 2026-10-19 for the Accounts page and Principal account approval (TC-012 to TC-016, TC-044, TC-072 to TC-076); the UAT on 2026-10-16 used the earlier User Management and Teacher Management pages.</t>
+  </si>
+  <si>
     <t>Test session</t>
   </si>
   <si>
@@ -177,6 +180,9 @@
     <t>Admin</t>
   </si>
   <si>
+    <t>Reviews and approves records; adds accounts in Accounts and finishes their setup after the Principal approves them.</t>
+  </si>
+  <si>
     <t>adviser.grade6a</t>
   </si>
   <si>
@@ -201,6 +207,9 @@
     <t>Principal</t>
   </si>
   <si>
+    <t>Approves or rejects new accounts in Account Approvals; everything else is view-only.</t>
+  </si>
+  <si>
     <t>Test data</t>
   </si>
   <si>
@@ -223,6 +232,9 @@
   </si>
   <si>
     <t>Before starting</t>
+  </si>
+  <si>
+    <t>Back up the database so testing can be repeated from the same state. After restoring a backup taken before 2026-10-17, re-run migrations 010 and 011 (see the Day Kit).</t>
   </si>
   <si>
     <t>Module</t>
@@ -331,6 +343,9 @@
     <t>Inactive account cannot log in</t>
   </si>
   <si>
+    <t>Admin has set a test account to Inactive in Accounts.</t>
+  </si>
+  <si>
     <t>1. Log in with the inactive account's correct password.</t>
   </si>
   <si>
@@ -388,6 +403,11 @@
   </si>
   <si>
     <t>Logged in as Subject Teacher.</t>
+  </si>
+  <si>
+    <t>1. Type /accounts in the address bar.
+2. Type /audit-log.
+3. Type /consolidated-records.</t>
   </si>
   <si>
     <t>Each attempt redirects to the user's own Dashboard. No Admin or Adviser data is shown.</t>
@@ -471,31 +491,104 @@
     <t>TC-012</t>
   </si>
   <si>
-    <t>Logged in as Admin.</t>
+    <t>Accounts</t>
+  </si>
+  <si>
+    <t>§6.2, US-015</t>
+  </si>
+  <si>
+    <t>Create an account (waits for the Principal)</t>
+  </si>
+  <si>
+    <t>Logged in as Admin. A Principal account is Active.</t>
+  </si>
+  <si>
+    <t>1. Open Accounts and click Add Account.
+2. Enter a DepEd email, the role, and (for a teacher) the name. The username is suggested from the email.
+3. Click Create Account.
+4. Log out and try to log in as the new account.</t>
+  </si>
+  <si>
+    <t>New test account, e.g. test.teacher@deped.gov.ph</t>
+  </si>
+  <si>
+    <t>The account is listed as Pending Approval and the Principal is notified. It cannot log in until the Principal approves it (TC-073) and the Admin finishes its setup (TC-075).</t>
   </si>
   <si>
     <t>TC-013</t>
   </si>
   <si>
+    <t>Edit an account and deactivate it</t>
+  </si>
+  <si>
+    <t>An Active test account exists (after TC-075).</t>
+  </si>
+  <si>
+    <t>1. Edit the account and change the email (must end in @deped.gov.ph) or the name.
+2. Set Status to Inactive and save.</t>
+  </si>
+  <si>
+    <t>Test account</t>
+  </si>
+  <si>
+    <t>Changes are saved and shown in the list. The inactive account can no longer log in (TC-004).</t>
+  </si>
+  <si>
+    <t>TC-014</t>
+  </si>
+  <si>
+    <t>L-02</t>
+  </si>
+  <si>
+    <t>Admin resets a user's password</t>
+  </si>
+  <si>
     <t>A test user exists.</t>
   </si>
   <si>
-    <t>TC-014</t>
-  </si>
-  <si>
-    <t>L-02</t>
-  </si>
-  <si>
-    <t>Admin resets a user's password</t>
+    <t>1. Edit the account, type a new password in Reset Password (or generate one) and save.
+2. Log in as that user with the old password, then with the new one.</t>
+  </si>
+  <si>
+    <t>The old password stops working. The new one works and must be replaced at sign-in, like a temporary password. With internet, it is also emailed to the DepEd address (L-02).</t>
   </si>
   <si>
     <t>TC-015</t>
   </si>
   <si>
+    <t>Search accounts</t>
+  </si>
+  <si>
+    <t>Several accounts exist.</t>
+  </si>
+  <si>
+    <t>1. Open Accounts.
+2. Type part of a name, username, email or role in the search box.</t>
+  </si>
+  <si>
     <t>e.g. grade6</t>
   </si>
   <si>
+    <t>Only matching accounts are listed.</t>
+  </si>
+  <si>
     <t>TC-016</t>
+  </si>
+  <si>
+    <t>Teacher details are kept with the account</t>
+  </si>
+  <si>
+    <t>A Subject Teacher or Class Adviser account exists.</t>
+  </si>
+  <si>
+    <t>1. Open Accounts and edit a teacher's account.
+2. Change the first name or contact number and save.</t>
+  </si>
+  <si>
+    <t>e.g. subject.grade6a</t>
+  </si>
+  <si>
+    <t>The details are saved with the account and shown in the list. There is no separate Teacher Management page; /teachers opens Accounts.</t>
   </si>
   <si>
     <t>TC-017</t>
@@ -530,6 +623,9 @@
     <t>Only the section's own grade-level subjects are offered</t>
   </si>
   <si>
+    <t>Logged in as Admin.</t>
+  </si>
+  <si>
     <t>1. Open Add Assignment and choose a Grade 6 section.
 2. Look at the subject checklist.</t>
   </si>
@@ -1036,6 +1132,15 @@
   </si>
   <si>
     <t>D-03</t>
+  </si>
+  <si>
+    <t>Principal cannot change records</t>
+  </si>
+  <si>
+    <t>1. Look for Approve, Reject, Upload, Edit or Download SF10 buttons on Submission Review, Section Progress, Records &amp; SF10 and Analytics.</t>
+  </si>
+  <si>
+    <t>No action buttons are shown on these pages; the records are read-only. The Principal's only action is deciding on accounts in Account Approvals (TC-073, TC-074).</t>
   </si>
   <si>
     <t>TC-045</t>
@@ -1532,381 +1637,6 @@
   </si>
   <si>
     <t>The import is refused with a message that the SF10 belongs to LRN 100000000001. Nothing is saved.</t>
-  </si>
-  <si>
-    <t>Test Summary</t>
-  </si>
-  <si>
-    <t>Counts update from the Status column of the Test Cases sheet.</t>
-  </si>
-  <si>
-    <t>Overall</t>
-  </si>
-  <si>
-    <t>Total test cases</t>
-  </si>
-  <si>
-    <t>Fail</t>
-  </si>
-  <si>
-    <t>Blocked</t>
-  </si>
-  <si>
-    <t>Not Run (or blank)</t>
-  </si>
-  <si>
-    <t>Executed (Pass + Fail)</t>
-  </si>
-  <si>
-    <t>Pass rate of executed</t>
-  </si>
-  <si>
-    <t>Progress (executed or blocked)</t>
-  </si>
-  <si>
-    <t>Results by module</t>
-  </si>
-  <si>
-    <t>Total</t>
-  </si>
-  <si>
-    <t>Not Run</t>
-  </si>
-  <si>
-    <t>Pass rate</t>
-  </si>
-  <si>
-    <t>Results by ISO 25010 characteristic</t>
-  </si>
-  <si>
-    <t>Iso 25010 characteristic</t>
-  </si>
-  <si>
-    <t>Severity</t>
-  </si>
-  <si>
-    <t>Summary</t>
-  </si>
-  <si>
-    <t>Steps to Reproduce</t>
-  </si>
-  <si>
-    <t>Expected</t>
-  </si>
-  <si>
-    <t>Actual</t>
-  </si>
-  <si>
-    <t>Found By</t>
-  </si>
-  <si>
-    <t>Date Found</t>
-  </si>
-  <si>
-    <t>Fixed In (commit)</t>
-  </si>
-  <si>
-    <t>Retest Result</t>
-  </si>
-  <si>
-    <t>DEF-001</t>
-  </si>
-  <si>
-    <t>DEF-002</t>
-  </si>
-  <si>
-    <t>DEF-003</t>
-  </si>
-  <si>
-    <t>DEF-004</t>
-  </si>
-  <si>
-    <t>DEF-005</t>
-  </si>
-  <si>
-    <t>DEF-006</t>
-  </si>
-  <si>
-    <t>DEF-007</t>
-  </si>
-  <si>
-    <t>DEF-008</t>
-  </si>
-  <si>
-    <t>DEF-009</t>
-  </si>
-  <si>
-    <t>DEF-010</t>
-  </si>
-  <si>
-    <t>DEF-011</t>
-  </si>
-  <si>
-    <t>DEF-012</t>
-  </si>
-  <si>
-    <t>DEF-013</t>
-  </si>
-  <si>
-    <t>DEF-014</t>
-  </si>
-  <si>
-    <t>DEF-015</t>
-  </si>
-  <si>
-    <t>DEF-016</t>
-  </si>
-  <si>
-    <t>DEF-017</t>
-  </si>
-  <si>
-    <t>DEF-018</t>
-  </si>
-  <si>
-    <t>DEF-019</t>
-  </si>
-  <si>
-    <t>DEF-020</t>
-  </si>
-  <si>
-    <t>DEF-021</t>
-  </si>
-  <si>
-    <t>DEF-022</t>
-  </si>
-  <si>
-    <t>DEF-023</t>
-  </si>
-  <si>
-    <t>DEF-024</t>
-  </si>
-  <si>
-    <t>DEF-025</t>
-  </si>
-  <si>
-    <t>DEF-026</t>
-  </si>
-  <si>
-    <t>DEF-027</t>
-  </si>
-  <si>
-    <t>DEF-028</t>
-  </si>
-  <si>
-    <t>DEF-029</t>
-  </si>
-  <si>
-    <t>DEF-030</t>
-  </si>
-  <si>
-    <t>DEF-031</t>
-  </si>
-  <si>
-    <t>DEF-032</t>
-  </si>
-  <si>
-    <t>DEF-033</t>
-  </si>
-  <si>
-    <t>DEF-034</t>
-  </si>
-  <si>
-    <t>DEF-035</t>
-  </si>
-  <si>
-    <t>DEF-036</t>
-  </si>
-  <si>
-    <t>DEF-037</t>
-  </si>
-  <si>
-    <t>DEF-038</t>
-  </si>
-  <si>
-    <t>DEF-039</t>
-  </si>
-  <si>
-    <t>DEF-040</t>
-  </si>
-  <si>
-    <t>DEF-041</t>
-  </si>
-  <si>
-    <t>DEF-042</t>
-  </si>
-  <si>
-    <t>DEF-043</t>
-  </si>
-  <si>
-    <t>DEF-044</t>
-  </si>
-  <si>
-    <t>DEF-045</t>
-  </si>
-  <si>
-    <t>DEF-046</t>
-  </si>
-  <si>
-    <t>DEF-047</t>
-  </si>
-  <si>
-    <t>DEF-048</t>
-  </si>
-  <si>
-    <t>DEF-049</t>
-  </si>
-  <si>
-    <t>DEF-050</t>
-  </si>
-  <si>
-    <t>DEF-051</t>
-  </si>
-  <si>
-    <t>DEF-052</t>
-  </si>
-  <si>
-    <t>DEF-053</t>
-  </si>
-  <si>
-    <t>DEF-054</t>
-  </si>
-  <si>
-    <t>DEF-055</t>
-  </si>
-  <si>
-    <t>DEF-056</t>
-  </si>
-  <si>
-    <t>DEF-057</t>
-  </si>
-  <si>
-    <t>DEF-058</t>
-  </si>
-  <si>
-    <t>DEF-059</t>
-  </si>
-  <si>
-    <t>DEF-060</t>
-  </si>
-  <si>
-    <t>Severity guide</t>
-  </si>
-  <si>
-    <t>Critical</t>
-  </si>
-  <si>
-    <t>Wrong grades saved or shown, data lost, or a user sees/changes data they should not.</t>
-  </si>
-  <si>
-    <t>High</t>
-  </si>
-  <si>
-    <t>A main task (upload, submit, approve, SF10) cannot be completed.</t>
-  </si>
-  <si>
-    <t>Medium</t>
-  </si>
-  <si>
-    <t>A task works but with a wrong message, wrong count or a workaround.</t>
-  </si>
-  <si>
-    <t>Low</t>
-  </si>
-  <si>
-    <t>Cosmetic: layout, wording, alignment.</t>
-  </si>
-  <si>
-    <t>Admin has set a test account to Inactive in Accounts.</t>
-  </si>
-  <si>
-    <t>1. Type /accounts in the address bar.
-2. Type /audit-log.
-3. Type /consolidated-records.</t>
-  </si>
-  <si>
-    <t>Accounts</t>
-  </si>
-  <si>
-    <t>§6.2, US-015</t>
-  </si>
-  <si>
-    <t>Create an account (waits for the Principal)</t>
-  </si>
-  <si>
-    <t>Logged in as Admin. A Principal account is Active.</t>
-  </si>
-  <si>
-    <t>1. Open Accounts and click Add Account.
-2. Enter a DepEd email, the role, and (for a teacher) the name. The username is suggested from the email.
-3. Click Create Account.
-4. Log out and try to log in as the new account.</t>
-  </si>
-  <si>
-    <t>New test account, e.g. test.teacher@deped.gov.ph</t>
-  </si>
-  <si>
-    <t>The account is listed as Pending Approval and the Principal is notified. It cannot log in until the Principal approves it (TC-073) and the Admin finishes its setup (TC-075).</t>
-  </si>
-  <si>
-    <t>Edit an account and deactivate it</t>
-  </si>
-  <si>
-    <t>An Active test account exists (after TC-075).</t>
-  </si>
-  <si>
-    <t>1. Edit the account and change the email (must end in @deped.gov.ph) or the name.
-2. Set Status to Inactive and save.</t>
-  </si>
-  <si>
-    <t>Test account</t>
-  </si>
-  <si>
-    <t>Changes are saved and shown in the list. The inactive account can no longer log in (TC-004).</t>
-  </si>
-  <si>
-    <t>1. Edit the account, type a new password in Reset Password (or generate one) and save.
-2. Log in as that user with the old password, then with the new one.</t>
-  </si>
-  <si>
-    <t>The old password stops working. The new one works and must be replaced at sign-in, like a temporary password. With internet, it is also emailed to the DepEd address (L-02).</t>
-  </si>
-  <si>
-    <t>Search accounts</t>
-  </si>
-  <si>
-    <t>Several accounts exist.</t>
-  </si>
-  <si>
-    <t>1. Open Accounts.
-2. Type part of a name, username, email or role in the search box.</t>
-  </si>
-  <si>
-    <t>Only matching accounts are listed.</t>
-  </si>
-  <si>
-    <t>Teacher details are kept with the account</t>
-  </si>
-  <si>
-    <t>A Subject Teacher or Class Adviser account exists.</t>
-  </si>
-  <si>
-    <t>1. Open Accounts and edit a teacher's account.
-2. Change the first name or contact number and save.</t>
-  </si>
-  <si>
-    <t>e.g. subject.grade6a</t>
-  </si>
-  <si>
-    <t>The details are saved with the account and shown in the list. There is no separate Teacher Management page; /teachers opens Accounts.</t>
-  </si>
-  <si>
-    <t>Principal cannot change records</t>
-  </si>
-  <si>
-    <t>1. Look for Approve, Reject, Upload, Edit or Download SF10 buttons on Submission Review, Section Progress, Records &amp; SF10 and Analytics.</t>
-  </si>
-  <si>
-    <t>No action buttons are shown on these pages; the records are read-only. The Principal's only action is deciding on accounts in Account Approvals (TC-073, TC-074).</t>
   </si>
   <si>
     <t>TC-072</t>
@@ -2015,16 +1745,386 @@
     <t>Step 1 opens "Set your own password" and step 2 returns to it. Step 3 is refused (passwords do not match). Step 4 opens the Dashboard. In step 5 the temporary password is refused and the new one works.</t>
   </si>
   <si>
-    <t>Formal testing and UAT, ISO/IEC 25010. Read 03-Testing/EduCheck_Known_Limitations.md first: items listed there are not defects. Revised 2026-10-19 for the Accounts page and Principal account approval (TC-012 to TC-016, TC-044, TC-072 to TC-076); the UAT on 2026-10-16 used the earlier User Management and Teacher Management pages.</t>
-  </si>
-  <si>
-    <t>Reviews and approves records; adds accounts in Accounts and finishes their setup after the Principal approves them.</t>
-  </si>
-  <si>
-    <t>Approves or rejects new accounts in Account Approvals; everything else is view-only.</t>
-  </si>
-  <si>
-    <t>Back up the database so testing can be repeated from the same state. After restoring a backup taken before 2026-10-17, re-run migrations 010 and 011 (see the Day Kit).</t>
+    <t>Test Summary</t>
+  </si>
+  <si>
+    <t>Counts update from the Status column of the Test Cases sheet.</t>
+  </si>
+  <si>
+    <t>Overall</t>
+  </si>
+  <si>
+    <t>Total test cases</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>Blocked</t>
+  </si>
+  <si>
+    <t>Not Run (or blank)</t>
+  </si>
+  <si>
+    <t>Executed (Pass + Fail)</t>
+  </si>
+  <si>
+    <t>Pass rate of executed</t>
+  </si>
+  <si>
+    <t>Progress (executed or blocked)</t>
+  </si>
+  <si>
+    <t>Results by module</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Not Run</t>
+  </si>
+  <si>
+    <t>Pass rate</t>
+  </si>
+  <si>
+    <t>Results by ISO 25010 characteristic</t>
+  </si>
+  <si>
+    <t>Iso 25010 characteristic</t>
+  </si>
+  <si>
+    <t>Severity</t>
+  </si>
+  <si>
+    <t>Summary</t>
+  </si>
+  <si>
+    <t>Steps to Reproduce</t>
+  </si>
+  <si>
+    <t>Expected</t>
+  </si>
+  <si>
+    <t>Actual</t>
+  </si>
+  <si>
+    <t>Found By</t>
+  </si>
+  <si>
+    <t>Date Found</t>
+  </si>
+  <si>
+    <t>Fixed In (commit)</t>
+  </si>
+  <si>
+    <t>Retest Result</t>
+  </si>
+  <si>
+    <t>DEF-001</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>Deleting a section or account appears to do nothing; only "Failed to delete" is shown.</t>
+  </si>
+  <si>
+    <t>1. Sign in as Administrator.
+2. Open Section &amp; Teacher Assignments (or Accounts).
+3. Click Delete on a section that has class records or learners (or an account that has records).</t>
+  </si>
+  <si>
+    <t>Either the item is deleted, or the reason it cannot be deleted is shown before trying.</t>
+  </si>
+  <si>
+    <t>A generic "Failed to delete" message appears. The database keeps the section or account because other records still point to it, but the screen does not say so.</t>
+  </si>
+  <si>
+    <t>Project team</t>
+  </si>
+  <si>
+    <t>Fixed</t>
+  </si>
+  <si>
+    <t>797b022</t>
+  </si>
+  <si>
+    <t>Delete is now greyed out when records exist and explains why; accounts point to setting the status to Inactive. The API returns the reason (409). Awaiting retest.</t>
+  </si>
+  <si>
+    <t>DEF-002</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>Upload page does not show which subjects are already uploaded, so teachers lose track of the next subject.</t>
+  </si>
+  <si>
+    <t>1. Sign in as a Subject Teacher or Adviser with several subjects.
+2. Upload one subject's e-Class Record.
+3. Return to the upload page.</t>
+  </si>
+  <si>
+    <t>Each subject shows whether it is uploaded and validated, and the next subject to upload is easy to find.</t>
+  </si>
+  <si>
+    <t>Every subject tile only shows "Last uploaded &lt;date&gt;", with no status and no indication of which subject comes next.</t>
+  </si>
+  <si>
+    <t>09cc7fa</t>
+  </si>
+  <si>
+    <t>Each tile now shows Validated / Needs fixes / Not uploaded yet, with an "X of N uploaded" count; the next subject not yet uploaded is preselected. Tiles stay selectable for re-uploads. Awaiting retest.</t>
+  </si>
+  <si>
+    <t>DEF-003</t>
+  </si>
+  <si>
+    <t>Pages load slowly on the hosted (Render) link.</t>
+  </si>
+  <si>
+    <t>1. Leave the hosted site unused for more than 15 minutes.
+2. Open the Render link and sign in.</t>
+  </si>
+  <si>
+    <t>Sign-in and pages load in a few seconds.</t>
+  </si>
+  <si>
+    <t>The first request after a quiet period takes up to about a minute; the page looks stuck.</t>
+  </si>
+  <si>
+    <t>In Progress</t>
+  </si>
+  <si>
+    <t>Cause: the Render free plan puts the server to sleep when idle (local API responses measured at 3-20 ms). Sign-in now explains that the server is starting up. Remaining fix is hosting: keep-alive ping (e.g. UptimeRobot every 5 min) or a paid instance.</t>
+  </si>
+  <si>
+    <t>DEF-004</t>
+  </si>
+  <si>
+    <t>No help or support information inside the system.</t>
+  </si>
+  <si>
+    <t>1. Sign in as any role.
+2. Look for help, FAQ or who to contact.</t>
+  </si>
+  <si>
+    <t>Users can find answers to common questions and know who to contact.</t>
+  </si>
+  <si>
+    <t>There is no help page; users have to ask the team.</t>
+  </si>
+  <si>
+    <t>Added Help &amp; Support (sidebar) with role-specific FAQ and search, pointing to the School Administrator; the User's Manual download appears once the PDF is published. Enhancement raised during testing. Awaiting retest.</t>
+  </si>
+  <si>
+    <t>DEF-005</t>
+  </si>
+  <si>
+    <t>Submission Review does not show each learner's section, and has no section filter.</t>
+  </si>
+  <si>
+    <t>1. Sign in as Administrator or Principal.
+2. Open Submission Review with more than one section in the school year.</t>
+  </si>
+  <si>
+    <t>Each learner's section is visible, and the list can be narrowed to one section.</t>
+  </si>
+  <si>
+    <t>Learners of every section are mixed in one list showing only the grade level; a section filter is only reachable from Section Progress.</t>
+  </si>
+  <si>
+    <t>6af7357</t>
+  </si>
+  <si>
+    <t>Rows now show Grade and Section, and a Section picker sits beside the School Year. Awaiting retest.</t>
+  </si>
+  <si>
+    <t>DEF-006</t>
+  </si>
+  <si>
+    <t>DEF-007</t>
+  </si>
+  <si>
+    <t>DEF-008</t>
+  </si>
+  <si>
+    <t>DEF-009</t>
+  </si>
+  <si>
+    <t>DEF-010</t>
+  </si>
+  <si>
+    <t>DEF-011</t>
+  </si>
+  <si>
+    <t>DEF-012</t>
+  </si>
+  <si>
+    <t>DEF-013</t>
+  </si>
+  <si>
+    <t>DEF-014</t>
+  </si>
+  <si>
+    <t>DEF-015</t>
+  </si>
+  <si>
+    <t>DEF-016</t>
+  </si>
+  <si>
+    <t>DEF-017</t>
+  </si>
+  <si>
+    <t>DEF-018</t>
+  </si>
+  <si>
+    <t>DEF-019</t>
+  </si>
+  <si>
+    <t>DEF-020</t>
+  </si>
+  <si>
+    <t>DEF-021</t>
+  </si>
+  <si>
+    <t>DEF-022</t>
+  </si>
+  <si>
+    <t>DEF-023</t>
+  </si>
+  <si>
+    <t>DEF-024</t>
+  </si>
+  <si>
+    <t>DEF-025</t>
+  </si>
+  <si>
+    <t>DEF-026</t>
+  </si>
+  <si>
+    <t>DEF-027</t>
+  </si>
+  <si>
+    <t>DEF-028</t>
+  </si>
+  <si>
+    <t>DEF-029</t>
+  </si>
+  <si>
+    <t>DEF-030</t>
+  </si>
+  <si>
+    <t>DEF-031</t>
+  </si>
+  <si>
+    <t>DEF-032</t>
+  </si>
+  <si>
+    <t>DEF-033</t>
+  </si>
+  <si>
+    <t>DEF-034</t>
+  </si>
+  <si>
+    <t>DEF-035</t>
+  </si>
+  <si>
+    <t>DEF-036</t>
+  </si>
+  <si>
+    <t>DEF-037</t>
+  </si>
+  <si>
+    <t>DEF-038</t>
+  </si>
+  <si>
+    <t>DEF-039</t>
+  </si>
+  <si>
+    <t>DEF-040</t>
+  </si>
+  <si>
+    <t>DEF-041</t>
+  </si>
+  <si>
+    <t>DEF-042</t>
+  </si>
+  <si>
+    <t>DEF-043</t>
+  </si>
+  <si>
+    <t>DEF-044</t>
+  </si>
+  <si>
+    <t>DEF-045</t>
+  </si>
+  <si>
+    <t>DEF-046</t>
+  </si>
+  <si>
+    <t>DEF-047</t>
+  </si>
+  <si>
+    <t>DEF-048</t>
+  </si>
+  <si>
+    <t>DEF-049</t>
+  </si>
+  <si>
+    <t>DEF-050</t>
+  </si>
+  <si>
+    <t>DEF-051</t>
+  </si>
+  <si>
+    <t>DEF-052</t>
+  </si>
+  <si>
+    <t>DEF-053</t>
+  </si>
+  <si>
+    <t>DEF-054</t>
+  </si>
+  <si>
+    <t>DEF-055</t>
+  </si>
+  <si>
+    <t>DEF-056</t>
+  </si>
+  <si>
+    <t>DEF-057</t>
+  </si>
+  <si>
+    <t>DEF-058</t>
+  </si>
+  <si>
+    <t>DEF-059</t>
+  </si>
+  <si>
+    <t>DEF-060</t>
+  </si>
+  <si>
+    <t>Severity guide</t>
+  </si>
+  <si>
+    <t>Critical</t>
+  </si>
+  <si>
+    <t>Wrong grades saved or shown, data lost, or a user sees/changes data they should not.</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>A main task (upload, submit, approve, SF10) cannot be completed.</t>
+  </si>
+  <si>
+    <t>A task works but with a wrong message, wrong count or a workaround.</t>
+  </si>
+  <si>
+    <t>Cosmetic: layout, wording, alignment.</t>
   </si>
 </sst>
 </file>
@@ -2537,12 +2637,12 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>632</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -2550,43 +2650,43 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B5" s="6"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B6" s="6"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B7" s="6"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B8" s="6"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B9" s="6"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B10" s="6"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
@@ -2594,67 +2694,67 @@
     </row>
     <row r="13" spans="1:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B13" s="24" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" s="25"/>
       <c r="D13" s="25"/>
     </row>
     <row r="14" spans="1:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C14" s="25"/>
       <c r="D14" s="25"/>
     </row>
     <row r="15" spans="1:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B15" s="24" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C15" s="25"/>
       <c r="D15" s="25"/>
     </row>
     <row r="16" spans="1:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B16" s="24" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C16" s="25"/>
       <c r="D16" s="25"/>
     </row>
     <row r="17" spans="1:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B17" s="24" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C17" s="25"/>
       <c r="D17" s="25"/>
     </row>
     <row r="18" spans="1:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B18" s="24" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C18" s="25"/>
       <c r="D18" s="25"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
@@ -2662,71 +2762,71 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
@@ -2734,69 +2834,69 @@
     </row>
     <row r="31" spans="1:4" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" ht="39.6" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="13" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" ht="39.6" x14ac:dyDescent="0.3">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="12" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C33" s="6"/>
       <c r="D33" s="13" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" ht="39.6" x14ac:dyDescent="0.3">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="12" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="13" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" ht="26.4" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="12" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C35" s="6"/>
       <c r="D35" s="13" t="s">
-        <v>634</v>
+        <v>55</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
@@ -2804,40 +2904,40 @@
     </row>
     <row r="38" spans="1:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B38" s="24" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C38" s="25"/>
       <c r="D38" s="25"/>
     </row>
     <row r="39" spans="1:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B39" s="24" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C39" s="25"/>
       <c r="D39" s="25"/>
     </row>
     <row r="40" spans="1:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B40" s="24" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C40" s="25"/>
       <c r="D40" s="25"/>
     </row>
     <row r="41" spans="1:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B41" s="24" t="s">
-        <v>635</v>
+        <v>64</v>
       </c>
       <c r="C41" s="25"/>
       <c r="D41" s="25"/>
@@ -2888,90 +2988,90 @@
   <sheetData>
     <row r="1" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="I1" s="11" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="J1" s="11" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="K1" s="11" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="L1" s="11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M1" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N1" s="11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O1" s="11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="P1" s="11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q1" s="11" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" ht="39.6" x14ac:dyDescent="0.3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="14" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H2" s="13" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="I2" s="13" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J2" s="13" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="K2" s="13" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="L2" s="16"/>
       <c r="M2" s="17"/>
@@ -2980,39 +3080,39 @@
       <c r="P2" s="17"/>
       <c r="Q2" s="16"/>
     </row>
-    <row r="3" spans="1:17" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="G3" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="H3" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="H3" s="13" t="s">
-        <v>77</v>
-      </c>
       <c r="I3" s="13" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="J3" s="13" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="K3" s="13" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="L3" s="16"/>
       <c r="M3" s="17"/>
@@ -3021,39 +3121,39 @@
       <c r="P3" s="17"/>
       <c r="Q3" s="16"/>
     </row>
-    <row r="4" spans="1:17" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="14" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="H4" s="13" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="J4" s="13" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="K4" s="13" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="L4" s="16"/>
       <c r="M4" s="17"/>
@@ -3062,39 +3162,39 @@
       <c r="P4" s="17"/>
       <c r="Q4" s="16"/>
     </row>
-    <row r="5" spans="1:17" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="14" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="H5" s="13" t="s">
-        <v>573</v>
+        <v>99</v>
       </c>
       <c r="I5" s="13" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="J5" s="13" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="K5" s="13" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="L5" s="16"/>
       <c r="M5" s="17"/>
@@ -3103,39 +3203,39 @@
       <c r="P5" s="17"/>
       <c r="Q5" s="16"/>
     </row>
-    <row r="6" spans="1:17" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="14" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="H6" s="13" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="I6" s="13" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="J6" s="13" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="K6" s="13" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="L6" s="16"/>
       <c r="M6" s="17"/>
@@ -3144,39 +3244,39 @@
       <c r="P6" s="17"/>
       <c r="Q6" s="16"/>
     </row>
-    <row r="7" spans="1:17" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="14" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="H7" s="13" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="I7" s="13" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="J7" s="13" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="K7" s="13" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="L7" s="16"/>
       <c r="M7" s="17"/>
@@ -3185,39 +3285,39 @@
       <c r="P7" s="17"/>
       <c r="Q7" s="16"/>
     </row>
-    <row r="8" spans="1:17" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="14" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="H8" s="13" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>574</v>
+        <v>119</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="L8" s="16"/>
       <c r="M8" s="17"/>
@@ -3226,39 +3326,39 @@
       <c r="P8" s="17"/>
       <c r="Q8" s="16"/>
     </row>
-    <row r="9" spans="1:17" ht="66" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" ht="66" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="14" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="K9" s="13" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="L9" s="16"/>
       <c r="M9" s="17"/>
@@ -3267,39 +3367,39 @@
       <c r="P9" s="17"/>
       <c r="Q9" s="16"/>
     </row>
-    <row r="10" spans="1:17" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" ht="79.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="14" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="K10" s="13" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="L10" s="16"/>
       <c r="M10" s="17"/>
@@ -3308,39 +3408,39 @@
       <c r="P10" s="17"/>
       <c r="Q10" s="16"/>
     </row>
-    <row r="11" spans="1:17" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="14" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K11" s="13" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="L11" s="16"/>
       <c r="M11" s="17"/>
@@ -3349,39 +3449,39 @@
       <c r="P11" s="17"/>
       <c r="Q11" s="16"/>
     </row>
-    <row r="12" spans="1:17" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="14" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="L12" s="16"/>
       <c r="M12" s="17"/>
@@ -3390,39 +3490,39 @@
       <c r="P12" s="17"/>
       <c r="Q12" s="16"/>
     </row>
-    <row r="13" spans="1:17" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" ht="79.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="14" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>575</v>
+        <v>145</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>576</v>
+        <v>146</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>577</v>
+        <v>147</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>578</v>
+        <v>148</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>579</v>
+        <v>149</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>580</v>
+        <v>150</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>581</v>
+        <v>151</v>
       </c>
       <c r="L13" s="16"/>
       <c r="M13" s="17"/>
@@ -3431,39 +3531,39 @@
       <c r="P13" s="17"/>
       <c r="Q13" s="16"/>
     </row>
-    <row r="14" spans="1:17" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="14" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>575</v>
+        <v>145</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="G14" s="13" t="s">
-        <v>582</v>
+        <v>153</v>
       </c>
       <c r="H14" s="13" t="s">
-        <v>583</v>
+        <v>154</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>584</v>
+        <v>155</v>
       </c>
       <c r="J14" s="13" t="s">
-        <v>585</v>
+        <v>156</v>
       </c>
       <c r="K14" s="13" t="s">
-        <v>586</v>
+        <v>157</v>
       </c>
       <c r="L14" s="16"/>
       <c r="M14" s="17"/>
@@ -3472,39 +3572,39 @@
       <c r="P14" s="17"/>
       <c r="Q14" s="16"/>
     </row>
-    <row r="15" spans="1:17" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="14" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>575</v>
+        <v>145</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="G15" s="13" t="s">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="H15" s="13" t="s">
-        <v>141</v>
+        <v>161</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>587</v>
+        <v>162</v>
       </c>
       <c r="J15" s="13" t="s">
-        <v>585</v>
+        <v>156</v>
       </c>
       <c r="K15" s="13" t="s">
-        <v>588</v>
+        <v>163</v>
       </c>
       <c r="L15" s="16"/>
       <c r="M15" s="17"/>
@@ -3513,39 +3613,39 @@
       <c r="P15" s="17"/>
       <c r="Q15" s="16"/>
     </row>
-    <row r="16" spans="1:17" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="B16" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="B16" s="13" t="s">
-        <v>575</v>
-      </c>
       <c r="C16" s="15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="G16" s="13" t="s">
-        <v>589</v>
+        <v>165</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>590</v>
+        <v>166</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>591</v>
+        <v>167</v>
       </c>
       <c r="J16" s="13" t="s">
-        <v>146</v>
+        <v>168</v>
       </c>
       <c r="K16" s="13" t="s">
-        <v>592</v>
+        <v>169</v>
       </c>
       <c r="L16" s="16"/>
       <c r="M16" s="17"/>
@@ -3554,39 +3654,39 @@
       <c r="P16" s="17"/>
       <c r="Q16" s="16"/>
     </row>
-    <row r="17" spans="1:17" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="14" t="s">
-        <v>147</v>
+        <v>170</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>575</v>
+        <v>145</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="G17" s="13" t="s">
-        <v>593</v>
+        <v>171</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>594</v>
+        <v>172</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>595</v>
+        <v>173</v>
       </c>
       <c r="J17" s="13" t="s">
-        <v>596</v>
+        <v>174</v>
       </c>
       <c r="K17" s="13" t="s">
-        <v>597</v>
+        <v>175</v>
       </c>
       <c r="L17" s="16"/>
       <c r="M17" s="17"/>
@@ -3595,39 +3695,39 @@
       <c r="P17" s="17"/>
       <c r="Q17" s="16"/>
     </row>
-    <row r="18" spans="1:17" ht="66" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" ht="66" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="14" t="s">
-        <v>148</v>
+        <v>176</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>149</v>
+        <v>177</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="F18" s="13" t="s">
-        <v>150</v>
+        <v>178</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>151</v>
+        <v>179</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>152</v>
+        <v>180</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>153</v>
+        <v>181</v>
       </c>
       <c r="J18" s="13" t="s">
-        <v>154</v>
+        <v>182</v>
       </c>
       <c r="K18" s="13" t="s">
-        <v>155</v>
+        <v>183</v>
       </c>
       <c r="L18" s="16"/>
       <c r="M18" s="17"/>
@@ -3636,39 +3736,39 @@
       <c r="P18" s="17"/>
       <c r="Q18" s="16"/>
     </row>
-    <row r="19" spans="1:17" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="14" t="s">
-        <v>156</v>
+        <v>184</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>149</v>
+        <v>177</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="F19" s="13" t="s">
-        <v>150</v>
+        <v>178</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>157</v>
+        <v>185</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>139</v>
+        <v>186</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="J19" s="13" t="s">
-        <v>159</v>
+        <v>188</v>
       </c>
       <c r="K19" s="13" t="s">
-        <v>160</v>
+        <v>189</v>
       </c>
       <c r="L19" s="16"/>
       <c r="M19" s="17"/>
@@ -3677,39 +3777,39 @@
       <c r="P19" s="17"/>
       <c r="Q19" s="16"/>
     </row>
-    <row r="20" spans="1:17" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:17" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="14" t="s">
-        <v>161</v>
+        <v>190</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>149</v>
+        <v>177</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F20" s="13" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>162</v>
+        <v>191</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>163</v>
+        <v>192</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>164</v>
+        <v>193</v>
       </c>
       <c r="J20" s="13" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="K20" s="13" t="s">
-        <v>165</v>
+        <v>194</v>
       </c>
       <c r="L20" s="16"/>
       <c r="M20" s="17"/>
@@ -3718,39 +3818,39 @@
       <c r="P20" s="17"/>
       <c r="Q20" s="16"/>
     </row>
-    <row r="21" spans="1:17" ht="66" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:17" ht="66" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="14" t="s">
-        <v>166</v>
+        <v>195</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>149</v>
+        <v>177</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>167</v>
+        <v>196</v>
       </c>
       <c r="H21" s="13" t="s">
-        <v>168</v>
+        <v>197</v>
       </c>
       <c r="I21" s="13" t="s">
-        <v>169</v>
+        <v>198</v>
       </c>
       <c r="J21" s="13" t="s">
-        <v>170</v>
+        <v>199</v>
       </c>
       <c r="K21" s="13" t="s">
-        <v>171</v>
+        <v>200</v>
       </c>
       <c r="L21" s="16"/>
       <c r="M21" s="17"/>
@@ -3759,39 +3859,39 @@
       <c r="P21" s="17"/>
       <c r="Q21" s="16"/>
     </row>
-    <row r="22" spans="1:17" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:17" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="14" t="s">
-        <v>172</v>
+        <v>201</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>173</v>
+        <v>202</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>174</v>
+        <v>203</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>175</v>
+        <v>204</v>
       </c>
       <c r="H22" s="13" t="s">
-        <v>176</v>
+        <v>205</v>
       </c>
       <c r="I22" s="13" t="s">
-        <v>177</v>
+        <v>206</v>
       </c>
       <c r="J22" s="13" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="K22" s="13" t="s">
-        <v>178</v>
+        <v>207</v>
       </c>
       <c r="L22" s="16"/>
       <c r="M22" s="17"/>
@@ -3800,39 +3900,39 @@
       <c r="P22" s="17"/>
       <c r="Q22" s="16"/>
     </row>
-    <row r="23" spans="1:17" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:17" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="14" t="s">
-        <v>179</v>
+        <v>208</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>180</v>
+        <v>209</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="F23" s="13" t="s">
-        <v>181</v>
+        <v>210</v>
       </c>
       <c r="G23" s="13" t="s">
-        <v>182</v>
+        <v>211</v>
       </c>
       <c r="H23" s="13" t="s">
-        <v>183</v>
+        <v>212</v>
       </c>
       <c r="I23" s="13" t="s">
-        <v>184</v>
+        <v>213</v>
       </c>
       <c r="J23" s="13" t="s">
-        <v>185</v>
+        <v>214</v>
       </c>
       <c r="K23" s="13" t="s">
-        <v>186</v>
+        <v>215</v>
       </c>
       <c r="L23" s="16"/>
       <c r="M23" s="17"/>
@@ -3841,39 +3941,39 @@
       <c r="P23" s="17"/>
       <c r="Q23" s="16"/>
     </row>
-    <row r="24" spans="1:17" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:17" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="14" t="s">
-        <v>187</v>
+        <v>216</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>180</v>
+        <v>209</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="F24" s="13" t="s">
-        <v>181</v>
+        <v>210</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>188</v>
+        <v>217</v>
       </c>
       <c r="H24" s="13" t="s">
-        <v>189</v>
+        <v>218</v>
       </c>
       <c r="I24" s="13" t="s">
-        <v>190</v>
+        <v>219</v>
       </c>
       <c r="J24" s="13" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="K24" s="13" t="s">
-        <v>191</v>
+        <v>220</v>
       </c>
       <c r="L24" s="16"/>
       <c r="M24" s="17"/>
@@ -3882,39 +3982,39 @@
       <c r="P24" s="17"/>
       <c r="Q24" s="16"/>
     </row>
-    <row r="25" spans="1:17" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:17" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="14" t="s">
-        <v>192</v>
+        <v>221</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>180</v>
+        <v>209</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F25" s="13" t="s">
-        <v>193</v>
+        <v>222</v>
       </c>
       <c r="G25" s="13" t="s">
-        <v>194</v>
+        <v>223</v>
       </c>
       <c r="H25" s="13" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="I25" s="13" t="s">
-        <v>195</v>
+        <v>224</v>
       </c>
       <c r="J25" s="13" t="s">
-        <v>196</v>
+        <v>225</v>
       </c>
       <c r="K25" s="13" t="s">
-        <v>197</v>
+        <v>226</v>
       </c>
       <c r="L25" s="16"/>
       <c r="M25" s="17"/>
@@ -3923,39 +4023,39 @@
       <c r="P25" s="17"/>
       <c r="Q25" s="16"/>
     </row>
-    <row r="26" spans="1:17" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:17" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="14" t="s">
-        <v>198</v>
+        <v>227</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>180</v>
+        <v>209</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F26" s="13" t="s">
-        <v>199</v>
+        <v>228</v>
       </c>
       <c r="G26" s="13" t="s">
-        <v>200</v>
+        <v>229</v>
       </c>
       <c r="H26" s="13" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="I26" s="13" t="s">
-        <v>201</v>
+        <v>230</v>
       </c>
       <c r="J26" s="13" t="s">
-        <v>202</v>
+        <v>231</v>
       </c>
       <c r="K26" s="13" t="s">
-        <v>203</v>
+        <v>232</v>
       </c>
       <c r="L26" s="16"/>
       <c r="M26" s="17"/>
@@ -3964,39 +4064,39 @@
       <c r="P26" s="17"/>
       <c r="Q26" s="16"/>
     </row>
-    <row r="27" spans="1:17" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:17" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="14" t="s">
-        <v>204</v>
+        <v>233</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>180</v>
+        <v>209</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="F27" s="13" t="s">
-        <v>205</v>
+        <v>234</v>
       </c>
       <c r="G27" s="13" t="s">
-        <v>206</v>
+        <v>235</v>
       </c>
       <c r="H27" s="13" t="s">
-        <v>207</v>
+        <v>236</v>
       </c>
       <c r="I27" s="13" t="s">
-        <v>208</v>
+        <v>237</v>
       </c>
       <c r="J27" s="13" t="s">
-        <v>209</v>
+        <v>238</v>
       </c>
       <c r="K27" s="13" t="s">
-        <v>210</v>
+        <v>239</v>
       </c>
       <c r="L27" s="16"/>
       <c r="M27" s="17"/>
@@ -4005,39 +4105,39 @@
       <c r="P27" s="17"/>
       <c r="Q27" s="16"/>
     </row>
-    <row r="28" spans="1:17" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:17" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="14" t="s">
-        <v>211</v>
+        <v>240</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>212</v>
+        <v>241</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="F28" s="13" t="s">
-        <v>213</v>
+        <v>242</v>
       </c>
       <c r="G28" s="13" t="s">
-        <v>214</v>
+        <v>243</v>
       </c>
       <c r="H28" s="13" t="s">
-        <v>215</v>
+        <v>244</v>
       </c>
       <c r="I28" s="13" t="s">
-        <v>216</v>
+        <v>245</v>
       </c>
       <c r="J28" s="13" t="s">
-        <v>217</v>
+        <v>246</v>
       </c>
       <c r="K28" s="13" t="s">
-        <v>218</v>
+        <v>247</v>
       </c>
       <c r="L28" s="16"/>
       <c r="M28" s="17"/>
@@ -4046,39 +4146,39 @@
       <c r="P28" s="17"/>
       <c r="Q28" s="16"/>
     </row>
-    <row r="29" spans="1:17" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:17" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="14" t="s">
-        <v>219</v>
+        <v>248</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>212</v>
+        <v>241</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="F29" s="13" t="s">
-        <v>220</v>
+        <v>249</v>
       </c>
       <c r="G29" s="13" t="s">
-        <v>221</v>
+        <v>250</v>
       </c>
       <c r="H29" s="13" t="s">
-        <v>222</v>
+        <v>251</v>
       </c>
       <c r="I29" s="13" t="s">
-        <v>223</v>
+        <v>252</v>
       </c>
       <c r="J29" s="13" t="s">
-        <v>224</v>
+        <v>253</v>
       </c>
       <c r="K29" s="13" t="s">
-        <v>225</v>
+        <v>254</v>
       </c>
       <c r="L29" s="16"/>
       <c r="M29" s="17"/>
@@ -4087,39 +4187,39 @@
       <c r="P29" s="17"/>
       <c r="Q29" s="16"/>
     </row>
-    <row r="30" spans="1:17" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:17" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="14" t="s">
-        <v>226</v>
+        <v>255</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>212</v>
+        <v>241</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="F30" s="13" t="s">
-        <v>227</v>
+        <v>256</v>
       </c>
       <c r="G30" s="13" t="s">
-        <v>228</v>
+        <v>257</v>
       </c>
       <c r="H30" s="13" t="s">
-        <v>139</v>
+        <v>186</v>
       </c>
       <c r="I30" s="13" t="s">
-        <v>229</v>
+        <v>258</v>
       </c>
       <c r="J30" s="13" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="K30" s="13" t="s">
-        <v>230</v>
+        <v>259</v>
       </c>
       <c r="L30" s="16"/>
       <c r="M30" s="17"/>
@@ -4128,39 +4228,39 @@
       <c r="P30" s="17"/>
       <c r="Q30" s="16"/>
     </row>
-    <row r="31" spans="1:17" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:17" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="14" t="s">
-        <v>231</v>
+        <v>260</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>180</v>
+        <v>209</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="F31" s="13" t="s">
-        <v>232</v>
+        <v>261</v>
       </c>
       <c r="G31" s="13" t="s">
-        <v>233</v>
+        <v>262</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>234</v>
+        <v>263</v>
       </c>
       <c r="I31" s="13" t="s">
-        <v>235</v>
+        <v>264</v>
       </c>
       <c r="J31" s="13" t="s">
-        <v>236</v>
+        <v>265</v>
       </c>
       <c r="K31" s="13" t="s">
-        <v>237</v>
+        <v>266</v>
       </c>
       <c r="L31" s="16"/>
       <c r="M31" s="17"/>
@@ -4169,39 +4269,39 @@
       <c r="P31" s="17"/>
       <c r="Q31" s="16"/>
     </row>
-    <row r="32" spans="1:17" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:17" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="14" t="s">
-        <v>238</v>
+        <v>267</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>239</v>
+        <v>268</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="F32" s="13" t="s">
-        <v>240</v>
+        <v>269</v>
       </c>
       <c r="G32" s="13" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="H32" s="13" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="I32" s="13" t="s">
-        <v>243</v>
+        <v>272</v>
       </c>
       <c r="J32" s="13" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K32" s="13" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="L32" s="16"/>
       <c r="M32" s="17"/>
@@ -4210,39 +4310,39 @@
       <c r="P32" s="17"/>
       <c r="Q32" s="16"/>
     </row>
-    <row r="33" spans="1:17" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:17" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="14" t="s">
-        <v>245</v>
+        <v>274</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>239</v>
+        <v>268</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F33" s="13" t="s">
-        <v>246</v>
+        <v>275</v>
       </c>
       <c r="G33" s="13" t="s">
-        <v>247</v>
+        <v>276</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>248</v>
+        <v>277</v>
       </c>
       <c r="I33" s="13" t="s">
-        <v>249</v>
+        <v>278</v>
       </c>
       <c r="J33" s="13" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="K33" s="13" t="s">
-        <v>250</v>
+        <v>279</v>
       </c>
       <c r="L33" s="16"/>
       <c r="M33" s="17"/>
@@ -4251,39 +4351,39 @@
       <c r="P33" s="17"/>
       <c r="Q33" s="16"/>
     </row>
-    <row r="34" spans="1:17" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:17" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="14" t="s">
-        <v>251</v>
+        <v>280</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>239</v>
+        <v>268</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="F34" s="13" t="s">
-        <v>252</v>
+        <v>281</v>
       </c>
       <c r="G34" s="13" t="s">
-        <v>253</v>
+        <v>282</v>
       </c>
       <c r="H34" s="13" t="s">
-        <v>254</v>
+        <v>283</v>
       </c>
       <c r="I34" s="13" t="s">
-        <v>255</v>
+        <v>284</v>
       </c>
       <c r="J34" s="13" t="s">
-        <v>256</v>
+        <v>285</v>
       </c>
       <c r="K34" s="13" t="s">
-        <v>257</v>
+        <v>286</v>
       </c>
       <c r="L34" s="16"/>
       <c r="M34" s="17"/>
@@ -4292,39 +4392,39 @@
       <c r="P34" s="17"/>
       <c r="Q34" s="16"/>
     </row>
-    <row r="35" spans="1:17" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:17" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="14" t="s">
-        <v>258</v>
+        <v>287</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>239</v>
+        <v>268</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D35" s="15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="F35" s="13" t="s">
-        <v>259</v>
+        <v>288</v>
       </c>
       <c r="G35" s="13" t="s">
-        <v>260</v>
+        <v>289</v>
       </c>
       <c r="H35" s="13" t="s">
-        <v>261</v>
+        <v>290</v>
       </c>
       <c r="I35" s="13" t="s">
-        <v>262</v>
+        <v>291</v>
       </c>
       <c r="J35" s="13" t="s">
-        <v>263</v>
+        <v>292</v>
       </c>
       <c r="K35" s="13" t="s">
-        <v>264</v>
+        <v>293</v>
       </c>
       <c r="L35" s="16"/>
       <c r="M35" s="17"/>
@@ -4333,39 +4433,39 @@
       <c r="P35" s="17"/>
       <c r="Q35" s="16"/>
     </row>
-    <row r="36" spans="1:17" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:17" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="14" t="s">
-        <v>265</v>
+        <v>294</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>266</v>
+        <v>295</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D36" s="15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E36" s="13" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="F36" s="13" t="s">
-        <v>252</v>
+        <v>281</v>
       </c>
       <c r="G36" s="13" t="s">
-        <v>267</v>
+        <v>296</v>
       </c>
       <c r="H36" s="13" t="s">
-        <v>268</v>
+        <v>297</v>
       </c>
       <c r="I36" s="13" t="s">
-        <v>269</v>
+        <v>298</v>
       </c>
       <c r="J36" s="13" t="s">
-        <v>270</v>
+        <v>299</v>
       </c>
       <c r="K36" s="13" t="s">
-        <v>271</v>
+        <v>300</v>
       </c>
       <c r="L36" s="16"/>
       <c r="M36" s="17"/>
@@ -4374,39 +4474,39 @@
       <c r="P36" s="17"/>
       <c r="Q36" s="16"/>
     </row>
-    <row r="37" spans="1:17" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:17" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="14" t="s">
-        <v>272</v>
+        <v>301</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>266</v>
+        <v>295</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="F37" s="13" t="s">
-        <v>259</v>
+        <v>288</v>
       </c>
       <c r="G37" s="13" t="s">
-        <v>273</v>
+        <v>302</v>
       </c>
       <c r="H37" s="13" t="s">
-        <v>274</v>
+        <v>303</v>
       </c>
       <c r="I37" s="13" t="s">
-        <v>275</v>
+        <v>304</v>
       </c>
       <c r="J37" s="13" t="s">
-        <v>276</v>
+        <v>305</v>
       </c>
       <c r="K37" s="13" t="s">
-        <v>277</v>
+        <v>306</v>
       </c>
       <c r="L37" s="16"/>
       <c r="M37" s="17"/>
@@ -4415,39 +4515,39 @@
       <c r="P37" s="17"/>
       <c r="Q37" s="16"/>
     </row>
-    <row r="38" spans="1:17" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:17" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="14" t="s">
-        <v>278</v>
+        <v>307</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>266</v>
+        <v>295</v>
       </c>
       <c r="C38" s="15" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D38" s="15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="F38" s="13" t="s">
-        <v>259</v>
+        <v>288</v>
       </c>
       <c r="G38" s="13" t="s">
-        <v>279</v>
+        <v>308</v>
       </c>
       <c r="H38" s="13" t="s">
-        <v>280</v>
+        <v>309</v>
       </c>
       <c r="I38" s="13" t="s">
-        <v>281</v>
+        <v>310</v>
       </c>
       <c r="J38" s="13" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="K38" s="13" t="s">
-        <v>282</v>
+        <v>311</v>
       </c>
       <c r="L38" s="16"/>
       <c r="M38" s="17"/>
@@ -4456,39 +4556,39 @@
       <c r="P38" s="17"/>
       <c r="Q38" s="16"/>
     </row>
-    <row r="39" spans="1:17" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:17" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="14" t="s">
-        <v>283</v>
+        <v>312</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>284</v>
+        <v>313</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D39" s="15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E39" s="13" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="F39" s="13" t="s">
-        <v>285</v>
+        <v>314</v>
       </c>
       <c r="G39" s="13" t="s">
-        <v>286</v>
+        <v>315</v>
       </c>
       <c r="H39" s="13" t="s">
-        <v>287</v>
+        <v>316</v>
       </c>
       <c r="I39" s="13" t="s">
-        <v>288</v>
+        <v>317</v>
       </c>
       <c r="J39" s="13" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="K39" s="13" t="s">
-        <v>289</v>
+        <v>318</v>
       </c>
       <c r="L39" s="16"/>
       <c r="M39" s="17"/>
@@ -4497,39 +4597,39 @@
       <c r="P39" s="17"/>
       <c r="Q39" s="16"/>
     </row>
-    <row r="40" spans="1:17" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:17" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="14" t="s">
-        <v>290</v>
+        <v>319</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>291</v>
+        <v>320</v>
       </c>
       <c r="C40" s="15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D40" s="15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E40" s="13" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="F40" s="13" t="s">
-        <v>292</v>
+        <v>321</v>
       </c>
       <c r="G40" s="13" t="s">
-        <v>293</v>
+        <v>322</v>
       </c>
       <c r="H40" s="13" t="s">
-        <v>294</v>
+        <v>323</v>
       </c>
       <c r="I40" s="13" t="s">
-        <v>295</v>
+        <v>324</v>
       </c>
       <c r="J40" s="13" t="s">
-        <v>296</v>
+        <v>325</v>
       </c>
       <c r="K40" s="13" t="s">
-        <v>297</v>
+        <v>326</v>
       </c>
       <c r="L40" s="16"/>
       <c r="M40" s="17"/>
@@ -4538,39 +4638,39 @@
       <c r="P40" s="17"/>
       <c r="Q40" s="16"/>
     </row>
-    <row r="41" spans="1:17" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:17" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="14" t="s">
-        <v>298</v>
+        <v>327</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>291</v>
+        <v>320</v>
       </c>
       <c r="C41" s="15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D41" s="15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E41" s="13" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="F41" s="13" t="s">
-        <v>292</v>
+        <v>321</v>
       </c>
       <c r="G41" s="13" t="s">
-        <v>299</v>
+        <v>328</v>
       </c>
       <c r="H41" s="13" t="s">
-        <v>294</v>
+        <v>323</v>
       </c>
       <c r="I41" s="13" t="s">
-        <v>300</v>
+        <v>329</v>
       </c>
       <c r="J41" s="13" t="s">
-        <v>301</v>
+        <v>330</v>
       </c>
       <c r="K41" s="13" t="s">
-        <v>302</v>
+        <v>331</v>
       </c>
       <c r="L41" s="16"/>
       <c r="M41" s="17"/>
@@ -4579,39 +4679,39 @@
       <c r="P41" s="17"/>
       <c r="Q41" s="16"/>
     </row>
-    <row r="42" spans="1:17" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:17" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="14" t="s">
-        <v>303</v>
+        <v>332</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>291</v>
+        <v>320</v>
       </c>
       <c r="C42" s="15" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D42" s="15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E42" s="13" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="F42" s="13" t="s">
-        <v>304</v>
+        <v>333</v>
       </c>
       <c r="G42" s="13" t="s">
-        <v>305</v>
+        <v>334</v>
       </c>
       <c r="H42" s="13" t="s">
-        <v>306</v>
+        <v>335</v>
       </c>
       <c r="I42" s="13" t="s">
-        <v>307</v>
+        <v>336</v>
       </c>
       <c r="J42" s="13" t="s">
-        <v>308</v>
+        <v>337</v>
       </c>
       <c r="K42" s="13" t="s">
-        <v>309</v>
+        <v>338</v>
       </c>
       <c r="L42" s="16"/>
       <c r="M42" s="17"/>
@@ -4620,39 +4720,39 @@
       <c r="P42" s="17"/>
       <c r="Q42" s="16"/>
     </row>
-    <row r="43" spans="1:17" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:17" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="14" t="s">
-        <v>310</v>
+        <v>339</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>291</v>
+        <v>320</v>
       </c>
       <c r="C43" s="15" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D43" s="15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E43" s="13" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="F43" s="13" t="s">
-        <v>311</v>
+        <v>340</v>
       </c>
       <c r="G43" s="13" t="s">
-        <v>312</v>
+        <v>341</v>
       </c>
       <c r="H43" s="13" t="s">
-        <v>306</v>
+        <v>335</v>
       </c>
       <c r="I43" s="13" t="s">
-        <v>313</v>
+        <v>342</v>
       </c>
       <c r="J43" s="13" t="s">
-        <v>256</v>
+        <v>285</v>
       </c>
       <c r="K43" s="13" t="s">
-        <v>314</v>
+        <v>343</v>
       </c>
       <c r="L43" s="16"/>
       <c r="M43" s="17"/>
@@ -4661,39 +4761,39 @@
       <c r="P43" s="17"/>
       <c r="Q43" s="16"/>
     </row>
-    <row r="44" spans="1:17" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:17" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="14" t="s">
-        <v>315</v>
+        <v>344</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C44" s="15" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D44" s="15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="F44" s="13" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="G44" s="13" t="s">
-        <v>316</v>
+        <v>345</v>
       </c>
       <c r="H44" s="13" t="s">
-        <v>317</v>
+        <v>346</v>
       </c>
       <c r="I44" s="13" t="s">
-        <v>318</v>
+        <v>347</v>
       </c>
       <c r="J44" s="13" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K44" s="13" t="s">
-        <v>319</v>
+        <v>348</v>
       </c>
       <c r="L44" s="16"/>
       <c r="M44" s="17"/>
@@ -4702,39 +4802,39 @@
       <c r="P44" s="17"/>
       <c r="Q44" s="16"/>
     </row>
-    <row r="45" spans="1:17" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:17" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="14" t="s">
-        <v>320</v>
+        <v>349</v>
       </c>
       <c r="B45" s="13" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C45" s="15" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D45" s="15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F45" s="13" t="s">
-        <v>321</v>
+        <v>350</v>
       </c>
       <c r="G45" s="13" t="s">
-        <v>598</v>
+        <v>351</v>
       </c>
       <c r="H45" s="13" t="s">
-        <v>317</v>
+        <v>346</v>
       </c>
       <c r="I45" s="13" t="s">
-        <v>599</v>
+        <v>352</v>
       </c>
       <c r="J45" s="13" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K45" s="13" t="s">
-        <v>600</v>
+        <v>353</v>
       </c>
       <c r="L45" s="16"/>
       <c r="M45" s="17"/>
@@ -4743,39 +4843,39 @@
       <c r="P45" s="17"/>
       <c r="Q45" s="16"/>
     </row>
-    <row r="46" spans="1:17" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:17" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="14" t="s">
-        <v>322</v>
+        <v>354</v>
       </c>
       <c r="B46" s="13" t="s">
-        <v>323</v>
+        <v>355</v>
       </c>
       <c r="C46" s="15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D46" s="15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E46" s="13" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="F46" s="13" t="s">
-        <v>324</v>
+        <v>356</v>
       </c>
       <c r="G46" s="13" t="s">
-        <v>325</v>
+        <v>357</v>
       </c>
       <c r="H46" s="13" t="s">
-        <v>326</v>
+        <v>358</v>
       </c>
       <c r="I46" s="13" t="s">
-        <v>327</v>
+        <v>359</v>
       </c>
       <c r="J46" s="13" t="s">
-        <v>328</v>
+        <v>360</v>
       </c>
       <c r="K46" s="13" t="s">
-        <v>329</v>
+        <v>361</v>
       </c>
       <c r="L46" s="16"/>
       <c r="M46" s="17"/>
@@ -4784,39 +4884,39 @@
       <c r="P46" s="17"/>
       <c r="Q46" s="16"/>
     </row>
-    <row r="47" spans="1:17" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:17" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="14" t="s">
-        <v>330</v>
+        <v>362</v>
       </c>
       <c r="B47" s="13" t="s">
-        <v>331</v>
+        <v>363</v>
       </c>
       <c r="C47" s="15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D47" s="15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E47" s="13" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="F47" s="13" t="s">
-        <v>332</v>
+        <v>364</v>
       </c>
       <c r="G47" s="13" t="s">
-        <v>333</v>
+        <v>365</v>
       </c>
       <c r="H47" s="13" t="s">
-        <v>334</v>
+        <v>366</v>
       </c>
       <c r="I47" s="13" t="s">
-        <v>335</v>
+        <v>367</v>
       </c>
       <c r="J47" s="13" t="s">
-        <v>328</v>
+        <v>360</v>
       </c>
       <c r="K47" s="13" t="s">
-        <v>336</v>
+        <v>368</v>
       </c>
       <c r="L47" s="16"/>
       <c r="M47" s="17"/>
@@ -4825,39 +4925,39 @@
       <c r="P47" s="17"/>
       <c r="Q47" s="16"/>
     </row>
-    <row r="48" spans="1:17" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:17" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="14" t="s">
-        <v>337</v>
+        <v>369</v>
       </c>
       <c r="B48" s="13" t="s">
-        <v>331</v>
+        <v>363</v>
       </c>
       <c r="C48" s="15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D48" s="15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E48" s="13" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="F48" s="13" t="s">
-        <v>338</v>
+        <v>370</v>
       </c>
       <c r="G48" s="13" t="s">
-        <v>339</v>
+        <v>371</v>
       </c>
       <c r="H48" s="13" t="s">
-        <v>340</v>
+        <v>372</v>
       </c>
       <c r="I48" s="13" t="s">
-        <v>341</v>
+        <v>373</v>
       </c>
       <c r="J48" s="13" t="s">
-        <v>342</v>
+        <v>374</v>
       </c>
       <c r="K48" s="13" t="s">
-        <v>343</v>
+        <v>375</v>
       </c>
       <c r="L48" s="16"/>
       <c r="M48" s="17"/>
@@ -4866,39 +4966,39 @@
       <c r="P48" s="17"/>
       <c r="Q48" s="16"/>
     </row>
-    <row r="49" spans="1:17" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:17" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="14" t="s">
-        <v>344</v>
+        <v>376</v>
       </c>
       <c r="B49" s="13" t="s">
-        <v>331</v>
+        <v>363</v>
       </c>
       <c r="C49" s="15" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D49" s="15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E49" s="13" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="F49" s="13" t="s">
-        <v>345</v>
+        <v>377</v>
       </c>
       <c r="G49" s="13" t="s">
-        <v>346</v>
+        <v>378</v>
       </c>
       <c r="H49" s="13" t="s">
-        <v>347</v>
+        <v>379</v>
       </c>
       <c r="I49" s="13" t="s">
-        <v>348</v>
+        <v>380</v>
       </c>
       <c r="J49" s="13" t="s">
-        <v>349</v>
+        <v>381</v>
       </c>
       <c r="K49" s="13" t="s">
-        <v>350</v>
+        <v>382</v>
       </c>
       <c r="L49" s="16"/>
       <c r="M49" s="17"/>
@@ -4907,39 +5007,39 @@
       <c r="P49" s="17"/>
       <c r="Q49" s="16"/>
     </row>
-    <row r="50" spans="1:17" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:17" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="14" t="s">
-        <v>351</v>
+        <v>383</v>
       </c>
       <c r="B50" s="13" t="s">
-        <v>331</v>
+        <v>363</v>
       </c>
       <c r="C50" s="15" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D50" s="15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E50" s="13" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="F50" s="13" t="s">
-        <v>345</v>
+        <v>377</v>
       </c>
       <c r="G50" s="13" t="s">
-        <v>352</v>
+        <v>384</v>
       </c>
       <c r="H50" s="13" t="s">
-        <v>353</v>
+        <v>385</v>
       </c>
       <c r="I50" s="13" t="s">
-        <v>354</v>
+        <v>386</v>
       </c>
       <c r="J50" s="13" t="s">
-        <v>355</v>
+        <v>387</v>
       </c>
       <c r="K50" s="13" t="s">
-        <v>356</v>
+        <v>388</v>
       </c>
       <c r="L50" s="16"/>
       <c r="M50" s="17"/>
@@ -4948,39 +5048,39 @@
       <c r="P50" s="17"/>
       <c r="Q50" s="16"/>
     </row>
-    <row r="51" spans="1:17" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:17" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="14" t="s">
-        <v>357</v>
+        <v>389</v>
       </c>
       <c r="B51" s="13" t="s">
-        <v>358</v>
+        <v>390</v>
       </c>
       <c r="C51" s="15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D51" s="15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E51" s="13" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="F51" s="13" t="s">
-        <v>359</v>
+        <v>391</v>
       </c>
       <c r="G51" s="13" t="s">
-        <v>360</v>
+        <v>392</v>
       </c>
       <c r="H51" s="13" t="s">
-        <v>361</v>
+        <v>393</v>
       </c>
       <c r="I51" s="13" t="s">
-        <v>362</v>
+        <v>394</v>
       </c>
       <c r="J51" s="13" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="K51" s="13" t="s">
-        <v>363</v>
+        <v>395</v>
       </c>
       <c r="L51" s="16"/>
       <c r="M51" s="17"/>
@@ -4989,39 +5089,39 @@
       <c r="P51" s="17"/>
       <c r="Q51" s="16"/>
     </row>
-    <row r="52" spans="1:17" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:17" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="14" t="s">
-        <v>364</v>
+        <v>396</v>
       </c>
       <c r="B52" s="13" t="s">
-        <v>365</v>
+        <v>397</v>
       </c>
       <c r="C52" s="15" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D52" s="15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E52" s="13" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="F52" s="13" t="s">
-        <v>259</v>
+        <v>288</v>
       </c>
       <c r="G52" s="13" t="s">
-        <v>366</v>
+        <v>398</v>
       </c>
       <c r="H52" s="13" t="s">
-        <v>367</v>
+        <v>399</v>
       </c>
       <c r="I52" s="13" t="s">
-        <v>368</v>
+        <v>400</v>
       </c>
       <c r="J52" s="13" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="K52" s="13" t="s">
-        <v>369</v>
+        <v>401</v>
       </c>
       <c r="L52" s="16"/>
       <c r="M52" s="17"/>
@@ -5030,39 +5130,39 @@
       <c r="P52" s="17"/>
       <c r="Q52" s="16"/>
     </row>
-    <row r="53" spans="1:17" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:17" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="14" t="s">
-        <v>370</v>
+        <v>402</v>
       </c>
       <c r="B53" s="13" t="s">
-        <v>371</v>
+        <v>403</v>
       </c>
       <c r="C53" s="15" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D53" s="15" t="s">
-        <v>371</v>
+        <v>403</v>
       </c>
       <c r="E53" s="13" t="s">
-        <v>372</v>
+        <v>404</v>
       </c>
       <c r="F53" s="13" t="s">
-        <v>373</v>
+        <v>405</v>
       </c>
       <c r="G53" s="13" t="s">
-        <v>374</v>
+        <v>406</v>
       </c>
       <c r="H53" s="13" t="s">
-        <v>375</v>
+        <v>407</v>
       </c>
       <c r="I53" s="13" t="s">
-        <v>376</v>
+        <v>408</v>
       </c>
       <c r="J53" s="13" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="K53" s="13" t="s">
-        <v>377</v>
+        <v>409</v>
       </c>
       <c r="L53" s="16"/>
       <c r="M53" s="17"/>
@@ -5071,39 +5171,39 @@
       <c r="P53" s="17"/>
       <c r="Q53" s="16"/>
     </row>
-    <row r="54" spans="1:17" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:17" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="14" t="s">
-        <v>378</v>
+        <v>410</v>
       </c>
       <c r="B54" s="13" t="s">
-        <v>371</v>
+        <v>403</v>
       </c>
       <c r="C54" s="15" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D54" s="15" t="s">
-        <v>371</v>
+        <v>403</v>
       </c>
       <c r="E54" s="13" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="F54" s="13" t="s">
-        <v>373</v>
+        <v>405</v>
       </c>
       <c r="G54" s="13" t="s">
-        <v>379</v>
+        <v>411</v>
       </c>
       <c r="H54" s="13" t="s">
-        <v>380</v>
+        <v>412</v>
       </c>
       <c r="I54" s="13" t="s">
-        <v>381</v>
+        <v>413</v>
       </c>
       <c r="J54" s="13" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="K54" s="13" t="s">
-        <v>382</v>
+        <v>414</v>
       </c>
       <c r="L54" s="16"/>
       <c r="M54" s="17"/>
@@ -5112,39 +5212,39 @@
       <c r="P54" s="17"/>
       <c r="Q54" s="16"/>
     </row>
-    <row r="55" spans="1:17" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:17" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="14" t="s">
-        <v>383</v>
+        <v>415</v>
       </c>
       <c r="B55" s="13" t="s">
-        <v>371</v>
+        <v>403</v>
       </c>
       <c r="C55" s="15" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D55" s="15" t="s">
-        <v>371</v>
+        <v>403</v>
       </c>
       <c r="E55" s="13" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="F55" s="13" t="s">
-        <v>373</v>
+        <v>405</v>
       </c>
       <c r="G55" s="13" t="s">
-        <v>384</v>
+        <v>416</v>
       </c>
       <c r="H55" s="13" t="s">
-        <v>385</v>
+        <v>417</v>
       </c>
       <c r="I55" s="13" t="s">
-        <v>386</v>
+        <v>418</v>
       </c>
       <c r="J55" s="13" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K55" s="13" t="s">
-        <v>387</v>
+        <v>419</v>
       </c>
       <c r="L55" s="16"/>
       <c r="M55" s="17"/>
@@ -5153,39 +5253,39 @@
       <c r="P55" s="17"/>
       <c r="Q55" s="16"/>
     </row>
-    <row r="56" spans="1:17" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:17" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="14" t="s">
-        <v>388</v>
+        <v>420</v>
       </c>
       <c r="B56" s="13" t="s">
-        <v>371</v>
+        <v>403</v>
       </c>
       <c r="C56" s="15" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D56" s="15" t="s">
-        <v>371</v>
+        <v>403</v>
       </c>
       <c r="E56" s="13" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="F56" s="13" t="s">
-        <v>373</v>
+        <v>405</v>
       </c>
       <c r="G56" s="13" t="s">
-        <v>389</v>
+        <v>421</v>
       </c>
       <c r="H56" s="13" t="s">
-        <v>261</v>
+        <v>290</v>
       </c>
       <c r="I56" s="13" t="s">
-        <v>390</v>
+        <v>422</v>
       </c>
       <c r="J56" s="13" t="s">
-        <v>256</v>
+        <v>285</v>
       </c>
       <c r="K56" s="13" t="s">
-        <v>391</v>
+        <v>423</v>
       </c>
       <c r="L56" s="16"/>
       <c r="M56" s="17"/>
@@ -5194,39 +5294,39 @@
       <c r="P56" s="17"/>
       <c r="Q56" s="16"/>
     </row>
-    <row r="57" spans="1:17" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:17" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="14" t="s">
-        <v>392</v>
+        <v>424</v>
       </c>
       <c r="B57" s="13" t="s">
-        <v>371</v>
+        <v>403</v>
       </c>
       <c r="C57" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="D57" s="15" t="s">
+        <v>403</v>
+      </c>
+      <c r="E57" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="F57" s="13" t="s">
+        <v>405</v>
+      </c>
+      <c r="G57" s="13" t="s">
+        <v>425</v>
+      </c>
+      <c r="H57" s="13" t="s">
+        <v>426</v>
+      </c>
+      <c r="I57" s="13" t="s">
+        <v>427</v>
+      </c>
+      <c r="J57" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="D57" s="15" t="s">
-        <v>371</v>
-      </c>
-      <c r="E57" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="F57" s="13" t="s">
-        <v>373</v>
-      </c>
-      <c r="G57" s="13" t="s">
-        <v>393</v>
-      </c>
-      <c r="H57" s="13" t="s">
-        <v>394</v>
-      </c>
-      <c r="I57" s="13" t="s">
-        <v>395</v>
-      </c>
-      <c r="J57" s="13" t="s">
-        <v>43</v>
-      </c>
       <c r="K57" s="13" t="s">
-        <v>396</v>
+        <v>428</v>
       </c>
       <c r="L57" s="16"/>
       <c r="M57" s="17"/>
@@ -5237,37 +5337,37 @@
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A58" s="14" t="s">
-        <v>397</v>
+        <v>429</v>
       </c>
       <c r="B58" s="13" t="s">
-        <v>371</v>
+        <v>403</v>
       </c>
       <c r="C58" s="15" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D58" s="15" t="s">
-        <v>371</v>
+        <v>403</v>
       </c>
       <c r="E58" s="13" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F58" s="13" t="s">
-        <v>321</v>
+        <v>350</v>
       </c>
       <c r="G58" s="13" t="s">
-        <v>398</v>
+        <v>430</v>
       </c>
       <c r="H58" s="13" t="s">
-        <v>317</v>
+        <v>346</v>
       </c>
       <c r="I58" s="13" t="s">
-        <v>399</v>
+        <v>431</v>
       </c>
       <c r="J58" s="13" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K58" s="13" t="s">
-        <v>400</v>
+        <v>432</v>
       </c>
       <c r="L58" s="16"/>
       <c r="M58" s="17"/>
@@ -5276,39 +5376,39 @@
       <c r="P58" s="17"/>
       <c r="Q58" s="16"/>
     </row>
-    <row r="59" spans="1:17" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:17" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="14" t="s">
-        <v>401</v>
+        <v>433</v>
       </c>
       <c r="B59" s="13" t="s">
-        <v>371</v>
+        <v>403</v>
       </c>
       <c r="C59" s="15" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D59" s="15" t="s">
-        <v>371</v>
+        <v>403</v>
       </c>
       <c r="E59" s="13" t="s">
-        <v>402</v>
+        <v>434</v>
       </c>
       <c r="F59" s="13" t="s">
-        <v>373</v>
+        <v>405</v>
       </c>
       <c r="G59" s="13" t="s">
-        <v>403</v>
+        <v>435</v>
       </c>
       <c r="H59" s="13" t="s">
-        <v>404</v>
+        <v>436</v>
       </c>
       <c r="I59" s="13" t="s">
-        <v>405</v>
+        <v>437</v>
       </c>
       <c r="J59" s="13" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="K59" s="13" t="s">
-        <v>406</v>
+        <v>438</v>
       </c>
       <c r="L59" s="16"/>
       <c r="M59" s="17"/>
@@ -5317,39 +5417,39 @@
       <c r="P59" s="17"/>
       <c r="Q59" s="16"/>
     </row>
-    <row r="60" spans="1:17" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:17" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="14" t="s">
-        <v>407</v>
+        <v>439</v>
       </c>
       <c r="B60" s="13" t="s">
-        <v>371</v>
+        <v>403</v>
       </c>
       <c r="C60" s="15" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D60" s="15" t="s">
-        <v>371</v>
+        <v>403</v>
       </c>
       <c r="E60" s="13" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="F60" s="13" t="s">
-        <v>408</v>
+        <v>440</v>
       </c>
       <c r="G60" s="13" t="s">
-        <v>409</v>
+        <v>441</v>
       </c>
       <c r="H60" s="13" t="s">
-        <v>410</v>
+        <v>442</v>
       </c>
       <c r="I60" s="13" t="s">
-        <v>411</v>
+        <v>443</v>
       </c>
       <c r="J60" s="13" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="K60" s="13" t="s">
-        <v>412</v>
+        <v>444</v>
       </c>
       <c r="L60" s="16"/>
       <c r="M60" s="17"/>
@@ -5358,39 +5458,39 @@
       <c r="P60" s="17"/>
       <c r="Q60" s="16"/>
     </row>
-    <row r="61" spans="1:17" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:17" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="14" t="s">
-        <v>413</v>
+        <v>445</v>
       </c>
       <c r="B61" s="13" t="s">
-        <v>371</v>
+        <v>403</v>
       </c>
       <c r="C61" s="15" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D61" s="15" t="s">
-        <v>371</v>
+        <v>403</v>
       </c>
       <c r="E61" s="13" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F61" s="13" t="s">
-        <v>373</v>
+        <v>405</v>
       </c>
       <c r="G61" s="13" t="s">
-        <v>414</v>
+        <v>446</v>
       </c>
       <c r="H61" s="13" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="I61" s="13" t="s">
-        <v>415</v>
+        <v>447</v>
       </c>
       <c r="J61" s="13" t="s">
-        <v>416</v>
+        <v>448</v>
       </c>
       <c r="K61" s="13" t="s">
-        <v>417</v>
+        <v>449</v>
       </c>
       <c r="L61" s="16"/>
       <c r="M61" s="17"/>
@@ -5399,39 +5499,39 @@
       <c r="P61" s="17"/>
       <c r="Q61" s="16"/>
     </row>
-    <row r="62" spans="1:17" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:17" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="14" t="s">
-        <v>418</v>
+        <v>450</v>
       </c>
       <c r="B62" s="13" t="s">
-        <v>419</v>
+        <v>451</v>
       </c>
       <c r="C62" s="15" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D62" s="15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E62" s="13" t="s">
-        <v>420</v>
+        <v>452</v>
       </c>
       <c r="F62" s="13" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G62" s="13" t="s">
-        <v>421</v>
+        <v>453</v>
       </c>
       <c r="H62" s="13" t="s">
-        <v>422</v>
+        <v>454</v>
       </c>
       <c r="I62" s="13" t="s">
-        <v>423</v>
+        <v>455</v>
       </c>
       <c r="J62" s="13" t="s">
-        <v>185</v>
+        <v>214</v>
       </c>
       <c r="K62" s="13" t="s">
-        <v>424</v>
+        <v>456</v>
       </c>
       <c r="L62" s="16"/>
       <c r="M62" s="17"/>
@@ -5440,39 +5540,39 @@
       <c r="P62" s="17"/>
       <c r="Q62" s="16"/>
     </row>
-    <row r="63" spans="1:17" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:17" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="14" t="s">
-        <v>425</v>
+        <v>457</v>
       </c>
       <c r="B63" s="13" t="s">
-        <v>419</v>
+        <v>451</v>
       </c>
       <c r="C63" s="15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D63" s="15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E63" s="13" t="s">
-        <v>420</v>
+        <v>452</v>
       </c>
       <c r="F63" s="13" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G63" s="13" t="s">
-        <v>426</v>
+        <v>458</v>
       </c>
       <c r="H63" s="13" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="I63" s="13" t="s">
-        <v>427</v>
+        <v>459</v>
       </c>
       <c r="J63" s="13" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="K63" s="13" t="s">
-        <v>428</v>
+        <v>460</v>
       </c>
       <c r="L63" s="16"/>
       <c r="M63" s="17"/>
@@ -5481,39 +5581,39 @@
       <c r="P63" s="17"/>
       <c r="Q63" s="16"/>
     </row>
-    <row r="64" spans="1:17" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:17" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="14" t="s">
-        <v>429</v>
+        <v>461</v>
       </c>
       <c r="B64" s="13" t="s">
-        <v>372</v>
+        <v>404</v>
       </c>
       <c r="C64" s="15" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D64" s="15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E64" s="13" t="s">
-        <v>372</v>
+        <v>404</v>
       </c>
       <c r="F64" s="13" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G64" s="13" t="s">
-        <v>430</v>
+        <v>462</v>
       </c>
       <c r="H64" s="13" t="s">
-        <v>431</v>
+        <v>463</v>
       </c>
       <c r="I64" s="13" t="s">
-        <v>432</v>
+        <v>464</v>
       </c>
       <c r="J64" s="13" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="K64" s="13" t="s">
-        <v>433</v>
+        <v>465</v>
       </c>
       <c r="L64" s="16"/>
       <c r="M64" s="17"/>
@@ -5522,39 +5622,39 @@
       <c r="P64" s="17"/>
       <c r="Q64" s="16"/>
     </row>
-    <row r="65" spans="1:17" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:17" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="14" t="s">
-        <v>434</v>
+        <v>466</v>
       </c>
       <c r="B65" s="13" t="s">
-        <v>372</v>
+        <v>404</v>
       </c>
       <c r="C65" s="15" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D65" s="15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E65" s="13" t="s">
-        <v>372</v>
+        <v>404</v>
       </c>
       <c r="F65" s="13" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G65" s="13" t="s">
-        <v>435</v>
+        <v>467</v>
       </c>
       <c r="H65" s="13" t="s">
-        <v>436</v>
+        <v>468</v>
       </c>
       <c r="I65" s="13" t="s">
-        <v>437</v>
+        <v>469</v>
       </c>
       <c r="J65" s="13" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="K65" s="13" t="s">
-        <v>438</v>
+        <v>470</v>
       </c>
       <c r="L65" s="16"/>
       <c r="M65" s="17"/>
@@ -5563,39 +5663,39 @@
       <c r="P65" s="17"/>
       <c r="Q65" s="16"/>
     </row>
-    <row r="66" spans="1:17" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:17" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="14" t="s">
-        <v>439</v>
+        <v>471</v>
       </c>
       <c r="B66" s="13" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C66" s="15" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D66" s="15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E66" s="13" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="F66" s="13" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G66" s="13" t="s">
-        <v>440</v>
+        <v>472</v>
       </c>
       <c r="H66" s="13" t="s">
-        <v>441</v>
+        <v>473</v>
       </c>
       <c r="I66" s="13" t="s">
-        <v>442</v>
+        <v>474</v>
       </c>
       <c r="J66" s="13" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="K66" s="13" t="s">
-        <v>443</v>
+        <v>475</v>
       </c>
       <c r="L66" s="16"/>
       <c r="M66" s="17"/>
@@ -5604,39 +5704,39 @@
       <c r="P66" s="17"/>
       <c r="Q66" s="16"/>
     </row>
-    <row r="67" spans="1:17" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:17" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="14" t="s">
-        <v>444</v>
+        <v>476</v>
       </c>
       <c r="B67" s="13" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C67" s="15" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D67" s="15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E67" s="13" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="F67" s="13" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G67" s="13" t="s">
-        <v>445</v>
+        <v>477</v>
       </c>
       <c r="H67" s="13" t="s">
-        <v>446</v>
+        <v>478</v>
       </c>
       <c r="I67" s="13" t="s">
-        <v>447</v>
+        <v>479</v>
       </c>
       <c r="J67" s="13" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="K67" s="13" t="s">
-        <v>448</v>
+        <v>480</v>
       </c>
       <c r="L67" s="16"/>
       <c r="M67" s="17"/>
@@ -5645,39 +5745,39 @@
       <c r="P67" s="17"/>
       <c r="Q67" s="16"/>
     </row>
-    <row r="68" spans="1:17" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:17" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="14" t="s">
-        <v>449</v>
+        <v>481</v>
       </c>
       <c r="B68" s="13" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C68" s="15" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D68" s="15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E68" s="13" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F68" s="13" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G68" s="13" t="s">
-        <v>450</v>
+        <v>482</v>
       </c>
       <c r="H68" s="13" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="I68" s="13" t="s">
-        <v>451</v>
+        <v>483</v>
       </c>
       <c r="J68" s="13" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="K68" s="13" t="s">
-        <v>452</v>
+        <v>484</v>
       </c>
       <c r="L68" s="16"/>
       <c r="M68" s="17"/>
@@ -5686,39 +5786,39 @@
       <c r="P68" s="17"/>
       <c r="Q68" s="16"/>
     </row>
-    <row r="69" spans="1:17" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:17" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="14" t="s">
-        <v>453</v>
+        <v>485</v>
       </c>
       <c r="B69" s="13" t="s">
-        <v>180</v>
+        <v>209</v>
       </c>
       <c r="C69" s="15" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D69" s="15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E69" s="13" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="F69" s="13" t="s">
-        <v>454</v>
+        <v>486</v>
       </c>
       <c r="G69" s="13" t="s">
-        <v>455</v>
+        <v>487</v>
       </c>
       <c r="H69" s="13" t="s">
-        <v>456</v>
+        <v>488</v>
       </c>
       <c r="I69" s="13" t="s">
-        <v>457</v>
+        <v>489</v>
       </c>
       <c r="J69" s="13" t="s">
-        <v>458</v>
+        <v>490</v>
       </c>
       <c r="K69" s="13" t="s">
-        <v>459</v>
+        <v>491</v>
       </c>
       <c r="L69" s="16"/>
       <c r="M69" s="17"/>
@@ -5727,39 +5827,39 @@
       <c r="P69" s="17"/>
       <c r="Q69" s="16"/>
     </row>
-    <row r="70" spans="1:17" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:17" ht="79.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="14" t="s">
-        <v>460</v>
+        <v>492</v>
       </c>
       <c r="B70" s="13" t="s">
-        <v>331</v>
+        <v>363</v>
       </c>
       <c r="C70" s="15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D70" s="15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E70" s="13" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="F70" s="13" t="s">
-        <v>461</v>
+        <v>493</v>
       </c>
       <c r="G70" s="13" t="s">
-        <v>462</v>
+        <v>494</v>
       </c>
       <c r="H70" s="13" t="s">
-        <v>463</v>
+        <v>495</v>
       </c>
       <c r="I70" s="13" t="s">
-        <v>464</v>
+        <v>496</v>
       </c>
       <c r="J70" s="13" t="s">
-        <v>465</v>
+        <v>497</v>
       </c>
       <c r="K70" s="13" t="s">
-        <v>466</v>
+        <v>498</v>
       </c>
       <c r="L70" s="16"/>
       <c r="M70" s="17"/>
@@ -5768,39 +5868,39 @@
       <c r="P70" s="17"/>
       <c r="Q70" s="16"/>
     </row>
-    <row r="71" spans="1:17" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:17" ht="92.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="14" t="s">
-        <v>467</v>
+        <v>499</v>
       </c>
       <c r="B71" s="13" t="s">
-        <v>331</v>
+        <v>363</v>
       </c>
       <c r="C71" s="15" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D71" s="15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E71" s="13" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="F71" s="13" t="s">
-        <v>345</v>
+        <v>377</v>
       </c>
       <c r="G71" s="13" t="s">
-        <v>468</v>
+        <v>500</v>
       </c>
       <c r="H71" s="13" t="s">
-        <v>469</v>
+        <v>501</v>
       </c>
       <c r="I71" s="13" t="s">
-        <v>470</v>
+        <v>502</v>
       </c>
       <c r="J71" s="13" t="s">
-        <v>471</v>
+        <v>503</v>
       </c>
       <c r="K71" s="13" t="s">
-        <v>472</v>
+        <v>504</v>
       </c>
       <c r="L71" s="16"/>
       <c r="M71" s="17"/>
@@ -5809,39 +5909,39 @@
       <c r="P71" s="17"/>
       <c r="Q71" s="16"/>
     </row>
-    <row r="72" spans="1:17" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:17" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="14" t="s">
-        <v>473</v>
+        <v>505</v>
       </c>
       <c r="B72" s="13" t="s">
-        <v>331</v>
+        <v>363</v>
       </c>
       <c r="C72" s="15" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D72" s="15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E72" s="13" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F72" s="13" t="s">
-        <v>345</v>
+        <v>377</v>
       </c>
       <c r="G72" s="13" t="s">
-        <v>474</v>
+        <v>506</v>
       </c>
       <c r="H72" s="13" t="s">
-        <v>475</v>
+        <v>507</v>
       </c>
       <c r="I72" s="13" t="s">
-        <v>476</v>
+        <v>508</v>
       </c>
       <c r="J72" s="13" t="s">
-        <v>477</v>
+        <v>509</v>
       </c>
       <c r="K72" s="13" t="s">
-        <v>478</v>
+        <v>510</v>
       </c>
       <c r="L72" s="16"/>
       <c r="M72" s="17"/>
@@ -5850,39 +5950,39 @@
       <c r="P72" s="17"/>
       <c r="Q72" s="16"/>
     </row>
-    <row r="73" spans="1:17" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:17" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="14" t="s">
-        <v>601</v>
+        <v>511</v>
       </c>
       <c r="B73" s="13" t="s">
-        <v>575</v>
+        <v>145</v>
       </c>
       <c r="C73" s="15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D73" s="15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E73" s="13" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="F73" s="13" t="s">
-        <v>602</v>
+        <v>512</v>
       </c>
       <c r="G73" s="13" t="s">
-        <v>603</v>
+        <v>513</v>
       </c>
       <c r="H73" s="13" t="s">
-        <v>139</v>
+        <v>186</v>
       </c>
       <c r="I73" s="13" t="s">
-        <v>604</v>
+        <v>514</v>
       </c>
       <c r="J73" s="13" t="s">
-        <v>605</v>
+        <v>515</v>
       </c>
       <c r="K73" s="13" t="s">
-        <v>606</v>
+        <v>516</v>
       </c>
       <c r="L73" s="16"/>
       <c r="M73" s="17"/>
@@ -5891,39 +5991,39 @@
       <c r="P73" s="17"/>
       <c r="Q73" s="16"/>
     </row>
-    <row r="74" spans="1:17" ht="66" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:17" ht="66" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="14" t="s">
-        <v>607</v>
+        <v>517</v>
       </c>
       <c r="B74" s="13" t="s">
-        <v>608</v>
+        <v>518</v>
       </c>
       <c r="C74" s="15" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D74" s="15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E74" s="13" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="F74" s="13" t="s">
-        <v>609</v>
+        <v>519</v>
       </c>
       <c r="G74" s="13" t="s">
-        <v>610</v>
+        <v>520</v>
       </c>
       <c r="H74" s="13" t="s">
-        <v>611</v>
+        <v>521</v>
       </c>
       <c r="I74" s="13" t="s">
-        <v>612</v>
+        <v>522</v>
       </c>
       <c r="J74" s="13" t="s">
-        <v>613</v>
+        <v>523</v>
       </c>
       <c r="K74" s="13" t="s">
-        <v>614</v>
+        <v>524</v>
       </c>
       <c r="L74" s="16"/>
       <c r="M74" s="17"/>
@@ -5932,39 +6032,39 @@
       <c r="P74" s="17"/>
       <c r="Q74" s="16"/>
     </row>
-    <row r="75" spans="1:17" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:17" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="14" t="s">
-        <v>615</v>
+        <v>525</v>
       </c>
       <c r="B75" s="13" t="s">
-        <v>608</v>
+        <v>518</v>
       </c>
       <c r="C75" s="15" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D75" s="15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E75" s="13" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F75" s="13" t="s">
-        <v>602</v>
+        <v>512</v>
       </c>
       <c r="G75" s="13" t="s">
-        <v>616</v>
+        <v>526</v>
       </c>
       <c r="H75" s="13" t="s">
-        <v>617</v>
+        <v>527</v>
       </c>
       <c r="I75" s="13" t="s">
-        <v>618</v>
+        <v>528</v>
       </c>
       <c r="J75" s="13" t="s">
-        <v>619</v>
+        <v>529</v>
       </c>
       <c r="K75" s="13" t="s">
-        <v>620</v>
+        <v>530</v>
       </c>
       <c r="L75" s="16"/>
       <c r="M75" s="17"/>
@@ -5973,39 +6073,39 @@
       <c r="P75" s="17"/>
       <c r="Q75" s="16"/>
     </row>
-    <row r="76" spans="1:17" ht="66" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:17" ht="66" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="14" t="s">
-        <v>621</v>
+        <v>531</v>
       </c>
       <c r="B76" s="13" t="s">
-        <v>575</v>
+        <v>145</v>
       </c>
       <c r="C76" s="15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D76" s="15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E76" s="13" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="F76" s="13" t="s">
-        <v>602</v>
+        <v>512</v>
       </c>
       <c r="G76" s="13" t="s">
-        <v>622</v>
+        <v>532</v>
       </c>
       <c r="H76" s="13" t="s">
-        <v>623</v>
+        <v>533</v>
       </c>
       <c r="I76" s="13" t="s">
-        <v>624</v>
+        <v>534</v>
       </c>
       <c r="J76" s="13" t="s">
-        <v>625</v>
+        <v>535</v>
       </c>
       <c r="K76" s="13" t="s">
-        <v>626</v>
+        <v>536</v>
       </c>
       <c r="L76" s="16"/>
       <c r="M76" s="17"/>
@@ -6014,39 +6114,39 @@
       <c r="P76" s="17"/>
       <c r="Q76" s="16"/>
     </row>
-    <row r="77" spans="1:17" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:17" ht="105.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="14" t="s">
-        <v>627</v>
+        <v>537</v>
       </c>
       <c r="B77" s="13" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C77" s="15" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D77" s="15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E77" s="13" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F77" s="13" t="s">
-        <v>602</v>
+        <v>512</v>
       </c>
       <c r="G77" s="13" t="s">
-        <v>628</v>
+        <v>538</v>
       </c>
       <c r="H77" s="13" t="s">
-        <v>629</v>
+        <v>539</v>
       </c>
       <c r="I77" s="13" t="s">
-        <v>630</v>
+        <v>540</v>
       </c>
       <c r="J77" s="13" t="s">
-        <v>585</v>
+        <v>156</v>
       </c>
       <c r="K77" s="13" t="s">
-        <v>631</v>
+        <v>541</v>
       </c>
       <c r="L77" s="16"/>
       <c r="M77" s="17"/>
@@ -6095,22 +6195,22 @@
   <sheetData>
     <row r="1" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>479</v>
+        <v>542</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>480</v>
+        <v>543</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="19" t="s">
-        <v>481</v>
+        <v>544</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
-        <v>482</v>
+        <v>545</v>
       </c>
       <c r="B5" s="20">
         <f>COUNTA('Test Cases'!$A$2:$A$77)</f>
@@ -6119,7 +6219,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B6" s="20">
         <f>COUNTIF('Test Cases'!$M$2:$M$77,"Pass")</f>
@@ -6128,7 +6228,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
-        <v>483</v>
+        <v>546</v>
       </c>
       <c r="B7" s="20">
         <f>COUNTIF('Test Cases'!$M$2:$M$77,"Fail")</f>
@@ -6137,7 +6237,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>484</v>
+        <v>547</v>
       </c>
       <c r="B8" s="20">
         <f>COUNTIF('Test Cases'!$M$2:$M$77,"Blocked")</f>
@@ -6146,7 +6246,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
-        <v>485</v>
+        <v>548</v>
       </c>
       <c r="B9" s="20">
         <f>B5-B6-B7-B8</f>
@@ -6155,7 +6255,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
-        <v>486</v>
+        <v>549</v>
       </c>
       <c r="B10" s="20">
         <f>B6+B7</f>
@@ -6164,7 +6264,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
-        <v>487</v>
+        <v>550</v>
       </c>
       <c r="B11" s="21" t="str">
         <f>IF(B10=0,"-",B6/B10)</f>
@@ -6173,7 +6273,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
-        <v>488</v>
+        <v>551</v>
       </c>
       <c r="B12" s="21">
         <f>IF(B5=0,"-",(B10+B8)/B5)</f>
@@ -6182,35 +6282,35 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="19" t="s">
-        <v>489</v>
+        <v>552</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="11" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>490</v>
+        <v>553</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>483</v>
+        <v>546</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>484</v>
+        <v>547</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>491</v>
+        <v>554</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>492</v>
+        <v>555</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="12" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B17" s="20">
         <f>COUNTIF('Test Cases'!$B$2:$B$77,A17)</f>
@@ -6239,7 +6339,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="12" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="B18" s="20">
         <f>COUNTIF('Test Cases'!$B$2:$B$77,A18)</f>
@@ -6268,7 +6368,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="12" t="s">
-        <v>575</v>
+        <v>145</v>
       </c>
       <c r="B19" s="20">
         <f>COUNTIF('Test Cases'!$B$2:$B$77,A19)</f>
@@ -6297,7 +6397,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="12" t="s">
-        <v>608</v>
+        <v>518</v>
       </c>
       <c r="B20" s="20">
         <f>COUNTIF('Test Cases'!$B$2:$B$77,A20)</f>
@@ -6326,7 +6426,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="12" t="s">
-        <v>149</v>
+        <v>177</v>
       </c>
       <c r="B21" s="20">
         <f>COUNTIF('Test Cases'!$B$2:$B$77,A21)</f>
@@ -6355,7 +6455,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="12" t="s">
-        <v>173</v>
+        <v>202</v>
       </c>
       <c r="B22" s="20">
         <f>COUNTIF('Test Cases'!$B$2:$B$77,A22)</f>
@@ -6384,7 +6484,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="12" t="s">
-        <v>180</v>
+        <v>209</v>
       </c>
       <c r="B23" s="20">
         <f>COUNTIF('Test Cases'!$B$2:$B$77,A23)</f>
@@ -6413,7 +6513,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="12" t="s">
-        <v>212</v>
+        <v>241</v>
       </c>
       <c r="B24" s="20">
         <f>COUNTIF('Test Cases'!$B$2:$B$77,A24)</f>
@@ -6442,7 +6542,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="12" t="s">
-        <v>239</v>
+        <v>268</v>
       </c>
       <c r="B25" s="20">
         <f>COUNTIF('Test Cases'!$B$2:$B$77,A25)</f>
@@ -6471,7 +6571,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="12" t="s">
-        <v>266</v>
+        <v>295</v>
       </c>
       <c r="B26" s="20">
         <f>COUNTIF('Test Cases'!$B$2:$B$77,A26)</f>
@@ -6500,7 +6600,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="12" t="s">
-        <v>284</v>
+        <v>313</v>
       </c>
       <c r="B27" s="20">
         <f>COUNTIF('Test Cases'!$B$2:$B$77,A27)</f>
@@ -6529,7 +6629,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="12" t="s">
-        <v>291</v>
+        <v>320</v>
       </c>
       <c r="B28" s="20">
         <f>COUNTIF('Test Cases'!$B$2:$B$77,A28)</f>
@@ -6558,7 +6658,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="12" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B29" s="20">
         <f>COUNTIF('Test Cases'!$B$2:$B$77,A29)</f>
@@ -6587,7 +6687,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="12" t="s">
-        <v>323</v>
+        <v>355</v>
       </c>
       <c r="B30" s="20">
         <f>COUNTIF('Test Cases'!$B$2:$B$77,A30)</f>
@@ -6616,7 +6716,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="12" t="s">
-        <v>331</v>
+        <v>363</v>
       </c>
       <c r="B31" s="20">
         <f>COUNTIF('Test Cases'!$B$2:$B$77,A31)</f>
@@ -6645,7 +6745,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="12" t="s">
-        <v>358</v>
+        <v>390</v>
       </c>
       <c r="B32" s="20">
         <f>COUNTIF('Test Cases'!$B$2:$B$77,A32)</f>
@@ -6674,7 +6774,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="12" t="s">
-        <v>365</v>
+        <v>397</v>
       </c>
       <c r="B33" s="20">
         <f>COUNTIF('Test Cases'!$B$2:$B$77,A33)</f>
@@ -6703,7 +6803,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="12" t="s">
-        <v>371</v>
+        <v>403</v>
       </c>
       <c r="B34" s="20">
         <f>COUNTIF('Test Cases'!$B$2:$B$77,A34)</f>
@@ -6732,7 +6832,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="12" t="s">
-        <v>419</v>
+        <v>451</v>
       </c>
       <c r="B35" s="20">
         <f>COUNTIF('Test Cases'!$B$2:$B$77,A35)</f>
@@ -6761,7 +6861,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="12" t="s">
-        <v>372</v>
+        <v>404</v>
       </c>
       <c r="B36" s="20">
         <f>COUNTIF('Test Cases'!$B$2:$B$77,A36)</f>
@@ -6790,7 +6890,7 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="12" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B37" s="20">
         <f>COUNTIF('Test Cases'!$B$2:$B$77,A37)</f>
@@ -6819,7 +6919,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="12" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B38" s="20">
         <f>COUNTIF('Test Cases'!$B$2:$B$77,A38)</f>
@@ -6848,35 +6948,35 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="19" t="s">
-        <v>493</v>
+        <v>556</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="11" t="s">
-        <v>494</v>
+        <v>557</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>490</v>
+        <v>553</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>483</v>
+        <v>546</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>484</v>
+        <v>547</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>491</v>
+        <v>554</v>
       </c>
       <c r="G42" s="11" t="s">
-        <v>492</v>
+        <v>555</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="12" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B43" s="20">
         <f>COUNTIF('Test Cases'!$E$2:$E$77,A43)</f>
@@ -6905,7 +7005,7 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="12" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B44" s="20">
         <f>COUNTIF('Test Cases'!$E$2:$E$77,A44)</f>
@@ -6934,7 +7034,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="12" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="B45" s="20">
         <f>COUNTIF('Test Cases'!$E$2:$E$77,A45)</f>
@@ -6963,7 +7063,7 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="12" t="s">
-        <v>372</v>
+        <v>404</v>
       </c>
       <c r="B46" s="20">
         <f>COUNTIF('Test Cases'!$E$2:$E$77,A46)</f>
@@ -6992,7 +7092,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="12" t="s">
-        <v>402</v>
+        <v>434</v>
       </c>
       <c r="B47" s="20">
         <f>COUNTIF('Test Cases'!$E$2:$E$77,A47)</f>
@@ -7021,7 +7121,7 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="12" t="s">
-        <v>420</v>
+        <v>452</v>
       </c>
       <c r="B48" s="20">
         <f>COUNTIF('Test Cases'!$E$2:$E$77,A48)</f>
@@ -7073,133 +7173,243 @@
   <sheetData>
     <row r="1" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>495</v>
+        <v>558</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>496</v>
+        <v>559</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>497</v>
+        <v>560</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>498</v>
+        <v>561</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>499</v>
+        <v>562</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>500</v>
+        <v>563</v>
       </c>
       <c r="I1" s="11" t="s">
-        <v>501</v>
+        <v>564</v>
       </c>
       <c r="J1" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K1" s="11" t="s">
-        <v>502</v>
+        <v>565</v>
       </c>
       <c r="L1" s="11" t="s">
-        <v>503</v>
+        <v>566</v>
       </c>
       <c r="M1" s="11" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="92.4" x14ac:dyDescent="0.3">
       <c r="A2" s="14" t="s">
-        <v>504</v>
-      </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="22"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
+        <v>567</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>152</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>568</v>
+      </c>
+      <c r="D2" s="16" t="s">
+        <v>569</v>
+      </c>
+      <c r="E2" s="16" t="s">
+        <v>570</v>
+      </c>
+      <c r="F2" s="16" t="s">
+        <v>571</v>
+      </c>
+      <c r="G2" s="16" t="s">
+        <v>572</v>
+      </c>
+      <c r="H2" s="16" t="s">
+        <v>573</v>
+      </c>
+      <c r="I2" s="22">
+        <v>46315</v>
+      </c>
+      <c r="J2" s="16" t="s">
+        <v>574</v>
+      </c>
+      <c r="K2" s="16" t="s">
+        <v>575</v>
+      </c>
       <c r="L2" s="16"/>
-      <c r="M2" s="16"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M2" s="16" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="105.6" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
-        <v>505</v>
-      </c>
-      <c r="B3" s="16"/>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
-      <c r="H3" s="16"/>
-      <c r="I3" s="22"/>
-      <c r="J3" s="16"/>
-      <c r="K3" s="16"/>
+        <v>577</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>208</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>578</v>
+      </c>
+      <c r="D3" s="16" t="s">
+        <v>579</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>580</v>
+      </c>
+      <c r="F3" s="16" t="s">
+        <v>581</v>
+      </c>
+      <c r="G3" s="16" t="s">
+        <v>582</v>
+      </c>
+      <c r="H3" s="16" t="s">
+        <v>573</v>
+      </c>
+      <c r="I3" s="22">
+        <v>46317</v>
+      </c>
+      <c r="J3" s="16" t="s">
+        <v>574</v>
+      </c>
+      <c r="K3" s="16" t="s">
+        <v>583</v>
+      </c>
       <c r="L3" s="16"/>
-      <c r="M3" s="16"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M3" s="16" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="132" x14ac:dyDescent="0.3">
       <c r="A4" s="14" t="s">
-        <v>506</v>
-      </c>
-      <c r="B4" s="16"/>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
-      <c r="H4" s="16"/>
-      <c r="I4" s="22"/>
-      <c r="J4" s="16"/>
-      <c r="K4" s="16"/>
+        <v>585</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>457</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>568</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>586</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>587</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>588</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>589</v>
+      </c>
+      <c r="H4" s="16" t="s">
+        <v>573</v>
+      </c>
+      <c r="I4" s="22">
+        <v>46317</v>
+      </c>
+      <c r="J4" s="16" t="s">
+        <v>590</v>
+      </c>
+      <c r="K4" s="16" t="s">
+        <v>583</v>
+      </c>
       <c r="L4" s="16"/>
-      <c r="M4" s="16"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M4" s="16" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="118.8" x14ac:dyDescent="0.3">
       <c r="A5" s="14" t="s">
-        <v>507</v>
-      </c>
-      <c r="B5" s="16"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="16"/>
-      <c r="H5" s="16"/>
-      <c r="I5" s="22"/>
-      <c r="J5" s="16"/>
-      <c r="K5" s="16"/>
+        <v>592</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>471</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>578</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>593</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>594</v>
+      </c>
+      <c r="F5" s="16" t="s">
+        <v>595</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>596</v>
+      </c>
+      <c r="H5" s="16" t="s">
+        <v>573</v>
+      </c>
+      <c r="I5" s="22">
+        <v>46317</v>
+      </c>
+      <c r="J5" s="16" t="s">
+        <v>574</v>
+      </c>
+      <c r="K5" s="16" t="s">
+        <v>583</v>
+      </c>
       <c r="L5" s="16"/>
-      <c r="M5" s="16"/>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M5" s="16" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="66" x14ac:dyDescent="0.3">
       <c r="A6" s="14" t="s">
-        <v>508</v>
-      </c>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="16"/>
-      <c r="I6" s="22"/>
-      <c r="J6" s="16"/>
-      <c r="K6" s="16"/>
+        <v>598</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>319</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>578</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>599</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>600</v>
+      </c>
+      <c r="F6" s="16" t="s">
+        <v>601</v>
+      </c>
+      <c r="G6" s="16" t="s">
+        <v>602</v>
+      </c>
+      <c r="H6" s="16" t="s">
+        <v>573</v>
+      </c>
+      <c r="I6" s="22">
+        <v>46317</v>
+      </c>
+      <c r="J6" s="16" t="s">
+        <v>574</v>
+      </c>
+      <c r="K6" s="16" t="s">
+        <v>603</v>
+      </c>
       <c r="L6" s="16"/>
-      <c r="M6" s="16"/>
+      <c r="M6" s="16" t="s">
+        <v>604</v>
+      </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="14" t="s">
-        <v>509</v>
+        <v>605</v>
       </c>
       <c r="B7" s="16"/>
       <c r="C7" s="16"/>
@@ -7216,7 +7426,7 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="14" t="s">
-        <v>510</v>
+        <v>606</v>
       </c>
       <c r="B8" s="16"/>
       <c r="C8" s="16"/>
@@ -7233,7 +7443,7 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="14" t="s">
-        <v>511</v>
+        <v>607</v>
       </c>
       <c r="B9" s="16"/>
       <c r="C9" s="16"/>
@@ -7250,7 +7460,7 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="14" t="s">
-        <v>512</v>
+        <v>608</v>
       </c>
       <c r="B10" s="16"/>
       <c r="C10" s="16"/>
@@ -7267,7 +7477,7 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="14" t="s">
-        <v>513</v>
+        <v>609</v>
       </c>
       <c r="B11" s="16"/>
       <c r="C11" s="16"/>
@@ -7284,7 +7494,7 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="14" t="s">
-        <v>514</v>
+        <v>610</v>
       </c>
       <c r="B12" s="16"/>
       <c r="C12" s="16"/>
@@ -7301,7 +7511,7 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="14" t="s">
-        <v>515</v>
+        <v>611</v>
       </c>
       <c r="B13" s="16"/>
       <c r="C13" s="16"/>
@@ -7318,7 +7528,7 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="14" t="s">
-        <v>516</v>
+        <v>612</v>
       </c>
       <c r="B14" s="16"/>
       <c r="C14" s="16"/>
@@ -7335,7 +7545,7 @@
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="14" t="s">
-        <v>517</v>
+        <v>613</v>
       </c>
       <c r="B15" s="16"/>
       <c r="C15" s="16"/>
@@ -7352,7 +7562,7 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="14" t="s">
-        <v>518</v>
+        <v>614</v>
       </c>
       <c r="B16" s="16"/>
       <c r="C16" s="16"/>
@@ -7369,7 +7579,7 @@
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" s="14" t="s">
-        <v>519</v>
+        <v>615</v>
       </c>
       <c r="B17" s="16"/>
       <c r="C17" s="16"/>
@@ -7386,7 +7596,7 @@
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" s="14" t="s">
-        <v>520</v>
+        <v>616</v>
       </c>
       <c r="B18" s="16"/>
       <c r="C18" s="16"/>
@@ -7403,7 +7613,7 @@
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" s="14" t="s">
-        <v>521</v>
+        <v>617</v>
       </c>
       <c r="B19" s="16"/>
       <c r="C19" s="16"/>
@@ -7420,7 +7630,7 @@
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" s="14" t="s">
-        <v>522</v>
+        <v>618</v>
       </c>
       <c r="B20" s="16"/>
       <c r="C20" s="16"/>
@@ -7437,7 +7647,7 @@
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" s="14" t="s">
-        <v>523</v>
+        <v>619</v>
       </c>
       <c r="B21" s="16"/>
       <c r="C21" s="16"/>
@@ -7454,7 +7664,7 @@
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" s="14" t="s">
-        <v>524</v>
+        <v>620</v>
       </c>
       <c r="B22" s="16"/>
       <c r="C22" s="16"/>
@@ -7471,7 +7681,7 @@
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" s="14" t="s">
-        <v>525</v>
+        <v>621</v>
       </c>
       <c r="B23" s="16"/>
       <c r="C23" s="16"/>
@@ -7488,7 +7698,7 @@
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" s="14" t="s">
-        <v>526</v>
+        <v>622</v>
       </c>
       <c r="B24" s="16"/>
       <c r="C24" s="16"/>
@@ -7505,7 +7715,7 @@
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" s="14" t="s">
-        <v>527</v>
+        <v>623</v>
       </c>
       <c r="B25" s="16"/>
       <c r="C25" s="16"/>
@@ -7522,7 +7732,7 @@
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" s="14" t="s">
-        <v>528</v>
+        <v>624</v>
       </c>
       <c r="B26" s="16"/>
       <c r="C26" s="16"/>
@@ -7539,7 +7749,7 @@
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" s="14" t="s">
-        <v>529</v>
+        <v>625</v>
       </c>
       <c r="B27" s="16"/>
       <c r="C27" s="16"/>
@@ -7556,7 +7766,7 @@
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" s="14" t="s">
-        <v>530</v>
+        <v>626</v>
       </c>
       <c r="B28" s="16"/>
       <c r="C28" s="16"/>
@@ -7573,7 +7783,7 @@
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" s="14" t="s">
-        <v>531</v>
+        <v>627</v>
       </c>
       <c r="B29" s="16"/>
       <c r="C29" s="16"/>
@@ -7590,7 +7800,7 @@
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" s="14" t="s">
-        <v>532</v>
+        <v>628</v>
       </c>
       <c r="B30" s="16"/>
       <c r="C30" s="16"/>
@@ -7607,7 +7817,7 @@
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" s="14" t="s">
-        <v>533</v>
+        <v>629</v>
       </c>
       <c r="B31" s="16"/>
       <c r="C31" s="16"/>
@@ -7624,7 +7834,7 @@
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" s="14" t="s">
-        <v>534</v>
+        <v>630</v>
       </c>
       <c r="B32" s="16"/>
       <c r="C32" s="16"/>
@@ -7641,7 +7851,7 @@
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" s="14" t="s">
-        <v>535</v>
+        <v>631</v>
       </c>
       <c r="B33" s="16"/>
       <c r="C33" s="16"/>
@@ -7658,7 +7868,7 @@
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" s="14" t="s">
-        <v>536</v>
+        <v>632</v>
       </c>
       <c r="B34" s="16"/>
       <c r="C34" s="16"/>
@@ -7675,7 +7885,7 @@
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" s="14" t="s">
-        <v>537</v>
+        <v>633</v>
       </c>
       <c r="B35" s="16"/>
       <c r="C35" s="16"/>
@@ -7692,7 +7902,7 @@
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36" s="14" t="s">
-        <v>538</v>
+        <v>634</v>
       </c>
       <c r="B36" s="16"/>
       <c r="C36" s="16"/>
@@ -7709,7 +7919,7 @@
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" s="14" t="s">
-        <v>539</v>
+        <v>635</v>
       </c>
       <c r="B37" s="16"/>
       <c r="C37" s="16"/>
@@ -7726,7 +7936,7 @@
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" s="14" t="s">
-        <v>540</v>
+        <v>636</v>
       </c>
       <c r="B38" s="16"/>
       <c r="C38" s="16"/>
@@ -7743,7 +7953,7 @@
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39" s="14" t="s">
-        <v>541</v>
+        <v>637</v>
       </c>
       <c r="B39" s="16"/>
       <c r="C39" s="16"/>
@@ -7760,7 +7970,7 @@
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A40" s="14" t="s">
-        <v>542</v>
+        <v>638</v>
       </c>
       <c r="B40" s="16"/>
       <c r="C40" s="16"/>
@@ -7777,7 +7987,7 @@
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41" s="14" t="s">
-        <v>543</v>
+        <v>639</v>
       </c>
       <c r="B41" s="16"/>
       <c r="C41" s="16"/>
@@ -7794,7 +8004,7 @@
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A42" s="14" t="s">
-        <v>544</v>
+        <v>640</v>
       </c>
       <c r="B42" s="16"/>
       <c r="C42" s="16"/>
@@ -7811,7 +8021,7 @@
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A43" s="14" t="s">
-        <v>545</v>
+        <v>641</v>
       </c>
       <c r="B43" s="16"/>
       <c r="C43" s="16"/>
@@ -7828,7 +8038,7 @@
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A44" s="14" t="s">
-        <v>546</v>
+        <v>642</v>
       </c>
       <c r="B44" s="16"/>
       <c r="C44" s="16"/>
@@ -7845,7 +8055,7 @@
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A45" s="14" t="s">
-        <v>547</v>
+        <v>643</v>
       </c>
       <c r="B45" s="16"/>
       <c r="C45" s="16"/>
@@ -7862,7 +8072,7 @@
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A46" s="14" t="s">
-        <v>548</v>
+        <v>644</v>
       </c>
       <c r="B46" s="16"/>
       <c r="C46" s="16"/>
@@ -7879,7 +8089,7 @@
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A47" s="14" t="s">
-        <v>549</v>
+        <v>645</v>
       </c>
       <c r="B47" s="16"/>
       <c r="C47" s="16"/>
@@ -7896,7 +8106,7 @@
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A48" s="14" t="s">
-        <v>550</v>
+        <v>646</v>
       </c>
       <c r="B48" s="16"/>
       <c r="C48" s="16"/>
@@ -7913,7 +8123,7 @@
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A49" s="14" t="s">
-        <v>551</v>
+        <v>647</v>
       </c>
       <c r="B49" s="16"/>
       <c r="C49" s="16"/>
@@ -7930,7 +8140,7 @@
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A50" s="14" t="s">
-        <v>552</v>
+        <v>648</v>
       </c>
       <c r="B50" s="16"/>
       <c r="C50" s="16"/>
@@ -7947,7 +8157,7 @@
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A51" s="14" t="s">
-        <v>553</v>
+        <v>649</v>
       </c>
       <c r="B51" s="16"/>
       <c r="C51" s="16"/>
@@ -7964,7 +8174,7 @@
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A52" s="14" t="s">
-        <v>554</v>
+        <v>650</v>
       </c>
       <c r="B52" s="16"/>
       <c r="C52" s="16"/>
@@ -7981,7 +8191,7 @@
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A53" s="14" t="s">
-        <v>555</v>
+        <v>651</v>
       </c>
       <c r="B53" s="16"/>
       <c r="C53" s="16"/>
@@ -7998,7 +8208,7 @@
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A54" s="14" t="s">
-        <v>556</v>
+        <v>652</v>
       </c>
       <c r="B54" s="16"/>
       <c r="C54" s="16"/>
@@ -8015,7 +8225,7 @@
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A55" s="14" t="s">
-        <v>557</v>
+        <v>653</v>
       </c>
       <c r="B55" s="16"/>
       <c r="C55" s="16"/>
@@ -8032,7 +8242,7 @@
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A56" s="14" t="s">
-        <v>558</v>
+        <v>654</v>
       </c>
       <c r="B56" s="16"/>
       <c r="C56" s="16"/>
@@ -8049,7 +8259,7 @@
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A57" s="14" t="s">
-        <v>559</v>
+        <v>655</v>
       </c>
       <c r="B57" s="16"/>
       <c r="C57" s="16"/>
@@ -8066,7 +8276,7 @@
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A58" s="14" t="s">
-        <v>560</v>
+        <v>656</v>
       </c>
       <c r="B58" s="16"/>
       <c r="C58" s="16"/>
@@ -8083,7 +8293,7 @@
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A59" s="14" t="s">
-        <v>561</v>
+        <v>657</v>
       </c>
       <c r="B59" s="16"/>
       <c r="C59" s="16"/>
@@ -8100,7 +8310,7 @@
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A60" s="14" t="s">
-        <v>562</v>
+        <v>658</v>
       </c>
       <c r="B60" s="16"/>
       <c r="C60" s="16"/>
@@ -8117,7 +8327,7 @@
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A61" s="14" t="s">
-        <v>563</v>
+        <v>659</v>
       </c>
       <c r="B61" s="16"/>
       <c r="C61" s="16"/>
@@ -8134,15 +8344,15 @@
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A63" s="23" t="s">
-        <v>564</v>
+        <v>660</v>
       </c>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A64" s="5" t="s">
-        <v>565</v>
+        <v>661</v>
       </c>
       <c r="B64" s="26" t="s">
-        <v>566</v>
+        <v>662</v>
       </c>
       <c r="C64" s="25"/>
       <c r="D64" s="25"/>
@@ -8151,10 +8361,10 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" s="5" t="s">
-        <v>567</v>
+        <v>663</v>
       </c>
       <c r="B65" s="26" t="s">
-        <v>568</v>
+        <v>664</v>
       </c>
       <c r="C65" s="25"/>
       <c r="D65" s="25"/>
@@ -8163,10 +8373,10 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" s="5" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B66" s="26" t="s">
-        <v>570</v>
+        <v>665</v>
       </c>
       <c r="C66" s="25"/>
       <c r="D66" s="25"/>
@@ -8175,10 +8385,10 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" s="5" t="s">
-        <v>571</v>
+        <v>578</v>
       </c>
       <c r="B67" s="26" t="s">
-        <v>572</v>
+        <v>666</v>
       </c>
       <c r="C67" s="25"/>
       <c r="D67" s="25"/>

--- a/03-Testing/EduCheck_UAT_Test_Cases.xlsx
+++ b/03-Testing/EduCheck_UAT_Test_Cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/998bf0dccc2814d1/Documents/GitHub/Capstone-Project_EduCheck/03-Testing/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_C1F5BA203F8BA9F4AE009BB4139EBEDC2939DAAE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="52" documentId="11_C1F5BA203F8BA9F4AE009BB4139EBEDC2939DAAE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CF5645EF-A61C-4190-AC0B-0DB59C8CD1E5}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="11712" windowHeight="12240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1105" uniqueCount="667">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1131" uniqueCount="667">
   <si>
     <t>EduCheck - User Acceptance Test Cases</t>
   </si>
@@ -5165,9 +5165,15 @@
         <v>409</v>
       </c>
       <c r="L53" s="16"/>
-      <c r="M53" s="17"/>
-      <c r="N53" s="16"/>
-      <c r="O53" s="18"/>
+      <c r="M53" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="N53" s="16" t="s">
+        <v>573</v>
+      </c>
+      <c r="O53" s="18">
+        <v>46311</v>
+      </c>
       <c r="P53" s="17"/>
       <c r="Q53" s="16"/>
     </row>
@@ -5206,9 +5212,15 @@
         <v>414</v>
       </c>
       <c r="L54" s="16"/>
-      <c r="M54" s="17"/>
-      <c r="N54" s="16"/>
-      <c r="O54" s="18"/>
+      <c r="M54" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="N54" s="16" t="s">
+        <v>573</v>
+      </c>
+      <c r="O54" s="18">
+        <v>46311</v>
+      </c>
       <c r="P54" s="17"/>
       <c r="Q54" s="16"/>
     </row>
@@ -5247,9 +5259,15 @@
         <v>419</v>
       </c>
       <c r="L55" s="16"/>
-      <c r="M55" s="17"/>
-      <c r="N55" s="16"/>
-      <c r="O55" s="18"/>
+      <c r="M55" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="N55" s="16" t="s">
+        <v>573</v>
+      </c>
+      <c r="O55" s="18">
+        <v>46311</v>
+      </c>
       <c r="P55" s="17"/>
       <c r="Q55" s="16"/>
     </row>
@@ -5288,9 +5306,15 @@
         <v>423</v>
       </c>
       <c r="L56" s="16"/>
-      <c r="M56" s="17"/>
-      <c r="N56" s="16"/>
-      <c r="O56" s="18"/>
+      <c r="M56" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="N56" s="16" t="s">
+        <v>573</v>
+      </c>
+      <c r="O56" s="18">
+        <v>46311</v>
+      </c>
       <c r="P56" s="17"/>
       <c r="Q56" s="16"/>
     </row>
@@ -5329,9 +5353,15 @@
         <v>428</v>
       </c>
       <c r="L57" s="16"/>
-      <c r="M57" s="17"/>
-      <c r="N57" s="16"/>
-      <c r="O57" s="18"/>
+      <c r="M57" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="N57" s="16" t="s">
+        <v>573</v>
+      </c>
+      <c r="O57" s="18">
+        <v>46311</v>
+      </c>
       <c r="P57" s="17"/>
       <c r="Q57" s="16"/>
     </row>
@@ -5370,9 +5400,15 @@
         <v>432</v>
       </c>
       <c r="L58" s="16"/>
-      <c r="M58" s="17"/>
-      <c r="N58" s="16"/>
-      <c r="O58" s="18"/>
+      <c r="M58" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="N58" s="16" t="s">
+        <v>573</v>
+      </c>
+      <c r="O58" s="18">
+        <v>46311</v>
+      </c>
       <c r="P58" s="17"/>
       <c r="Q58" s="16"/>
     </row>
@@ -5411,9 +5447,15 @@
         <v>438</v>
       </c>
       <c r="L59" s="16"/>
-      <c r="M59" s="17"/>
-      <c r="N59" s="16"/>
-      <c r="O59" s="18"/>
+      <c r="M59" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="N59" s="16" t="s">
+        <v>573</v>
+      </c>
+      <c r="O59" s="18">
+        <v>46311</v>
+      </c>
       <c r="P59" s="17"/>
       <c r="Q59" s="16"/>
     </row>
@@ -5452,9 +5494,15 @@
         <v>444</v>
       </c>
       <c r="L60" s="16"/>
-      <c r="M60" s="17"/>
-      <c r="N60" s="16"/>
-      <c r="O60" s="18"/>
+      <c r="M60" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="N60" s="16" t="s">
+        <v>573</v>
+      </c>
+      <c r="O60" s="18">
+        <v>46311</v>
+      </c>
       <c r="P60" s="17"/>
       <c r="Q60" s="16"/>
     </row>
@@ -5493,9 +5541,15 @@
         <v>449</v>
       </c>
       <c r="L61" s="16"/>
-      <c r="M61" s="17"/>
-      <c r="N61" s="16"/>
-      <c r="O61" s="18"/>
+      <c r="M61" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="N61" s="16" t="s">
+        <v>573</v>
+      </c>
+      <c r="O61" s="18">
+        <v>46311</v>
+      </c>
       <c r="P61" s="17"/>
       <c r="Q61" s="16"/>
     </row>
@@ -5616,9 +5670,15 @@
         <v>465</v>
       </c>
       <c r="L64" s="16"/>
-      <c r="M64" s="17"/>
-      <c r="N64" s="16"/>
-      <c r="O64" s="18"/>
+      <c r="M64" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="N64" s="16" t="s">
+        <v>573</v>
+      </c>
+      <c r="O64" s="18">
+        <v>46311</v>
+      </c>
       <c r="P64" s="17"/>
       <c r="Q64" s="16"/>
     </row>
@@ -5657,9 +5717,15 @@
         <v>470</v>
       </c>
       <c r="L65" s="16"/>
-      <c r="M65" s="17"/>
-      <c r="N65" s="16"/>
-      <c r="O65" s="18"/>
+      <c r="M65" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="N65" s="16" t="s">
+        <v>573</v>
+      </c>
+      <c r="O65" s="18">
+        <v>46311</v>
+      </c>
       <c r="P65" s="17"/>
       <c r="Q65" s="16"/>
     </row>
@@ -5698,9 +5764,15 @@
         <v>475</v>
       </c>
       <c r="L66" s="16"/>
-      <c r="M66" s="17"/>
-      <c r="N66" s="16"/>
-      <c r="O66" s="18"/>
+      <c r="M66" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="N66" s="16" t="s">
+        <v>573</v>
+      </c>
+      <c r="O66" s="18">
+        <v>46311</v>
+      </c>
       <c r="P66" s="17"/>
       <c r="Q66" s="16"/>
     </row>
@@ -5739,9 +5811,15 @@
         <v>480</v>
       </c>
       <c r="L67" s="16"/>
-      <c r="M67" s="17"/>
-      <c r="N67" s="16"/>
-      <c r="O67" s="18"/>
+      <c r="M67" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="N67" s="16" t="s">
+        <v>573</v>
+      </c>
+      <c r="O67" s="18">
+        <v>46311</v>
+      </c>
       <c r="P67" s="17"/>
       <c r="Q67" s="16"/>
     </row>
@@ -6223,7 +6301,7 @@
       </c>
       <c r="B6" s="20">
         <f>COUNTIF('Test Cases'!$M$2:$M$77,"Pass")</f>
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -6250,7 +6328,7 @@
       </c>
       <c r="B9" s="20">
         <f>B5-B6-B7-B8</f>
-        <v>76</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
@@ -6259,16 +6337,16 @@
       </c>
       <c r="B10" s="20">
         <f>B6+B7</f>
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
         <v>550</v>
       </c>
-      <c r="B11" s="21" t="str">
+      <c r="B11" s="21">
         <f>IF(B10=0,"-",B6/B10)</f>
-        <v>-</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
@@ -6277,7 +6355,7 @@
       </c>
       <c r="B12" s="21">
         <f>IF(B5=0,"-",(B10+B8)/B5)</f>
-        <v>0</v>
+        <v>0.17105263157894737</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
@@ -6811,7 +6889,7 @@
       </c>
       <c r="C34" s="20">
         <f>COUNTIFS('Test Cases'!$B$2:$B$77,A34,'Test Cases'!$M$2:$M$77,"Pass")</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D34" s="20">
         <f>COUNTIFS('Test Cases'!$B$2:$B$77,A34,'Test Cases'!$M$2:$M$77,"Fail")</f>
@@ -6823,11 +6901,11 @@
       </c>
       <c r="F34" s="20">
         <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="G34" s="21" t="str">
+        <v>0</v>
+      </c>
+      <c r="G34" s="21">
         <f t="shared" si="1"/>
-        <v>-</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
@@ -6869,7 +6947,7 @@
       </c>
       <c r="C36" s="20">
         <f>COUNTIFS('Test Cases'!$B$2:$B$77,A36,'Test Cases'!$M$2:$M$77,"Pass")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D36" s="20">
         <f>COUNTIFS('Test Cases'!$B$2:$B$77,A36,'Test Cases'!$M$2:$M$77,"Fail")</f>
@@ -6881,11 +6959,11 @@
       </c>
       <c r="F36" s="20">
         <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="G36" s="21" t="str">
+        <v>0</v>
+      </c>
+      <c r="G36" s="21">
         <f t="shared" si="1"/>
-        <v>-</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
@@ -6898,7 +6976,7 @@
       </c>
       <c r="C37" s="20">
         <f>COUNTIFS('Test Cases'!$B$2:$B$77,A37,'Test Cases'!$M$2:$M$77,"Pass")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D37" s="20">
         <f>COUNTIFS('Test Cases'!$B$2:$B$77,A37,'Test Cases'!$M$2:$M$77,"Fail")</f>
@@ -6910,11 +6988,11 @@
       </c>
       <c r="F37" s="20">
         <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="G37" s="21" t="str">
+        <v>0</v>
+      </c>
+      <c r="G37" s="21">
         <f t="shared" si="1"/>
-        <v>-</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
@@ -6984,7 +7062,7 @@
       </c>
       <c r="C43" s="20">
         <f>COUNTIFS('Test Cases'!$E$2:$E$77,A43,'Test Cases'!$M$2:$M$77,"Pass")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D43" s="20">
         <f>COUNTIFS('Test Cases'!$E$2:$E$77,A43,'Test Cases'!$M$2:$M$77,"Fail")</f>
@@ -6996,11 +7074,11 @@
       </c>
       <c r="F43" s="20">
         <f t="shared" ref="F43:F48" si="2">B43-C43-D43-E43</f>
-        <v>19</v>
-      </c>
-      <c r="G43" s="21" t="str">
+        <v>17</v>
+      </c>
+      <c r="G43" s="21">
         <f t="shared" ref="G43:G48" si="3">IF(C43+D43=0,"-",C43/(C43+D43))</f>
-        <v>-</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
@@ -7013,7 +7091,7 @@
       </c>
       <c r="C44" s="20">
         <f>COUNTIFS('Test Cases'!$E$2:$E$77,A44,'Test Cases'!$M$2:$M$77,"Pass")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D44" s="20">
         <f>COUNTIFS('Test Cases'!$E$2:$E$77,A44,'Test Cases'!$M$2:$M$77,"Fail")</f>
@@ -7025,11 +7103,11 @@
       </c>
       <c r="F44" s="20">
         <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="G44" s="21" t="str">
+        <v>2</v>
+      </c>
+      <c r="G44" s="21">
         <f t="shared" si="3"/>
-        <v>-</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
@@ -7042,7 +7120,7 @@
       </c>
       <c r="C45" s="20">
         <f>COUNTIFS('Test Cases'!$E$2:$E$77,A45,'Test Cases'!$M$2:$M$77,"Pass")</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D45" s="20">
         <f>COUNTIFS('Test Cases'!$E$2:$E$77,A45,'Test Cases'!$M$2:$M$77,"Fail")</f>
@@ -7054,11 +7132,11 @@
       </c>
       <c r="F45" s="20">
         <f t="shared" si="2"/>
-        <v>47</v>
-      </c>
-      <c r="G45" s="21" t="str">
+        <v>42</v>
+      </c>
+      <c r="G45" s="21">
         <f t="shared" si="3"/>
-        <v>-</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
@@ -7071,7 +7149,7 @@
       </c>
       <c r="C46" s="20">
         <f>COUNTIFS('Test Cases'!$E$2:$E$77,A46,'Test Cases'!$M$2:$M$77,"Pass")</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D46" s="20">
         <f>COUNTIFS('Test Cases'!$E$2:$E$77,A46,'Test Cases'!$M$2:$M$77,"Fail")</f>
@@ -7083,11 +7161,11 @@
       </c>
       <c r="F46" s="20">
         <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-      <c r="G46" s="21" t="str">
+        <v>0</v>
+      </c>
+      <c r="G46" s="21">
         <f t="shared" si="3"/>
-        <v>-</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
@@ -7100,7 +7178,7 @@
       </c>
       <c r="C47" s="20">
         <f>COUNTIFS('Test Cases'!$E$2:$E$77,A47,'Test Cases'!$M$2:$M$77,"Pass")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D47" s="20">
         <f>COUNTIFS('Test Cases'!$E$2:$E$77,A47,'Test Cases'!$M$2:$M$77,"Fail")</f>
@@ -7112,11 +7190,11 @@
       </c>
       <c r="F47" s="20">
         <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G47" s="21">
+        <f t="shared" si="3"/>
         <v>1</v>
-      </c>
-      <c r="G47" s="21" t="str">
-        <f t="shared" si="3"/>
-        <v>-</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">

--- a/03-Testing/EduCheck_UAT_Test_Cases.xlsx
+++ b/03-Testing/EduCheck_UAT_Test_Cases.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/998bf0dccc2814d1/Documents/GitHub/Capstone-Project_EduCheck/03-Testing/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="52" documentId="11_C1F5BA203F8BA9F4AE009BB4139EBEDC2939DAAE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CF5645EF-A61C-4190-AC0B-0DB59C8CD1E5}"/>
+  <xr:revisionPtr revIDLastSave="78" documentId="11_C1F5BA203F8BA9F4AE009BB4139EBEDC2939DAAE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5C5A46DE-A9AB-46F7-A2A5-2FB0AD72CC6E}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="11712" windowHeight="12240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -2334,6 +2334,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5172,7 +5176,7 @@
         <v>573</v>
       </c>
       <c r="O53" s="18">
-        <v>46311</v>
+        <v>46310</v>
       </c>
       <c r="P53" s="17"/>
       <c r="Q53" s="16"/>
@@ -5219,7 +5223,7 @@
         <v>573</v>
       </c>
       <c r="O54" s="18">
-        <v>46311</v>
+        <v>46310</v>
       </c>
       <c r="P54" s="17"/>
       <c r="Q54" s="16"/>
@@ -5266,7 +5270,7 @@
         <v>573</v>
       </c>
       <c r="O55" s="18">
-        <v>46311</v>
+        <v>46310</v>
       </c>
       <c r="P55" s="17"/>
       <c r="Q55" s="16"/>
@@ -5313,7 +5317,7 @@
         <v>573</v>
       </c>
       <c r="O56" s="18">
-        <v>46311</v>
+        <v>46310</v>
       </c>
       <c r="P56" s="17"/>
       <c r="Q56" s="16"/>
@@ -5360,7 +5364,7 @@
         <v>573</v>
       </c>
       <c r="O57" s="18">
-        <v>46311</v>
+        <v>46310</v>
       </c>
       <c r="P57" s="17"/>
       <c r="Q57" s="16"/>
@@ -5407,7 +5411,7 @@
         <v>573</v>
       </c>
       <c r="O58" s="18">
-        <v>46311</v>
+        <v>46310</v>
       </c>
       <c r="P58" s="17"/>
       <c r="Q58" s="16"/>
@@ -5454,7 +5458,7 @@
         <v>573</v>
       </c>
       <c r="O59" s="18">
-        <v>46311</v>
+        <v>46310</v>
       </c>
       <c r="P59" s="17"/>
       <c r="Q59" s="16"/>
@@ -5501,7 +5505,7 @@
         <v>573</v>
       </c>
       <c r="O60" s="18">
-        <v>46311</v>
+        <v>46310</v>
       </c>
       <c r="P60" s="17"/>
       <c r="Q60" s="16"/>
@@ -5548,7 +5552,7 @@
         <v>573</v>
       </c>
       <c r="O61" s="18">
-        <v>46311</v>
+        <v>46310</v>
       </c>
       <c r="P61" s="17"/>
       <c r="Q61" s="16"/>
@@ -5677,7 +5681,7 @@
         <v>573</v>
       </c>
       <c r="O64" s="18">
-        <v>46311</v>
+        <v>46310</v>
       </c>
       <c r="P64" s="17"/>
       <c r="Q64" s="16"/>
@@ -5724,7 +5728,7 @@
         <v>573</v>
       </c>
       <c r="O65" s="18">
-        <v>46311</v>
+        <v>46310</v>
       </c>
       <c r="P65" s="17"/>
       <c r="Q65" s="16"/>
@@ -5771,7 +5775,7 @@
         <v>573</v>
       </c>
       <c r="O66" s="18">
-        <v>46311</v>
+        <v>46310</v>
       </c>
       <c r="P66" s="17"/>
       <c r="Q66" s="16"/>
@@ -5818,7 +5822,7 @@
         <v>573</v>
       </c>
       <c r="O67" s="18">
-        <v>46311</v>
+        <v>46310</v>
       </c>
       <c r="P67" s="17"/>
       <c r="Q67" s="16"/>

--- a/03-Testing/EduCheck_UAT_Test_Cases.xlsx
+++ b/03-Testing/EduCheck_UAT_Test_Cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/998bf0dccc2814d1/Documents/GitHub/Capstone-Project_EduCheck/03-Testing/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="78" documentId="11_C1F5BA203F8BA9F4AE009BB4139EBEDC2939DAAE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5C5A46DE-A9AB-46F7-A2A5-2FB0AD72CC6E}"/>
+  <xr:revisionPtr revIDLastSave="81" documentId="11_C1F5BA203F8BA9F4AE009BB4139EBEDC2939DAAE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{68F26646-EBB3-4A0C-9456-35907B022EF1}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1131" uniqueCount="667">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1134" uniqueCount="670">
   <si>
     <t>EduCheck - User Acceptance Test Cases</t>
   </si>
@@ -2125,6 +2125,15 @@
   </si>
   <si>
     <t>Cosmetic: layout, wording, alignment.</t>
+  </si>
+  <si>
+    <t>Automated run 2026-10-23: Pass with remarks. The message reads "Username or password is incorrect. Check both and try again." instead of "Invalid username or password."; it still does not say which field was wrong.</t>
+  </si>
+  <si>
+    <t>Automated run 2026-10-23: Pass with remarks. The unread count on the Notifications page drops to 0 at once; the sidebar badge updates only after the page is refreshed.</t>
+  </si>
+  <si>
+    <t>Automated run 2026-10-23: Pass with remarks. Measured on the local server only; the first load of the hosted (Render) system is still slow (DEF-003).</t>
   </si>
 </sst>
 </file>
@@ -3123,7 +3132,9 @@
       <c r="N3" s="16"/>
       <c r="O3" s="18"/>
       <c r="P3" s="17"/>
-      <c r="Q3" s="16"/>
+      <c r="Q3" s="16" t="s">
+        <v>667</v>
+      </c>
     </row>
     <row r="4" spans="1:17" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="14" t="s">
@@ -5132,7 +5143,9 @@
       <c r="N52" s="16"/>
       <c r="O52" s="18"/>
       <c r="P52" s="17"/>
-      <c r="Q52" s="16"/>
+      <c r="Q52" s="16" t="s">
+        <v>668</v>
+      </c>
     </row>
     <row r="53" spans="1:17" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="14" t="s">
@@ -5637,7 +5650,9 @@
       <c r="N63" s="16"/>
       <c r="O63" s="18"/>
       <c r="P63" s="17"/>
-      <c r="Q63" s="16"/>
+      <c r="Q63" s="16" t="s">
+        <v>669</v>
+      </c>
     </row>
     <row r="64" spans="1:17" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="14" t="s">
